--- a/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
+++ b/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
@@ -13,12 +13,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_TA_Excluded_Sample" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Extraction_Verification" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_RoB_Review" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_FullText_ToObtain" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1_FullText_Inclusion'!$A$1:$I$244</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2_TA_Excluded_Sample'!$A$1:$E$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3_Extraction_Verification'!$A$1:$M$149</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4_RoB_Review'!$A$1:$Q$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -293,6 +295,21 @@
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>Where in the source the value came from — go here to confirm the extracted numbers.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>validation</author>
+  </authors>
+  <commentList>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>HIGH: a 'not retrieved' exclusion (a study we could not obtain, so eligibility is unconfirmed — the main risk of a missed study) or a quantitative estimate extracted without the main PDF. Obtain these first.</t>
       </text>
     </comment>
   </commentList>
@@ -588,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -687,22 +704,43 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Sheet 6 — Full-text to obtain (90 reports with no local PDF): obtain each and confirm/override the</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        include/exclude decision (cols G–H). HIGH-risk rows first — these are studies we could not</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        retrieve, the main place an eligible study could have been missed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Sheet 5 — Summary: agreement rates, computed automatically. Nothing to fill here.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Row 2 of each sheet is a grey EXAMPLE row showing the expected format — delete it before finalizing.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Yellow = you fill.  White = AI reference (do not edit).  Dropdowns are provided where applicable.</t>
         </is>
@@ -719,7 +757,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -938,8 +976,59 @@
         <v/>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Full-text reports to obtain (Sheet 6)</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Reports without local PDF</t>
+        </is>
+      </c>
+      <c r="B24" s="7">
+        <f>COUNTA('6_FullText_ToObtain'!A3:A400)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HIGH-risk (obtain first)</t>
+        </is>
+      </c>
+      <c r="B25" s="7">
+        <f>COUNTIF('6_FullText_ToObtain'!F3:F400,"HIGH*")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Author obtained</t>
+        </is>
+      </c>
+      <c r="B26" s="7">
+        <f>COUNTA('6_FullText_ToObtain'!G3:G400)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Obtained rate</t>
+        </is>
+      </c>
+      <c r="B27" s="8">
+        <f>IFERROR(B26/B24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Rates populate automatically as you fill the yellow columns in each sheet.</t>
         </is>
@@ -14490,12 +14579,12 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>140.4 [137.6, 143.2]</t>
         </is>
       </c>
       <c r="H41" s="13" t="inlineStr">
         <is>
-          <t>0.755 [0.677, 0.842]</t>
+          <t>0.769 [0.688, 0.860]</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
@@ -14505,7 +14594,7 @@
       </c>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>Table 4 (female breast)</t>
+          <t>Table 4 (origin female-breast rates); Table 2 (NHW-FL reference)</t>
         </is>
       </c>
       <c r="K41" s="15" t="inlineStr"/>
@@ -14545,12 +14634,12 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>140.4 [137.6, 143.2]</t>
         </is>
       </c>
       <c r="H42" s="13" t="inlineStr">
         <is>
-          <t>0.503 [0.376, 0.673]</t>
+          <t>0.512 [0.382, 0.686]</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
@@ -14560,7 +14649,7 @@
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>Table 4 (female breast)</t>
+          <t>Table 4 (origin female-breast rates); Table 2 (NHW-FL reference)</t>
         </is>
       </c>
       <c r="K42" s="15" t="inlineStr"/>
@@ -14600,12 +14689,12 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>140.4 [137.6, 143.2]</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
-          <t>0.817 [0.726, 0.920]</t>
+          <t>0.833 [0.738, 0.939]</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -14615,7 +14704,7 @@
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>Table 4 (female breast)</t>
+          <t>Table 4 (origin female-breast rates); Table 2 (NHW-FL reference)</t>
         </is>
       </c>
       <c r="K43" s="15" t="inlineStr"/>
@@ -14655,12 +14744,12 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>140.4 [137.6, 143.2]</t>
         </is>
       </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>0.684 [0.619, 0.756]</t>
+          <t>0.697 [0.629, 0.771]</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
@@ -14670,7 +14759,7 @@
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>Table 4 (female breast)</t>
+          <t>Table 4 (origin female-breast rates); Table 2 (NHW-FL reference)</t>
         </is>
       </c>
       <c r="K44" s="15" t="inlineStr"/>
@@ -23571,4 +23660,3215 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>record_id</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Current decision (AI)</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Citation / title</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>PMID</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>DOI</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>AUTHOR obtained full text? (Yes/No)</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>AUTHOR final decision (Include/Exclude)</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>AUTHOR note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>e.g. 2038</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Full text unavailable)</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Incidence trends in TNBC...</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr"/>
+      <c r="E2" s="11" t="inlineStr"/>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>HIGH — not retrieved (possible missed study)</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>Exclude</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>overlaps Sung 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (quant-extracted)</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>State Variation in Racial and Ethnic Disparities in Incidence of Triple-Negative Breast Cancer among US Women (2023)</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>36862439</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>10.1001/jamaoncol.2022.7835</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>HIGH — extracted without main PDF</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr"/>
+      <c r="H3" s="15" t="inlineStr"/>
+      <c r="I3" s="16" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (quant-extracted)</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Variation in breast cancer subtype incidence and distribution by race/ethnicity in the United States from 2010 to 2015 (2020)</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>33074325</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>10.1001/jamanetworkopen.2020.20303</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>HIGH — extracted without main PDF</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr"/>
+      <c r="H4" s="15" t="inlineStr"/>
+      <c r="I4" s="16" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Full text unavailable)</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>Breast cancer trends among black and white women in the United States (2005)</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>16258086</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>10.1200/jco.2004.01.0421</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>HIGH — not retrieved (possible missed study)</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr"/>
+      <c r="H5" s="15" t="inlineStr"/>
+      <c r="I5" s="16" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Full text unavailable)</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Breast cancer patterns and lifetime risk of developing breast cancer among Puerto Rican females. (2000)</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>10761199</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr"/>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>HIGH — not retrieved (possible missed study)</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr"/>
+      <c r="H6" s="15" t="inlineStr"/>
+      <c r="I6" s="16" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Full text unavailable)</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Women's cancers among Alaska Natives 1969-2003. (2006)</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>17929614</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr"/>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>HIGH — not retrieved (possible missed study)</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr"/>
+      <c r="H7" s="15" t="inlineStr"/>
+      <c r="I7" s="16" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Full text unavailable)</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Breast cancer in a multiethnic cohort in Hawaii and Los Angeles: Risk factor-adjusted incidence in Japanese equals and in Hawaiians exceeds that in whites (2002)</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>12223421</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr"/>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>HIGH — not retrieved (possible missed study)</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr"/>
+      <c r="H8" s="15" t="inlineStr"/>
+      <c r="I8" s="16" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Full text unavailable)</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Women's cancers among Alaska Natives: [corrected] 1969-2003. (2007)</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>18323374</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>HIGH — not retrieved (possible missed study)</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr"/>
+      <c r="H9" s="15" t="inlineStr"/>
+      <c r="I9" s="16" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>476</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Full text unavailable)</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Rural–urban disparities in breast cancer incidence among US women aged 20–49: trends by race/ethnicity, stage, poverty, and state from 2000–2019 (2026)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>41665696</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s10552-026-02134-3</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>HIGH — not retrieved (possible missed study)</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr"/>
+      <c r="H10" s="15" t="inlineStr"/>
+      <c r="I10" s="16" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>2038</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Full text unavailable)</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>Incidence trends in triple-negative breast cancer among women in the United States from 2010 to 2019 by race/ethnicity, age and tumor stage (2023)</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr"/>
+      <c r="E11" s="13" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>HIGH — not retrieved (possible missed study)</t>
+        </is>
+      </c>
+      <c r="G11" s="15" t="inlineStr"/>
+      <c r="H11" s="15" t="inlineStr"/>
+      <c r="I11" s="16" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>3116</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Full text unavailable)</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>Time trends and racial differences in female breast cancer incidence in Pennsylvania, 1985-2004 (2011)</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr"/>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>10.1089/jwh.2010.2082</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>HIGH — not retrieved (possible missed study)</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr"/>
+      <c r="H12" s="15" t="inlineStr"/>
+      <c r="I12" s="16" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Full text unavailable)</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr">
+        <is>
+          <t>Improving cancer incidence estimates for American Indians in Wisconsin (2007)</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>17844709</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>HIGH — not retrieved (possible missed study)</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr"/>
+      <c r="H13" s="15" t="inlineStr"/>
+      <c r="I13" s="16" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (quant-eligible)</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr">
+        <is>
+          <t>Racial and regional disparities of triple negative breast cancer incidence rates in the United States: An analysis of 2011-2019 NPCR and SEER incidence data (2022)</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>36530732</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>10.3389/fpubh.2022.1058722</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>MED — eligible, not extracted</t>
+        </is>
+      </c>
+      <c r="G14" s="15" t="inlineStr"/>
+      <c r="H14" s="15" t="inlineStr"/>
+      <c r="I14" s="16" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (quant-eligible)</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Higher population-based incidence rates of triple-negative breast cancer among young African-American women (2011)</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>21656753</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.25862</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>MED — eligible, not extracted</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr"/>
+      <c r="H15" s="15" t="inlineStr"/>
+      <c r="I15" s="16" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (quant-eligible)</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Cancer disparities among non-Hispanic urban American Indian and Alaska Native populations in the United States, 1999-2017 (2022)</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>35119703</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.34122</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>MED — eligible, not extracted</t>
+        </is>
+      </c>
+      <c r="G16" s="15" t="inlineStr"/>
+      <c r="H16" s="15" t="inlineStr"/>
+      <c r="I16" s="16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (quant-eligible)</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Cancer incidence among Asian American populations in the United States, 2009-2011 (2016)</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>26661680</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/ijc.29958</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>MED — eligible, not extracted</t>
+        </is>
+      </c>
+      <c r="G17" s="15" t="inlineStr"/>
+      <c r="H17" s="15" t="inlineStr"/>
+      <c r="I17" s="16" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Did not report the outcome of interest)</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Stage IV Breast Cancer Incidence and Survival, 2010-202 (2026)</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>42118535</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>10.1001/jamanetworkopen.2026.12042</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>MED — excluded without full text</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr"/>
+      <c r="H18" s="15" t="inlineStr"/>
+      <c r="I18" s="16" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Did not report the outcome of interest)</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Triple-negative breast cancer incidence in the United States: ecological correlations with area-level sociodemographics, healthcare, and health behaviors (2021)</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>32671723</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s12282-020-01132-w</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>MED — excluded without full text</t>
+        </is>
+      </c>
+      <c r="G19" s="15" t="inlineStr"/>
+      <c r="H19" s="15" t="inlineStr"/>
+      <c r="I19" s="16" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Did not report the outcome of interest)</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Risks of developing breast and colorectal cancer in association with incomes and geographic locations in Texas: A retrospective cohort study (2016)</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>27118258</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>10.1186/s12885-016-2324-z</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>MED — excluded without full text</t>
+        </is>
+      </c>
+      <c r="G20" s="15" t="inlineStr"/>
+      <c r="H20" s="15" t="inlineStr"/>
+      <c r="I20" s="16" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Breast Cancer Incidence Trends in Older US Women by Race, Ethnicity, Geography, and Stage (2025)</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>40553473</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>10.1001/jamanetworkopen.2025.16947</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G21" s="15" t="inlineStr"/>
+      <c r="H21" s="15" t="inlineStr"/>
+      <c r="I21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Invasive cancer incidence - United States, 2010. (2014)</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>24670926</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr"/>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G22" s="15" t="inlineStr"/>
+      <c r="H22" s="15" t="inlineStr"/>
+      <c r="I22" s="16" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>Incidence Rate Trends of Breast Cancer Overall and by Molecular Subtype by Race and Ethnicity and Age (2025)</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>39853979</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>10.1001/jamanetworkopen.2024.56142</t>
+        </is>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G23" s="15" t="inlineStr"/>
+      <c r="H23" s="15" t="inlineStr"/>
+      <c r="I23" s="16" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
+          <t>Breast, Colorectal, and Prostate Cancer Incidence among Filipino Americans by Generational Status in the Multiethnic Cohort Study (2024)</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>39132985</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>10.1158/1055-9965.epi-24-0647</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr"/>
+      <c r="H24" s="15" t="inlineStr"/>
+      <c r="I24" s="16" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Disparities of cancer incidence in Michigan's American Indians: Spotlight on breast cancer (2014)</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>24676851</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.28589</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr"/>
+      <c r="H25" s="15" t="inlineStr"/>
+      <c r="I25" s="16" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>Are There Regional Differences in Triple Negative Breast Cancer among Non-Hispanic Black Women? (2021)</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>32778443</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>10.1016/j.jnma.2020.07.016</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr"/>
+      <c r="H26" s="15" t="inlineStr"/>
+      <c r="I26" s="16" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>Persistence in breast cancer disparities between African Americans and whites in Wisconsin (2011)</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>21473509</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr"/>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr"/>
+      <c r="H27" s="15" t="inlineStr"/>
+      <c r="I27" s="16" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Trends in breast cancer incidence rates by race/ethnicity: Patterns by stage, socioeconomic position, and geography in the United States, 1999-2017 (2022)</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>34731501</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.34008</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr"/>
+      <c r="H28" s="15" t="inlineStr"/>
+      <c r="I28" s="16" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Breast cancer incidence trends in Asian women aged 20 or older as compared to other ethnic women in the United States from 2000 to 2018 by time period, age and tumor stage (2022)</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>34861613</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>10.1016/j.canep.2021.102076</t>
+        </is>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr"/>
+      <c r="H29" s="15" t="inlineStr"/>
+      <c r="I29" s="16" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C30" s="14" t="inlineStr">
+        <is>
+          <t>Home mortgage discrimination and incidence of triple-negative and Luminal A breast cancer among non-Hispanic Black and non-Hispanic White females in California, 2006–2015 (2022)</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>35113296</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s10552-022-01557-y</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr"/>
+      <c r="H30" s="15" t="inlineStr"/>
+      <c r="I30" s="16" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>Does socioeconomic disparity in cancer incidence vary across racial/ethnic groups? (2010)</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>20567897</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s10552-010-9601-y</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr"/>
+      <c r="H31" s="15" t="inlineStr"/>
+      <c r="I31" s="16" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Forty-year trends in menopausal hormone therapy use and breast cancer incidence  among postmenopausal black and white women (2020)</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>32212335</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.32846</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr"/>
+      <c r="H32" s="15" t="inlineStr"/>
+      <c r="I32" s="16" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr">
+        <is>
+          <t>What can we learn from the age- and race/ethnicity- specific rates of inflammatory breast carcinoma? (2011)</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>21850396</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s10549-011-1719-4</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr"/>
+      <c r="H33" s="15" t="inlineStr"/>
+      <c r="I33" s="16" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C34" s="14" t="inlineStr">
+        <is>
+          <t>Trends in Female Breast Cancer Incidence among Japanese, Korean, and US Populations: An Age-Period-Cohort Analysis (2026)</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>42065927</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>10.1158/1055-9965.epi-26-0101</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr"/>
+      <c r="H34" s="15" t="inlineStr"/>
+      <c r="I34" s="16" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>Recent breast cancer trends among Asian/Pacific Islander, Hispanic, and African-American women in the US: Changes by tumor subtype (2007)</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>18162138</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>10.1186/bcr1839</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr"/>
+      <c r="H35" s="15" t="inlineStr"/>
+      <c r="I35" s="16" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Early estimates of cancer incidence for 2015: Expanding to include estimates for white and black races (2018)</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>29509274</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.31315</t>
+        </is>
+      </c>
+      <c r="F36" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G36" s="15" t="inlineStr"/>
+      <c r="H36" s="15" t="inlineStr"/>
+      <c r="I36" s="16" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C37" s="14" t="inlineStr">
+        <is>
+          <t>Differences in breast cancer incidence among young women aged 20–49 years by stage and tumor characteristics, age, race, and ethnicity, 2004–2013 (2018)</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>29445940</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s10549-018-4699-9</t>
+        </is>
+      </c>
+      <c r="F37" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G37" s="15" t="inlineStr"/>
+      <c r="H37" s="15" t="inlineStr"/>
+      <c r="I37" s="16" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Racial/ethnicity disparities in invasive breast cancer among younger and older  women: An analysis using multiple measures of population health (2016)</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>27792934</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>10.1016/j.canep.2016.10.013</t>
+        </is>
+      </c>
+      <c r="F38" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr"/>
+      <c r="H38" s="15" t="inlineStr"/>
+      <c r="I38" s="16" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>402</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Disparities in Breast Cancer Incidence, Mortality, and Quality of Care among African American and European American Women in South Carolina (2016)</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>26741869</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>10.14423/smj.0000000000000396</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G39" s="15" t="inlineStr"/>
+      <c r="H39" s="15" t="inlineStr"/>
+      <c r="I39" s="16" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Trends in Incidence of Invasive Lobular Carcinoma of the Breast by Race: Patterns by Age, Cancer Stage, and Socioeconomic Factors in the United States, 1992-2019 (2025)</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>39837694</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>10.1016/j.clbc.2024.12.015</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="inlineStr"/>
+      <c r="H40" s="15" t="inlineStr"/>
+      <c r="I40" s="16" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Persistent poverty and breast cancer incidence by tumor subtype: intersections of rural/urban residence and race within USA Surveillance Epidemiology and End Results Registries, 2017 to 2021 (2026)</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>41546752</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s10552-025-02114-z</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G41" s="15" t="inlineStr"/>
+      <c r="H41" s="15" t="inlineStr"/>
+      <c r="I41" s="16" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Spillover effects of public school integration in the southern United States: diverging trends in statewide annual breast cancer incidence, 2001–2019 (2026)</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>41649619</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s10552-025-02124-x</t>
+        </is>
+      </c>
+      <c r="F42" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G42" s="15" t="inlineStr"/>
+      <c r="H42" s="15" t="inlineStr"/>
+      <c r="I42" s="16" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr">
+        <is>
+          <t>Cancer Incidence and Trends in Persistent Poverty Areas of California by Race/Ethnicity and Sex (2025)</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="inlineStr">
+        <is>
+          <t>40736150</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cam4.71088</t>
+        </is>
+      </c>
+      <c r="F43" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G43" s="15" t="inlineStr"/>
+      <c r="H43" s="15" t="inlineStr"/>
+      <c r="I43" s="16" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="B44" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Cancer statistics for Asian Americans, Native Hawaiians, and Pacific Islanders, 2016: Converging incidence in males and females (2016)</t>
+        </is>
+      </c>
+      <c r="D44" s="13" t="inlineStr">
+        <is>
+          <t>26766789</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/caac.21335</t>
+        </is>
+      </c>
+      <c r="F44" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr"/>
+      <c r="H44" s="15" t="inlineStr"/>
+      <c r="I44" s="16" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr">
+        <is>
+          <t>The role of area-level socioeconomic disadvantage in racial disparities in cancer incidence in metropolitan Detroit (2023)</t>
+        </is>
+      </c>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>37184135</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cam4.6065</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr"/>
+      <c r="H45" s="15" t="inlineStr"/>
+      <c r="I45" s="16" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>Cancer in Guam and Hawaii: A comparison of two U.S. Island populations (2017)</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>29120826</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>10.1016/j.canep.2017.08.005</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr"/>
+      <c r="H46" s="15" t="inlineStr"/>
+      <c r="I46" s="16" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>751</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
+          <t>Population-based statistics for women diagnosed with inflammatory breast cancer (United States) (2004)</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>15090727</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>10.1023/b:caco.0000024222.61114.18</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G47" s="15" t="inlineStr"/>
+      <c r="H47" s="15" t="inlineStr"/>
+      <c r="I47" s="16" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>Breast cancer incidence and stage at diagnosis in the six US-Affiliated Pacific  Islands (2024)</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>38996557</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>10.1016/j.canep.2024.102611</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr"/>
+      <c r="H48" s="15" t="inlineStr"/>
+      <c r="I48" s="16" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>Cancer-related risk factors and incidence of major cancers by race, gender and region; analysis of the NIH-AARP diet and health study (2017)</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>28854891</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>10.1186/s12885-017-3557-1</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr"/>
+      <c r="H49" s="15" t="inlineStr"/>
+      <c r="I49" s="16" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Cancer incidence in the Somali population of Olmsted County: A Rochester epidemiology project study (2023)</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>37740603</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cam4.6558</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G50" s="15" t="inlineStr"/>
+      <c r="H50" s="15" t="inlineStr"/>
+      <c r="I50" s="16" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>1398</t>
+        </is>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C51" s="14" t="inlineStr">
+        <is>
+          <t>Early-Onset Cancer Incidence Disparities Between Black and White Individuals in the US, 2003-2022 (2026)</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>41989785</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>10.1001/jamanetworkopen.2026.7529</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G51" s="15" t="inlineStr"/>
+      <c r="H51" s="15" t="inlineStr"/>
+      <c r="I51" s="16" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>1453</t>
+        </is>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>American Cancer Society’s Report on the Status of Cancer Disparities in the United States, 2025 (2026)</t>
+        </is>
+      </c>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>41400551</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/caac.70045</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G52" s="15" t="inlineStr"/>
+      <c r="H52" s="15" t="inlineStr"/>
+      <c r="I52" s="16" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C53" s="14" t="inlineStr">
+        <is>
+          <t>Cancer statistics, 2026 (2026)</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>41528114</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/caac.70043</t>
+        </is>
+      </c>
+      <c r="F53" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="inlineStr"/>
+      <c r="H53" s="15" t="inlineStr"/>
+      <c r="I53" s="16" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>1569</t>
+        </is>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Characterizing cancer patterns in Okinawan vs. mainland Japanese Americans: The Multiethnic Cohort Study (2025)</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr"/>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>10.1101/2025.07.14.25331338</t>
+        </is>
+      </c>
+      <c r="F54" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G54" s="15" t="inlineStr"/>
+      <c r="H54" s="15" t="inlineStr"/>
+      <c r="I54" s="16" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>1629</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>Inequalities in Fertility-Impacting Cancer Incidence Among Young Populations in the United States (2025)</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>40189850</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cam4.70797</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G55" s="15" t="inlineStr"/>
+      <c r="H55" s="15" t="inlineStr"/>
+      <c r="I55" s="16" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>1637</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>39808161</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>10.1158/1055-9965.epi-24-1325</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G56" s="15" t="inlineStr"/>
+      <c r="H56" s="15" t="inlineStr"/>
+      <c r="I56" s="16" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>38801414</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>10.1158/1055-9965.epi-24-0072</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G57" s="15" t="inlineStr"/>
+      <c r="H57" s="15" t="inlineStr"/>
+      <c r="I57" s="16" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>Cancer incidence and associations with known risk and protective factors: the Alaska EARTH study (2019)</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>31428891</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s10552-019-01216-9</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G58" s="15" t="inlineStr"/>
+      <c r="H58" s="15" t="inlineStr"/>
+      <c r="I58" s="16" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>2453</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>Incidence and survival among young women with stage I-III breast cancer: Seer 2000-2015 (2019)</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>31392297</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>10.1093/jncics/pkz040</t>
+        </is>
+      </c>
+      <c r="F59" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G59" s="15" t="inlineStr"/>
+      <c r="H59" s="15" t="inlineStr"/>
+      <c r="I59" s="16" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>3845</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>Characterizing inflammatory breast cancer among Arab Americans in the California, Detroit and New Jersey Surveillance, Epidemiology and End Results (SEER) registries (1988-2008) (2013)</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr"/>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>10.1186/2193-1801-2-3</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G60" s="15" t="inlineStr"/>
+      <c r="H60" s="15" t="inlineStr"/>
+      <c r="I60" s="16" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>4043</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>Trends in Breast Cancer Incidence and Mortality in the United States From 2004-2018: A Surveillance, Epidemiology, and End Results (SEER)-Based Study (2023)</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>37223193</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>10.7759/cureus.37982</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G61" s="15" t="inlineStr"/>
+      <c r="H61" s="15" t="inlineStr"/>
+      <c r="I61" s="16" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>4082</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C62" s="14" t="inlineStr">
+        <is>
+          <t>Annual Report to the Nation on the Status of Cancer, featuring state-level statistics after the onset of the COVID-19 pandemic (2025)</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>40257373</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.35833</t>
+        </is>
+      </c>
+      <c r="F62" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G62" s="15" t="inlineStr"/>
+      <c r="H62" s="15" t="inlineStr"/>
+      <c r="I62" s="16" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>4294</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>Cancer statistics for African American and Black people, 2025 (2025)</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>39976243</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/caac.21874</t>
+        </is>
+      </c>
+      <c r="F63" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G63" s="15" t="inlineStr"/>
+      <c r="H63" s="15" t="inlineStr"/>
+      <c r="I63" s="16" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>4389</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>Differences in the cancer burden among foreign-born and US-born Arab Americans living in metropolitan Detroit (2013)</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>24013772</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s10552-013-0271-4</t>
+        </is>
+      </c>
+      <c r="F64" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G64" s="15" t="inlineStr"/>
+      <c r="H64" s="15" t="inlineStr"/>
+      <c r="I64" s="16" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>4429</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="inlineStr">
+        <is>
+          <t>INCLUDED (narrative)</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>Cancer risk in different generations of Middle Eastern immigrants to California, 1988-2013 (2017)</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>28801942</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/ijc.30928</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="inlineStr">
+        <is>
+          <t>LOW — narrative only</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="inlineStr"/>
+      <c r="H65" s="15" t="inlineStr"/>
+      <c r="I65" s="16" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>1462</t>
+        </is>
+      </c>
+      <c r="B66" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Ineligible population)</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>Rising Breast Cancer Incidence and Poor Outcomes in Young Women: A Retrospective Study (2026)</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>41742962</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>10.1155/tbj/5584726</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="G66" s="15" t="inlineStr"/>
+      <c r="H66" s="15" t="inlineStr"/>
+      <c r="I66" s="16" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>Lobular breast cancer statistics, 2025 (2025)</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>41055508</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.70061</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G67" s="15" t="inlineStr"/>
+      <c r="H67" s="15" t="inlineStr"/>
+      <c r="I67" s="16" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>Annual report to the nation on the status of cancer, part 1: National cancer statistics (2022)</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>36301149</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.34479</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G68" s="15" t="inlineStr"/>
+      <c r="H68" s="15" t="inlineStr"/>
+      <c r="I68" s="16" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C69" s="14" t="inlineStr">
+        <is>
+          <t>Annual report to the nation on the status of cancer, part I: National cancer statistics (2020)</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>32162336</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.32802</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G69" s="15" t="inlineStr"/>
+      <c r="H69" s="15" t="inlineStr"/>
+      <c r="I69" s="16" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="B70" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>Annual Report to the Nation on the status of cancer, 1975-2010, featuring  prevalence of comorbidity and impact on survival among persons with lung, colorectal, breast, or prostate cancer (2014)</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>24343171</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.28509</t>
+        </is>
+      </c>
+      <c r="F70" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G70" s="15" t="inlineStr"/>
+      <c r="H70" s="15" t="inlineStr"/>
+      <c r="I70" s="16" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>362</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C71" s="14" t="inlineStr">
+        <is>
+          <t>Annual Report to the Nation on the Status of Cancer, 1975-2014, Featuring  Survival (2017)</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>28376154</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>10.1093/jnci/djx030</t>
+        </is>
+      </c>
+      <c r="F71" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G71" s="15" t="inlineStr"/>
+      <c r="H71" s="15" t="inlineStr"/>
+      <c r="I71" s="16" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>Annual report to the nation on the status of cancer, 1975-2003, featuring cancer  among U.S. Hispanic/Latino populations (2006)</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>16958083</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.22193</t>
+        </is>
+      </c>
+      <c r="F72" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G72" s="15" t="inlineStr"/>
+      <c r="H72" s="15" t="inlineStr"/>
+      <c r="I72" s="16" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>Annual report to the nation on the status of cancer, 1975-2011, featuring incidence of breast cancer subtypes by race/ethnicity, poverty, and state (2015)</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>25825511</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>10.1093/jnci/djv048</t>
+        </is>
+      </c>
+      <c r="F73" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G73" s="15" t="inlineStr"/>
+      <c r="H73" s="15" t="inlineStr"/>
+      <c r="I73" s="16" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C74" s="14" t="inlineStr">
+        <is>
+          <t>Annual Report to the Nation on the Status of Cancer, Featuring Cancer in Men and Women Age 20–49 Years (2019)</t>
+        </is>
+      </c>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>31145458</t>
+        </is>
+      </c>
+      <c r="E74" s="13" t="inlineStr">
+        <is>
+          <t>10.1093/jnci/djz106</t>
+        </is>
+      </c>
+      <c r="F74" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G74" s="15" t="inlineStr"/>
+      <c r="H74" s="15" t="inlineStr"/>
+      <c r="I74" s="16" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="B75" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C75" s="14" t="inlineStr">
+        <is>
+          <t>Annual report to the nation on the status of cancer, 1975-2006, featuring  colorectal cancer trends and impact of interventions (risk factors, screening, and treatment) to reduce future rates (2010)</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>19998273</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.24760</t>
+        </is>
+      </c>
+      <c r="F75" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G75" s="15" t="inlineStr"/>
+      <c r="H75" s="15" t="inlineStr"/>
+      <c r="I75" s="16" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>2151</t>
+        </is>
+      </c>
+      <c r="B76" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C76" s="14" t="inlineStr">
+        <is>
+          <t>American Cancer Society's report on the status of cancer disparities in the United States, 2021 (2022)</t>
+        </is>
+      </c>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>34878180</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/caac.21703</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G76" s="15" t="inlineStr"/>
+      <c r="H76" s="15" t="inlineStr"/>
+      <c r="I76" s="16" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>2163</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C77" s="14" t="inlineStr">
+        <is>
+          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr"/>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>10.1101/2022.02.21.22271266</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G77" s="15" t="inlineStr"/>
+      <c r="H77" s="15" t="inlineStr"/>
+      <c r="I77" s="16" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>3373</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="inlineStr">
+        <is>
+          <t>Cancer Statistics, 2004 (2004)</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>14974761</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/canjclin.54.1.8</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="inlineStr"/>
+      <c r="H78" s="15" t="inlineStr"/>
+      <c r="I78" s="16" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>3429</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C79" s="14" t="inlineStr">
+        <is>
+          <t>Cancer statistics, 2002 (2002)</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>11814064</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/canjclin.52.1.23</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G79" s="15" t="inlineStr"/>
+      <c r="H79" s="15" t="inlineStr"/>
+      <c r="I79" s="16" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>3522</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C80" s="14" t="inlineStr">
+        <is>
+          <t>Annual Report to the Nation on the Status of Cancer, part 2: Early assessment of the COVID-19 pandemic’s impact on cancer diagnosis (2024)</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr"/>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.35026</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G80" s="15" t="inlineStr"/>
+      <c r="H80" s="15" t="inlineStr"/>
+      <c r="I80" s="16" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>3713</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C81" s="14" t="inlineStr">
+        <is>
+          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr"/>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-319-41118-7_3</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G81" s="15" t="inlineStr"/>
+      <c r="H81" s="15" t="inlineStr"/>
+      <c r="I81" s="16" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
+        <is>
+          <t>4035</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>Annual report to the nation on the status of cancer, 1975-2001, with a special feature regarding survival (2004)</t>
+        </is>
+      </c>
+      <c r="D82" s="13" t="inlineStr">
+        <is>
+          <t>15221985</t>
+        </is>
+      </c>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.20288</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G82" s="15" t="inlineStr"/>
+      <c r="H82" s="15" t="inlineStr"/>
+      <c r="I82" s="16" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>4050</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="inlineStr">
+        <is>
+          <t>Annual Report to the Nation on the Status of Cancer, 19752009, Featuring the Burden and Trends in Human Papillomavirus (HPV)Associated Cancers and HPV Vaccination Coverage Levels (2013)</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>23297039</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="inlineStr">
+        <is>
+          <t>10.1093/jnci/djs491</t>
+        </is>
+      </c>
+      <c r="F83" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G83" s="15" t="inlineStr"/>
+      <c r="H83" s="15" t="inlineStr"/>
+      <c r="I83" s="16" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>4057</t>
+        </is>
+      </c>
+      <c r="B84" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>Breast cancer statistics, 2011 (2011)</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
+          <t>21969133</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/caac.20134</t>
+        </is>
+      </c>
+      <c r="F84" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G84" s="15" t="inlineStr"/>
+      <c r="H84" s="15" t="inlineStr"/>
+      <c r="I84" s="16" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>4065</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>Cancer Statistics, 2014 (2014)</t>
+        </is>
+      </c>
+      <c r="D85" s="13" t="inlineStr">
+        <is>
+          <t>24399786</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/caac.21208</t>
+        </is>
+      </c>
+      <c r="F85" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G85" s="15" t="inlineStr"/>
+      <c r="H85" s="15" t="inlineStr"/>
+      <c r="I85" s="16" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>4066</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C86" s="14" t="inlineStr">
+        <is>
+          <t>Annual Report to the Nation on the Status of Cancer, 1975-2007, Featuring Tumors of the Brain and Other Nervous System (2011)</t>
+        </is>
+      </c>
+      <c r="D86" s="13" t="inlineStr">
+        <is>
+          <t>21454908</t>
+        </is>
+      </c>
+      <c r="E86" s="13" t="inlineStr">
+        <is>
+          <t>10.1093/jnci/djr077</t>
+        </is>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="inlineStr"/>
+      <c r="H86" s="15" t="inlineStr"/>
+      <c r="I86" s="16" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="inlineStr">
+        <is>
+          <t>4071</t>
+        </is>
+      </c>
+      <c r="B87" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C87" s="14" t="inlineStr">
+        <is>
+          <t>Annual report to the nation on the status of cancer, 1975-2000, featuring the uses of surveillance data for cancer prevention and control (2003)</t>
+        </is>
+      </c>
+      <c r="D87" s="13" t="inlineStr">
+        <is>
+          <t>12953083</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>10.1093/jnci/djg040</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G87" s="15" t="inlineStr"/>
+      <c r="H87" s="15" t="inlineStr"/>
+      <c r="I87" s="16" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>4164</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr">
+        <is>
+          <t>Annual Report to the Nation on the Status of Cancer, 1975-2005, Featuring Trends in Lung Cancer, Tobacco Use, and Tobacco Control (2008)</t>
+        </is>
+      </c>
+      <c r="D88" s="13" t="inlineStr">
+        <is>
+          <t>19033571</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>10.1093/jnci/djn389</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G88" s="15" t="inlineStr"/>
+      <c r="H88" s="15" t="inlineStr"/>
+      <c r="I88" s="16" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>4172</t>
+        </is>
+      </c>
+      <c r="B89" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr">
+        <is>
+          <t>Cancer statistics, 2013 (2013)</t>
+        </is>
+      </c>
+      <c r="D89" s="13" t="inlineStr">
+        <is>
+          <t>23335087</t>
+        </is>
+      </c>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/caac.21166</t>
+        </is>
+      </c>
+      <c r="F89" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G89" s="15" t="inlineStr"/>
+      <c r="H89" s="15" t="inlineStr"/>
+      <c r="I89" s="16" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>4213</t>
+        </is>
+      </c>
+      <c r="B90" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr">
+        <is>
+          <t>Cancer statistics for Hispanics/Latinos, 2012 (2012)</t>
+        </is>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>22987332</t>
+        </is>
+      </c>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/caac.21153</t>
+        </is>
+      </c>
+      <c r="F90" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G90" s="15" t="inlineStr"/>
+      <c r="H90" s="15" t="inlineStr"/>
+      <c r="I90" s="16" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="inlineStr">
+        <is>
+          <t>4216</t>
+        </is>
+      </c>
+      <c r="B91" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
+        <is>
+          <t>Annual Report to the Nation on the status of cancer, 1975-2008, featuring cancers associated with excess weight and lack of sufficient physical activity (2012)</t>
+        </is>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>22460733</t>
+        </is>
+      </c>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>10.1002/cncr.27514</t>
+        </is>
+      </c>
+      <c r="F91" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G91" s="15" t="inlineStr"/>
+      <c r="H91" s="15" t="inlineStr"/>
+      <c r="I91" s="16" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="inlineStr">
+        <is>
+          <t>4357</t>
+        </is>
+      </c>
+      <c r="B92" s="13" t="inlineStr">
+        <is>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
+        </is>
+      </c>
+      <c r="C92" s="14" t="inlineStr">
+        <is>
+          <t>Cancer statistics for Hispanics, 2003 (2003)</t>
+        </is>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>12924775</t>
+        </is>
+      </c>
+      <c r="E92" s="13" t="inlineStr">
+        <is>
+          <t>10.3322/canjclin.53.4.208</t>
+        </is>
+      </c>
+      <c r="F92" s="14" t="inlineStr">
+        <is>
+          <t>LOW — metadata-defensible</t>
+        </is>
+      </c>
+      <c r="G92" s="15" t="inlineStr"/>
+      <c r="H92" s="15" t="inlineStr"/>
+      <c r="I92" s="16" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I92"/>
+  <dataValidations count="2">
+    <dataValidation sqref="G3:G92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H3:H92" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Include,Exclude"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
 </file>
--- a/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
+++ b/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2_TA_Excluded_Sample'!$A$1:$E$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3_Extraction_Verification'!$A$1:$M$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4_RoB_Review'!$A$1:$Q$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23574,7 +23574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24065,7 +24065,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -24075,17 +24075,17 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Trends in Female Breast Cancer Incidence among Japanese, Korean, and US Populations: An Age-Period-Cohort Analysis (2026)</t>
+          <t>Disparities in Breast Cancer Incidence, Mortality, and Quality of Care among African American and European American Women in South Carolina (2016)</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>42065927</t>
+          <t>26741869</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-26-0101</t>
+          <t>10.14423/smj.0000000000000396</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>426</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -24110,17 +24110,17 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Recent breast cancer trends among Asian/Pacific Islander, Hispanic, and African-American women in the US: Changes by tumor subtype (2007)</t>
+          <t>Trends in Incidence of Invasive Lobular Carcinoma of the Breast by Race: Patterns by Age, Cancer Stage, and Socioeconomic Factors in the United States, 1992-2019 (2025)</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>18162138</t>
+          <t>39837694</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>10.1186/bcr1839</t>
+          <t>10.1016/j.clbc.2024.12.015</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -24135,7 +24135,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>474</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -24145,17 +24145,17 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Early estimates of cancer incidence for 2015: Expanding to include estimates for white and black races (2018)</t>
+          <t>Persistent poverty and breast cancer incidence by tumor subtype: intersections of rural/urban residence and race within USA Surveillance Epidemiology and End Results Registries, 2017 to 2021 (2026)</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>29509274</t>
+          <t>41546752</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cncr.31315</t>
+          <t>10.1007/s10552-025-02114-z</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -24170,7 +24170,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>477</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -24180,17 +24180,17 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Differences in breast cancer incidence among young women aged 20–49 years by stage and tumor characteristics, age, race, and ethnicity, 2004–2013 (2018)</t>
+          <t>Spillover effects of public school integration in the southern United States: diverging trends in statewide annual breast cancer incidence, 2001–2019 (2026)</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>29445940</t>
+          <t>41649619</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>10.1007/s10549-018-4699-9</t>
+          <t>10.1007/s10552-025-02124-x</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -24205,7 +24205,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>504</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -24215,17 +24215,17 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Racial/ethnicity disparities in invasive breast cancer among younger and older  women: An analysis using multiple measures of population health (2016)</t>
+          <t>Cancer Incidence and Trends in Persistent Poverty Areas of California by Race/Ethnicity and Sex (2025)</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>27792934</t>
+          <t>40736150</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>10.1016/j.canep.2016.10.013</t>
+          <t>10.1002/cam4.71088</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -24240,7 +24240,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -24250,17 +24250,17 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Disparities in Breast Cancer Incidence, Mortality, and Quality of Care among African American and European American Women in South Carolina (2016)</t>
+          <t>Cancer statistics for Asian Americans, Native Hawaiians, and Pacific Islanders, 2016: Converging incidence in males and females (2016)</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>26741869</t>
+          <t>26766789</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>10.14423/smj.0000000000000396</t>
+          <t>10.3322/caac.21335</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -24275,7 +24275,7 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>516</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -24285,17 +24285,17 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Trends in Incidence of Invasive Lobular Carcinoma of the Breast by Race: Patterns by Age, Cancer Stage, and Socioeconomic Factors in the United States, 1992-2019 (2025)</t>
+          <t>The role of area-level socioeconomic disadvantage in racial disparities in cancer incidence in metropolitan Detroit (2023)</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>39837694</t>
+          <t>37184135</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>10.1016/j.clbc.2024.12.015</t>
+          <t>10.1002/cam4.6065</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -24310,7 +24310,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>565</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -24320,17 +24320,17 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Persistent poverty and breast cancer incidence by tumor subtype: intersections of rural/urban residence and race within USA Surveillance Epidemiology and End Results Registries, 2017 to 2021 (2026)</t>
+          <t>Cancer in Guam and Hawaii: A comparison of two U.S. Island populations (2017)</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>41546752</t>
+          <t>29120826</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>10.1007/s10552-025-02114-z</t>
+          <t>10.1016/j.canep.2017.08.005</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -24345,7 +24345,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>751</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -24355,17 +24355,17 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Spillover effects of public school integration in the southern United States: diverging trends in statewide annual breast cancer incidence, 2001–2019 (2026)</t>
+          <t>Population-based statistics for women diagnosed with inflammatory breast cancer (United States) (2004)</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>41649619</t>
+          <t>15090727</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>10.1007/s10552-025-02124-x</t>
+          <t>10.1023/b:caco.0000024222.61114.18</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
@@ -24380,7 +24380,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>754</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -24390,17 +24390,17 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Cancer Incidence and Trends in Persistent Poverty Areas of California by Race/Ethnicity and Sex (2025)</t>
+          <t>Breast cancer incidence and stage at diagnosis in the six US-Affiliated Pacific  Islands (2024)</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>40736150</t>
+          <t>38996557</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cam4.71088</t>
+          <t>10.1016/j.canep.2024.102611</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -24415,7 +24415,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>998</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -24425,17 +24425,17 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Cancer statistics for Asian Americans, Native Hawaiians, and Pacific Islanders, 2016: Converging incidence in males and females (2016)</t>
+          <t>Cancer-related risk factors and incidence of major cancers by race, gender and region; analysis of the NIH-AARP diet and health study (2017)</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>26766789</t>
+          <t>28854891</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>10.3322/caac.21335</t>
+          <t>10.1186/s12885-017-3557-1</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -24450,7 +24450,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -24460,17 +24460,17 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>The role of area-level socioeconomic disadvantage in racial disparities in cancer incidence in metropolitan Detroit (2023)</t>
+          <t>Cancer incidence in the Somali population of Olmsted County: A Rochester epidemiology project study (2023)</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>37184135</t>
+          <t>37740603</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cam4.6065</t>
+          <t>10.1002/cam4.6558</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -24485,7 +24485,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -24495,17 +24495,17 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Cancer in Guam and Hawaii: A comparison of two U.S. Island populations (2017)</t>
+          <t>Early-Onset Cancer Incidence Disparities Between Black and White Individuals in the US, 2003-2022 (2026)</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>29120826</t>
+          <t>41989785</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>10.1016/j.canep.2017.08.005</t>
+          <t>10.1001/jamanetworkopen.2026.7529</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
@@ -24520,7 +24520,7 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
@@ -24530,17 +24530,17 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Population-based statistics for women diagnosed with inflammatory breast cancer (United States) (2004)</t>
+          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>15090727</t>
+          <t>39808161</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>10.1023/b:caco.0000024222.61114.18</t>
+          <t>10.1158/1055-9965.epi-24-1325</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -24555,7 +24555,7 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
@@ -24565,17 +24565,17 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>Breast cancer incidence and stage at diagnosis in the six US-Affiliated Pacific  Islands (2024)</t>
+          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>38996557</t>
+          <t>38801414</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>10.1016/j.canep.2024.102611</t>
+          <t>10.1158/1055-9965.epi-24-0072</t>
         </is>
       </c>
       <c r="F29" s="14" t="inlineStr">
@@ -24590,32 +24590,28 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>INCLUDED (narrative)</t>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Cancer-related risk factors and incidence of major cancers by race, gender and region; analysis of the NIH-AARP diet and health study (2017)</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>28854891</t>
-        </is>
-      </c>
+          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr"/>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>10.1186/s12885-017-3557-1</t>
+          <t>10.1101/2022.02.21.22271266</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>LOW — narrative only</t>
+          <t>LOW — metadata-defensible</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr"/>
@@ -24625,212 +24621,41 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>INCLUDED (narrative)</t>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>Cancer incidence in the Somali population of Olmsted County: A Rochester epidemiology project study (2023)</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>37740603</t>
-        </is>
-      </c>
+          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr"/>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cam4.6558</t>
+          <t>10.1007/978-3-319-41118-7_3</t>
         </is>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>LOW — narrative only</t>
+          <t>LOW — metadata-defensible</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr"/>
       <c r="H31" s="15" t="inlineStr"/>
       <c r="I31" s="16" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>1398</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>INCLUDED (narrative)</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Early-Onset Cancer Incidence Disparities Between Black and White Individuals in the US, 2003-2022 (2026)</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>41989785</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>10.1001/jamanetworkopen.2026.7529</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
-        <is>
-          <t>LOW — narrative only</t>
-        </is>
-      </c>
-      <c r="G32" s="15" t="inlineStr"/>
-      <c r="H32" s="15" t="inlineStr"/>
-      <c r="I32" s="16" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>INCLUDED (narrative)</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr">
-        <is>
-          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>39808161</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>10.1158/1055-9965.epi-24-1325</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
-        <is>
-          <t>LOW — narrative only</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr"/>
-      <c r="H33" s="15" t="inlineStr"/>
-      <c r="I33" s="16" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>INCLUDED (narrative)</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="inlineStr">
-        <is>
-          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>38801414</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>10.1158/1055-9965.epi-24-0072</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
-        <is>
-          <t>LOW — narrative only</t>
-        </is>
-      </c>
-      <c r="G34" s="15" t="inlineStr"/>
-      <c r="H34" s="15" t="inlineStr"/>
-      <c r="I34" s="16" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>2163</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr"/>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>10.1101/2022.02.21.22271266</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
-        <is>
-          <t>LOW — metadata-defensible</t>
-        </is>
-      </c>
-      <c r="G35" s="15" t="inlineStr"/>
-      <c r="H35" s="15" t="inlineStr"/>
-      <c r="I35" s="16" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
-        </is>
-      </c>
-      <c r="C36" s="14" t="inlineStr">
-        <is>
-          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr"/>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-319-41118-7_3</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
-        <is>
-          <t>LOW — metadata-defensible</t>
-        </is>
-      </c>
-      <c r="G36" s="15" t="inlineStr"/>
-      <c r="H36" s="15" t="inlineStr"/>
-      <c r="I36" s="16" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I36"/>
+  <autoFilter ref="A1:I31"/>
   <dataValidations count="2">
-    <dataValidation sqref="G3:G36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G3:G31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Include,Exclude"</formula1>
     </dataValidation>
   </dataValidations>

--- a/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
+++ b/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2_TA_Excluded_Sample'!$A$1:$E$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3_Extraction_Verification'!$A$1:$M$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4_RoB_Review'!$A$1:$Q$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23574,7 +23574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24135,7 +24135,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -24145,17 +24145,17 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Persistent poverty and breast cancer incidence by tumor subtype: intersections of rural/urban residence and race within USA Surveillance Epidemiology and End Results Registries, 2017 to 2021 (2026)</t>
+          <t>Cancer statistics for Asian Americans, Native Hawaiians, and Pacific Islanders, 2016: Converging incidence in males and females (2016)</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>41546752</t>
+          <t>26766789</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>10.1007/s10552-025-02114-z</t>
+          <t>10.3322/caac.21335</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -24170,7 +24170,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>516</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -24180,17 +24180,17 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Spillover effects of public school integration in the southern United States: diverging trends in statewide annual breast cancer incidence, 2001–2019 (2026)</t>
+          <t>The role of area-level socioeconomic disadvantage in racial disparities in cancer incidence in metropolitan Detroit (2023)</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>41649619</t>
+          <t>37184135</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>10.1007/s10552-025-02124-x</t>
+          <t>10.1002/cam4.6065</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -24205,7 +24205,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>565</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -24215,17 +24215,17 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Cancer Incidence and Trends in Persistent Poverty Areas of California by Race/Ethnicity and Sex (2025)</t>
+          <t>Cancer in Guam and Hawaii: A comparison of two U.S. Island populations (2017)</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>40736150</t>
+          <t>29120826</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cam4.71088</t>
+          <t>10.1016/j.canep.2017.08.005</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -24240,7 +24240,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>751</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -24250,17 +24250,17 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Cancer statistics for Asian Americans, Native Hawaiians, and Pacific Islanders, 2016: Converging incidence in males and females (2016)</t>
+          <t>Population-based statistics for women diagnosed with inflammatory breast cancer (United States) (2004)</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>26766789</t>
+          <t>15090727</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>10.3322/caac.21335</t>
+          <t>10.1023/b:caco.0000024222.61114.18</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -24275,7 +24275,7 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>754</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -24285,17 +24285,17 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>The role of area-level socioeconomic disadvantage in racial disparities in cancer incidence in metropolitan Detroit (2023)</t>
+          <t>Breast cancer incidence and stage at diagnosis in the six US-Affiliated Pacific  Islands (2024)</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>37184135</t>
+          <t>38996557</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cam4.6065</t>
+          <t>10.1016/j.canep.2024.102611</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -24310,7 +24310,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>998</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -24320,17 +24320,17 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Cancer in Guam and Hawaii: A comparison of two U.S. Island populations (2017)</t>
+          <t>Cancer-related risk factors and incidence of major cancers by race, gender and region; analysis of the NIH-AARP diet and health study (2017)</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>29120826</t>
+          <t>28854891</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>10.1016/j.canep.2017.08.005</t>
+          <t>10.1186/s12885-017-3557-1</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -24345,7 +24345,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -24355,17 +24355,17 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Population-based statistics for women diagnosed with inflammatory breast cancer (United States) (2004)</t>
+          <t>Cancer incidence in the Somali population of Olmsted County: A Rochester epidemiology project study (2023)</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>15090727</t>
+          <t>37740603</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>10.1023/b:caco.0000024222.61114.18</t>
+          <t>10.1002/cam4.6558</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
@@ -24380,7 +24380,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -24390,17 +24390,17 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Breast cancer incidence and stage at diagnosis in the six US-Affiliated Pacific  Islands (2024)</t>
+          <t>Early-Onset Cancer Incidence Disparities Between Black and White Individuals in the US, 2003-2022 (2026)</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>38996557</t>
+          <t>41989785</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>10.1016/j.canep.2024.102611</t>
+          <t>10.1001/jamanetworkopen.2026.7529</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -24415,7 +24415,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -24425,17 +24425,17 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Cancer-related risk factors and incidence of major cancers by race, gender and region; analysis of the NIH-AARP diet and health study (2017)</t>
+          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>28854891</t>
+          <t>39808161</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>10.1186/s12885-017-3557-1</t>
+          <t>10.1158/1055-9965.epi-24-1325</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -24450,7 +24450,7 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
@@ -24460,17 +24460,17 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Cancer incidence in the Somali population of Olmsted County: A Rochester epidemiology project study (2023)</t>
+          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>37740603</t>
+          <t>38801414</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cam4.6558</t>
+          <t>10.1158/1055-9965.epi-24-0072</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -24485,32 +24485,28 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>INCLUDED (narrative)</t>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Early-Onset Cancer Incidence Disparities Between Black and White Individuals in the US, 2003-2022 (2026)</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>41989785</t>
-        </is>
-      </c>
+          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr"/>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>10.1001/jamanetworkopen.2026.7529</t>
+          <t>10.1101/2022.02.21.22271266</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>LOW — narrative only</t>
+          <t>LOW — metadata-defensible</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr"/>
@@ -24520,142 +24516,41 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>INCLUDED (narrative)</t>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>39808161</t>
-        </is>
-      </c>
+          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr"/>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-24-1325</t>
+          <t>10.1007/978-3-319-41118-7_3</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>LOW — narrative only</t>
+          <t>LOW — metadata-defensible</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr"/>
       <c r="H28" s="15" t="inlineStr"/>
       <c r="I28" s="16" t="inlineStr"/>
     </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>INCLUDED (narrative)</t>
-        </is>
-      </c>
-      <c r="C29" s="14" t="inlineStr">
-        <is>
-          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>38801414</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>10.1158/1055-9965.epi-24-0072</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
-        <is>
-          <t>LOW — narrative only</t>
-        </is>
-      </c>
-      <c r="G29" s="15" t="inlineStr"/>
-      <c r="H29" s="15" t="inlineStr"/>
-      <c r="I29" s="16" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>2163</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
-        </is>
-      </c>
-      <c r="C30" s="14" t="inlineStr">
-        <is>
-          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr"/>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>10.1101/2022.02.21.22271266</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
-        <is>
-          <t>LOW — metadata-defensible</t>
-        </is>
-      </c>
-      <c r="G30" s="15" t="inlineStr"/>
-      <c r="H30" s="15" t="inlineStr"/>
-      <c r="I30" s="16" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr">
-        <is>
-          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr"/>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-319-41118-7_3</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
-        <is>
-          <t>LOW — metadata-defensible</t>
-        </is>
-      </c>
-      <c r="G31" s="15" t="inlineStr"/>
-      <c r="H31" s="15" t="inlineStr"/>
-      <c r="I31" s="16" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I31"/>
+  <autoFilter ref="A1:I28"/>
   <dataValidations count="2">
-    <dataValidation sqref="G3:G31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G3:G28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Include,Exclude"</formula1>
     </dataValidation>
   </dataValidations>

--- a/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
+++ b/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2_TA_Excluded_Sample'!$A$1:$E$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3_Extraction_Verification'!$A$1:$M$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4_RoB_Review'!$A$1:$Q$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23574,7 +23574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24100,7 +24100,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>510</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -24110,17 +24110,17 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Trends in Incidence of Invasive Lobular Carcinoma of the Breast by Race: Patterns by Age, Cancer Stage, and Socioeconomic Factors in the United States, 1992-2019 (2025)</t>
+          <t>Cancer statistics for Asian Americans, Native Hawaiians, and Pacific Islanders, 2016: Converging incidence in males and females (2016)</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>39837694</t>
+          <t>26766789</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>10.1016/j.clbc.2024.12.015</t>
+          <t>10.3322/caac.21335</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -24135,7 +24135,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>516</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -24145,17 +24145,17 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Cancer statistics for Asian Americans, Native Hawaiians, and Pacific Islanders, 2016: Converging incidence in males and females (2016)</t>
+          <t>The role of area-level socioeconomic disadvantage in racial disparities in cancer incidence in metropolitan Detroit (2023)</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>26766789</t>
+          <t>37184135</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>10.3322/caac.21335</t>
+          <t>10.1002/cam4.6065</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -24170,7 +24170,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>565</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -24180,17 +24180,17 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>The role of area-level socioeconomic disadvantage in racial disparities in cancer incidence in metropolitan Detroit (2023)</t>
+          <t>Cancer in Guam and Hawaii: A comparison of two U.S. Island populations (2017)</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>37184135</t>
+          <t>29120826</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cam4.6065</t>
+          <t>10.1016/j.canep.2017.08.005</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -24205,7 +24205,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>751</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -24215,17 +24215,17 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Cancer in Guam and Hawaii: A comparison of two U.S. Island populations (2017)</t>
+          <t>Population-based statistics for women diagnosed with inflammatory breast cancer (United States) (2004)</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>29120826</t>
+          <t>15090727</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>10.1016/j.canep.2017.08.005</t>
+          <t>10.1023/b:caco.0000024222.61114.18</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -24240,7 +24240,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>754</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -24250,17 +24250,17 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Population-based statistics for women diagnosed with inflammatory breast cancer (United States) (2004)</t>
+          <t>Breast cancer incidence and stage at diagnosis in the six US-Affiliated Pacific  Islands (2024)</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>15090727</t>
+          <t>38996557</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>10.1023/b:caco.0000024222.61114.18</t>
+          <t>10.1016/j.canep.2024.102611</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -24275,7 +24275,7 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>998</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
@@ -24285,17 +24285,17 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Breast cancer incidence and stage at diagnosis in the six US-Affiliated Pacific  Islands (2024)</t>
+          <t>Cancer-related risk factors and incidence of major cancers by race, gender and region; analysis of the NIH-AARP diet and health study (2017)</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>38996557</t>
+          <t>28854891</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>10.1016/j.canep.2024.102611</t>
+          <t>10.1186/s12885-017-3557-1</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -24310,7 +24310,7 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
@@ -24320,17 +24320,17 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Cancer-related risk factors and incidence of major cancers by race, gender and region; analysis of the NIH-AARP diet and health study (2017)</t>
+          <t>Cancer incidence in the Somali population of Olmsted County: A Rochester epidemiology project study (2023)</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>28854891</t>
+          <t>37740603</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>10.1186/s12885-017-3557-1</t>
+          <t>10.1002/cam4.6558</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -24345,7 +24345,7 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
@@ -24355,17 +24355,17 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Cancer incidence in the Somali population of Olmsted County: A Rochester epidemiology project study (2023)</t>
+          <t>Early-Onset Cancer Incidence Disparities Between Black and White Individuals in the US, 2003-2022 (2026)</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>37740603</t>
+          <t>41989785</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cam4.6558</t>
+          <t>10.1001/jamanetworkopen.2026.7529</t>
         </is>
       </c>
       <c r="F23" s="14" t="inlineStr">
@@ -24380,7 +24380,7 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
@@ -24390,17 +24390,17 @@
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Early-Onset Cancer Incidence Disparities Between Black and White Individuals in the US, 2003-2022 (2026)</t>
+          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>41989785</t>
+          <t>39808161</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>10.1001/jamanetworkopen.2026.7529</t>
+          <t>10.1158/1055-9965.epi-24-1325</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
@@ -24415,7 +24415,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -24425,17 +24425,17 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
+          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>39808161</t>
+          <t>38801414</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-24-1325</t>
+          <t>10.1158/1055-9965.epi-24-0072</t>
         </is>
       </c>
       <c r="F25" s="14" t="inlineStr">
@@ -24450,32 +24450,28 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>INCLUDED (narrative)</t>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>38801414</t>
-        </is>
-      </c>
+          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-24-0072</t>
+          <t>10.1101/2022.02.21.22271266</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>LOW — narrative only</t>
+          <t>LOW — metadata-defensible</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr"/>
@@ -24485,7 +24481,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
@@ -24495,13 +24491,13 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
+          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr"/>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>10.1101/2022.02.21.22271266</t>
+          <t>10.1007/978-3-319-41118-7_3</t>
         </is>
       </c>
       <c r="F27" s="14" t="inlineStr">
@@ -24513,44 +24509,13 @@
       <c r="H27" s="15" t="inlineStr"/>
       <c r="I27" s="16" t="inlineStr"/>
     </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr"/>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-319-41118-7_3</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
-        <is>
-          <t>LOW — metadata-defensible</t>
-        </is>
-      </c>
-      <c r="G28" s="15" t="inlineStr"/>
-      <c r="H28" s="15" t="inlineStr"/>
-      <c r="I28" s="16" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I28"/>
+  <autoFilter ref="A1:I27"/>
   <dataValidations count="2">
-    <dataValidation sqref="G3:G28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G3:G27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Include,Exclude"</formula1>
     </dataValidation>
   </dataValidations>

--- a/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
+++ b/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2_TA_Excluded_Sample'!$A$1:$E$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3_Extraction_Verification'!$A$1:$M$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4_RoB_Review'!$A$1:$Q$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23574,7 +23574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24100,7 +24100,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>998</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -24110,17 +24110,17 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Cancer statistics for Asian Americans, Native Hawaiians, and Pacific Islanders, 2016: Converging incidence in males and females (2016)</t>
+          <t>Cancer-related risk factors and incidence of major cancers by race, gender and region; analysis of the NIH-AARP diet and health study (2017)</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>26766789</t>
+          <t>28854891</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>10.3322/caac.21335</t>
+          <t>10.1186/s12885-017-3557-1</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -24135,7 +24135,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -24145,17 +24145,17 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>The role of area-level socioeconomic disadvantage in racial disparities in cancer incidence in metropolitan Detroit (2023)</t>
+          <t>Cancer incidence in the Somali population of Olmsted County: A Rochester epidemiology project study (2023)</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>37184135</t>
+          <t>37740603</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cam4.6065</t>
+          <t>10.1002/cam4.6558</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -24170,7 +24170,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -24180,17 +24180,17 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Cancer in Guam and Hawaii: A comparison of two U.S. Island populations (2017)</t>
+          <t>Early-Onset Cancer Incidence Disparities Between Black and White Individuals in the US, 2003-2022 (2026)</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>29120826</t>
+          <t>41989785</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>10.1016/j.canep.2017.08.005</t>
+          <t>10.1001/jamanetworkopen.2026.7529</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -24205,7 +24205,7 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
@@ -24215,17 +24215,17 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Population-based statistics for women diagnosed with inflammatory breast cancer (United States) (2004)</t>
+          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>15090727</t>
+          <t>39808161</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>10.1023/b:caco.0000024222.61114.18</t>
+          <t>10.1158/1055-9965.epi-24-1325</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -24240,7 +24240,7 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
@@ -24250,17 +24250,17 @@
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Breast cancer incidence and stage at diagnosis in the six US-Affiliated Pacific  Islands (2024)</t>
+          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>38996557</t>
+          <t>38801414</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>10.1016/j.canep.2024.102611</t>
+          <t>10.1158/1055-9965.epi-24-0072</t>
         </is>
       </c>
       <c r="F20" s="14" t="inlineStr">
@@ -24275,32 +24275,28 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>INCLUDED (narrative)</t>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Cancer-related risk factors and incidence of major cancers by race, gender and region; analysis of the NIH-AARP diet and health study (2017)</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>28854891</t>
-        </is>
-      </c>
+          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr"/>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>10.1186/s12885-017-3557-1</t>
+          <t>10.1101/2022.02.21.22271266</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>LOW — narrative only</t>
+          <t>LOW — metadata-defensible</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr"/>
@@ -24310,212 +24306,41 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>INCLUDED (narrative)</t>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Cancer incidence in the Somali population of Olmsted County: A Rochester epidemiology project study (2023)</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>37740603</t>
-        </is>
-      </c>
+          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cam4.6558</t>
+          <t>10.1007/978-3-319-41118-7_3</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>LOW — narrative only</t>
+          <t>LOW — metadata-defensible</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr"/>
       <c r="H22" s="15" t="inlineStr"/>
       <c r="I22" s="16" t="inlineStr"/>
     </row>
-    <row r="23">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>1398</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>INCLUDED (narrative)</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>Early-Onset Cancer Incidence Disparities Between Black and White Individuals in the US, 2003-2022 (2026)</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>41989785</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>10.1001/jamanetworkopen.2026.7529</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
-        <is>
-          <t>LOW — narrative only</t>
-        </is>
-      </c>
-      <c r="G23" s="15" t="inlineStr"/>
-      <c r="H23" s="15" t="inlineStr"/>
-      <c r="I23" s="16" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>1637</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>INCLUDED (narrative)</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>39808161</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>10.1158/1055-9965.epi-24-1325</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
-        <is>
-          <t>LOW — narrative only</t>
-        </is>
-      </c>
-      <c r="G24" s="15" t="inlineStr"/>
-      <c r="H24" s="15" t="inlineStr"/>
-      <c r="I24" s="16" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>INCLUDED (narrative)</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="inlineStr">
-        <is>
-          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>38801414</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>10.1158/1055-9965.epi-24-0072</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>LOW — narrative only</t>
-        </is>
-      </c>
-      <c r="G25" s="15" t="inlineStr"/>
-      <c r="H25" s="15" t="inlineStr"/>
-      <c r="I25" s="16" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>2163</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr">
-        <is>
-          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr"/>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>10.1101/2022.02.21.22271266</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>LOW — metadata-defensible</t>
-        </is>
-      </c>
-      <c r="G26" s="15" t="inlineStr"/>
-      <c r="H26" s="15" t="inlineStr"/>
-      <c r="I26" s="16" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr"/>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-319-41118-7_3</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>LOW — metadata-defensible</t>
-        </is>
-      </c>
-      <c r="G27" s="15" t="inlineStr"/>
-      <c r="H27" s="15" t="inlineStr"/>
-      <c r="I27" s="16" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I27"/>
+  <autoFilter ref="A1:I22"/>
   <dataValidations count="2">
-    <dataValidation sqref="G3:G27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G3:G22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Include,Exclude"</formula1>
     </dataValidation>
   </dataValidations>

--- a/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
+++ b/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2_TA_Excluded_Sample'!$A$1:$E$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3_Extraction_Verification'!$A$1:$M$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4_RoB_Review'!$A$1:$Q$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23574,7 +23574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -24100,7 +24100,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -24110,17 +24110,17 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Cancer-related risk factors and incidence of major cancers by race, gender and region; analysis of the NIH-AARP diet and health study (2017)</t>
+          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>28854891</t>
+          <t>39808161</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>10.1186/s12885-017-3557-1</t>
+          <t>10.1158/1055-9965.epi-24-1325</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -24135,7 +24135,7 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
@@ -24145,17 +24145,17 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Cancer incidence in the Somali population of Olmsted County: A Rochester epidemiology project study (2023)</t>
+          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>37740603</t>
+          <t>38801414</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cam4.6558</t>
+          <t>10.1158/1055-9965.epi-24-0072</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
@@ -24170,32 +24170,28 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>INCLUDED (narrative)</t>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Early-Onset Cancer Incidence Disparities Between Black and White Individuals in the US, 2003-2022 (2026)</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>41989785</t>
-        </is>
-      </c>
+          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr"/>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>10.1001/jamanetworkopen.2026.7529</t>
+          <t>10.1101/2022.02.21.22271266</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>LOW — narrative only</t>
+          <t>LOW — metadata-defensible</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr"/>
@@ -24205,142 +24201,41 @@
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>INCLUDED (narrative)</t>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>39808161</t>
-        </is>
-      </c>
+          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr"/>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-24-1325</t>
+          <t>10.1007/978-3-319-41118-7_3</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>LOW — narrative only</t>
+          <t>LOW — metadata-defensible</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr"/>
       <c r="H19" s="15" t="inlineStr"/>
       <c r="I19" s="16" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>INCLUDED (narrative)</t>
-        </is>
-      </c>
-      <c r="C20" s="14" t="inlineStr">
-        <is>
-          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>38801414</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>10.1158/1055-9965.epi-24-0072</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
-        <is>
-          <t>LOW — narrative only</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="inlineStr"/>
-      <c r="H20" s="15" t="inlineStr"/>
-      <c r="I20" s="16" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>2163</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="inlineStr">
-        <is>
-          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>10.1101/2022.02.21.22271266</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
-        <is>
-          <t>LOW — metadata-defensible</t>
-        </is>
-      </c>
-      <c r="G21" s="15" t="inlineStr"/>
-      <c r="H21" s="15" t="inlineStr"/>
-      <c r="I21" s="16" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr"/>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-319-41118-7_3</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
-        <is>
-          <t>LOW — metadata-defensible</t>
-        </is>
-      </c>
-      <c r="G22" s="15" t="inlineStr"/>
-      <c r="H22" s="15" t="inlineStr"/>
-      <c r="I22" s="16" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
+  <autoFilter ref="A1:I19"/>
   <dataValidations count="2">
-    <dataValidation sqref="G3:G22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G3:G19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Include,Exclude"</formula1>
     </dataValidation>
   </dataValidations>

--- a/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
+++ b/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2_TA_Excluded_Sample'!$A$1:$E$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3_Extraction_Verification'!$A$1:$M$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4_RoB_Review'!$A$1:$Q$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23574,7 +23574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -23677,32 +23677,32 @@
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>157</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>INCLUDED (quant-extracted)</t>
+          <t>EXCLUDED (Full text unavailable)</t>
         </is>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>State Variation in Racial and Ethnic Disparities in Incidence of Triple-Negative Breast Cancer among US Women (2023)</t>
+          <t>Breast cancer trends among black and white women in the United States (2005)</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>36862439</t>
+          <t>16258086</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>10.1001/jamaoncol.2022.7835</t>
+          <t>10.1200/jco.2004.01.0421</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>HIGH — extracted without main PDF</t>
+          <t>HIGH — not retrieved (possible missed study)</t>
         </is>
       </c>
       <c r="G3" s="15" t="inlineStr"/>
@@ -23712,7 +23712,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>253</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -23722,19 +23722,15 @@
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>Breast cancer trends among black and white women in the United States (2005)</t>
+          <t>Breast cancer patterns and lifetime risk of developing breast cancer among Puerto Rican females. (2000)</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>16258086</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>10.1200/jco.2004.01.0421</t>
-        </is>
-      </c>
+          <t>10761199</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr"/>
       <c r="F4" s="14" t="inlineStr">
         <is>
           <t>HIGH — not retrieved (possible missed study)</t>
@@ -23747,7 +23743,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>415</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -23757,12 +23753,12 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Breast cancer patterns and lifetime risk of developing breast cancer among Puerto Rican females. (2000)</t>
+          <t>Women's cancers among Alaska Natives 1969-2003. (2006)</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>10761199</t>
+          <t>17929614</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr"/>
@@ -23778,7 +23774,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>424</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -23788,12 +23784,12 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Women's cancers among Alaska Natives 1969-2003. (2006)</t>
+          <t>Breast cancer in a multiethnic cohort in Hawaii and Los Angeles: Risk factor-adjusted incidence in Japanese equals and in Hawaiians exceeds that in whites (2002)</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>17929614</t>
+          <t>12223421</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr"/>
@@ -23809,7 +23805,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>428</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -23819,12 +23815,12 @@
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>Breast cancer in a multiethnic cohort in Hawaii and Los Angeles: Risk factor-adjusted incidence in Japanese equals and in Hawaiians exceeds that in whites (2002)</t>
+          <t>Women's cancers among Alaska Natives: [corrected] 1969-2003. (2007)</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>12223421</t>
+          <t>18323374</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr"/>
@@ -23840,7 +23836,7 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>476</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -23850,15 +23846,19 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Women's cancers among Alaska Natives: [corrected] 1969-2003. (2007)</t>
+          <t>Rural–urban disparities in breast cancer incidence among US women aged 20–49: trends by race/ethnicity, stage, poverty, and state from 2000–2019 (2026)</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>18323374</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr"/>
+          <t>41665696</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s10552-026-02134-3</t>
+        </is>
+      </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
           <t>HIGH — not retrieved (possible missed study)</t>
@@ -23871,7 +23871,7 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
@@ -23881,19 +23881,11 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>Rural–urban disparities in breast cancer incidence among US women aged 20–49: trends by race/ethnicity, stage, poverty, and state from 2000–2019 (2026)</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>41665696</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>10.1007/s10552-026-02134-3</t>
-        </is>
-      </c>
+          <t>Incidence trends in triple-negative breast cancer among women in the United States from 2010 to 2019 by race/ethnicity, age and tumor stage (2023)</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
       <c r="F9" s="14" t="inlineStr">
         <is>
           <t>HIGH — not retrieved (possible missed study)</t>
@@ -23906,7 +23898,7 @@
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
@@ -23916,11 +23908,15 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>Incidence trends in triple-negative breast cancer among women in the United States from 2010 to 2019 by race/ethnicity, age and tumor stage (2023)</t>
+          <t>Time trends and racial differences in female breast cancer incidence in Pennsylvania, 1985-2004 (2011)</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr"/>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>10.1089/jwh.2010.2082</t>
+        </is>
+      </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
           <t>HIGH — not retrieved (possible missed study)</t>
@@ -23933,7 +23929,7 @@
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
@@ -23943,15 +23939,15 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>Time trends and racial differences in female breast cancer incidence in Pennsylvania, 1985-2004 (2011)</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr"/>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>10.1089/jwh.2010.2082</t>
-        </is>
-      </c>
+          <t>Improving cancer incidence estimates for American Indians in Wisconsin (2007)</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>17844709</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr"/>
       <c r="F11" s="14" t="inlineStr">
         <is>
           <t>HIGH — not retrieved (possible missed study)</t>
@@ -23964,28 +23960,32 @@
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>251</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>EXCLUDED (Full text unavailable)</t>
+          <t>EXCLUDED (Did not report the outcome of interest)</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Improving cancer incidence estimates for American Indians in Wisconsin (2007)</t>
+          <t>Triple-negative breast cancer incidence in the United States: ecological correlations with area-level sociodemographics, healthcare, and health behaviors (2021)</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>17844709</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr"/>
+          <t>32671723</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>10.1007/s12282-020-01132-w</t>
+        </is>
+      </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>HIGH — not retrieved (possible missed study)</t>
+          <t>MED — excluded without full text</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr"/>
@@ -23995,32 +23995,32 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>251</t>
+          <t>80</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>EXCLUDED (Did not report the outcome of interest)</t>
+          <t>INCLUDED (narrative)</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Triple-negative breast cancer incidence in the United States: ecological correlations with area-level sociodemographics, healthcare, and health behaviors (2021)</t>
+          <t>Breast, Colorectal, and Prostate Cancer Incidence among Filipino Americans by Generational Status in the Multiethnic Cohort Study (2024)</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>32671723</t>
+          <t>39132985</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>10.1007/s12282-020-01132-w</t>
+          <t>10.1158/1055-9965.epi-24-0647</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>MED — excluded without full text</t>
+          <t>LOW — narrative only</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr"/>
@@ -24030,7 +24030,7 @@
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>402</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
@@ -24040,17 +24040,17 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Breast, Colorectal, and Prostate Cancer Incidence among Filipino Americans by Generational Status in the Multiethnic Cohort Study (2024)</t>
+          <t>Disparities in Breast Cancer Incidence, Mortality, and Quality of Care among African American and European American Women in South Carolina (2016)</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>39132985</t>
+          <t>26741869</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-24-0647</t>
+          <t>10.14423/smj.0000000000000396</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
@@ -24065,7 +24065,7 @@
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>1637</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
@@ -24075,17 +24075,17 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Disparities in Breast Cancer Incidence, Mortality, and Quality of Care among African American and European American Women in South Carolina (2016)</t>
+          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>26741869</t>
+          <t>39808161</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>10.14423/smj.0000000000000396</t>
+          <t>10.1158/1055-9965.epi-24-1325</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
@@ -24100,7 +24100,7 @@
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
@@ -24110,17 +24110,17 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Cancer Incidence in the Hispanic Community Health Study/Study of Latinos (HCHS/SOL)—The Onco-SOL Ancillary Study (2025)</t>
+          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>39808161</t>
+          <t>38801414</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-24-1325</t>
+          <t>10.1158/1055-9965.epi-24-0072</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -24135,32 +24135,28 @@
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>INCLUDED (narrative)</t>
+          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Rural–Urban Cancer Incidence and Trends in the United States, 2000 to 2019 (2024)</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>38801414</t>
-        </is>
-      </c>
+          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr"/>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-24-0072</t>
+          <t>10.1101/2022.02.21.22271266</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>LOW — narrative only</t>
+          <t>LOW — metadata-defensible</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr"/>
@@ -24170,7 +24166,7 @@
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
@@ -24180,13 +24176,13 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Estrogen receptor negative breast cancer incidence rates are similar in Ghanaian and Non-Hispanic Black women in the USA (2022)</t>
+          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr"/>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>10.1101/2022.02.21.22271266</t>
+          <t>10.1007/978-3-319-41118-7_3</t>
         </is>
       </c>
       <c r="F18" s="14" t="inlineStr">
@@ -24198,44 +24194,13 @@
       <c r="H18" s="15" t="inlineStr"/>
       <c r="I18" s="16" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>3713</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>EXCLUDED (Overlapping or duplicate dataset)</t>
-        </is>
-      </c>
-      <c r="C19" s="14" t="inlineStr">
-        <is>
-          <t>Cancer incidence and mortality among Filipinos in the USA and the Philippines: Patterns and trends (2016)</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr"/>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-319-41118-7_3</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>LOW — metadata-defensible</t>
-        </is>
-      </c>
-      <c r="G19" s="15" t="inlineStr"/>
-      <c r="H19" s="15" t="inlineStr"/>
-      <c r="I19" s="16" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I19"/>
+  <autoFilter ref="A1:I18"/>
   <dataValidations count="2">
-    <dataValidation sqref="G3:G19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G3:G18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H3:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Include,Exclude"</formula1>
     </dataValidation>
   </dataValidations>

--- a/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
+++ b/meta_agents/search_v2/outputs/Author_Validation_Workbook.xlsx
@@ -18,8 +18,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'1_FullText_Inclusion'!$A$1:$I$244</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2_TA_Excluded_Sample'!$A$1:$E$152</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3_Extraction_Verification'!$A$1:$M$147</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4_RoB_Review'!$A$1:$Q$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'3_Extraction_Verification'!$A$1:$M$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'4_RoB_Review'!$A$1:$Q$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'6_FullText_ToObtain'!$A$1:$I$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1747,22 +1747,22 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>209</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Breast Cancer Incidence in Asian American, Native Hawaiian, and Pacific Islander Populations, 2000-2022 (2026)</t>
+          <t>Racial and regional disparities of triple negative breast cancer incidence rates in the United States: An analysis of 2011-2019 NPCR and SEER incidence data (2022)</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>42377954</t>
+          <t>36530732</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>10.1001/jamanetworkopen.2026.21250</t>
+          <t>10.3389/fpubh.2022.1058722</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; SEER-21</t>
+          <t>Included — quant-extracted synthesis; NPCR + SEER (USCS)</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr"/>
@@ -1782,20 +1782,24 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Hidden breast cancer disparities in Asian women: disaggregating incidence rates by ethnicity and migrant status. (2010)</t>
+          <t>Breast Cancer Incidence in Asian American, Native Hawaiian, and Pacific Islander Populations, 2000-2022 (2026)</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>20147696</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr"/>
+          <t>42377954</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>10.1001/jamanetworkopen.2026.21250</t>
+        </is>
+      </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Include</t>
@@ -1803,7 +1807,7 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; California Cancer Registry</t>
+          <t>Included — quant-extracted synthesis; SEER-21</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr"/>
@@ -1813,24 +1817,20 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Age-related crossover in breast cancer incidence rates between black and white ethnic groups (2008)</t>
+          <t>Hidden breast cancer disparities in Asian women: disaggregating incidence rates by ethnicity and migrant status. (2010)</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>19066264</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>10.1093/jnci/djn411</t>
-        </is>
-      </c>
+          <t>20147696</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Include</t>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; SEER 9</t>
+          <t>Included — quant-extracted synthesis; California Cancer Registry</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr"/>
@@ -1848,22 +1848,22 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>265</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Variation in breast cancer subtype incidence and distribution by race/ethnicity in the United States from 2010 to 2015 (2020)</t>
+          <t>Age-related crossover in breast cancer incidence rates between black and white ethnic groups (2008)</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>33074325</t>
+          <t>19066264</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>10.1001/jamanetworkopen.2020.20303</t>
+          <t>10.1093/jnci/djn411</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; SEER 18</t>
+          <t>Included — quant-extracted synthesis; SEER 9</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr"/>
@@ -1883,22 +1883,22 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Breast cancer in Asian Americans in California, 1988–2013: increasing incidence trends and recent data on breast cancer subtypes (2017)</t>
+          <t>Variation in breast cancer subtype incidence and distribution by race/ethnicity in the United States from 2010 to 2015 (2020)</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>28365834</t>
+          <t>33074325</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>10.1007/s10549-017-4229-1</t>
+          <t>10.1001/jamanetworkopen.2020.20303</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; California Cancer Registry</t>
+          <t>Included — quant-extracted synthesis; SEER 18</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr"/>
@@ -1918,22 +1918,22 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>324</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Breast cancer incidence patterns among california hispanic women: Differences by nativity and residence in an enclave (2010)</t>
+          <t>Breast cancer in Asian Americans in California, 1988–2013: increasing incidence trends and recent data on breast cancer subtypes (2017)</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>20447917</t>
+          <t>28365834</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-10-0021</t>
+          <t>10.1007/s10549-017-4229-1</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -1953,22 +1953,22 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Patterns and Trends in Age-Specific Black-White Differences in Breast Cancer Incidence and Mortality - United States, 1999-2014 (2016)</t>
+          <t>Breast cancer incidence patterns among california hispanic women: Differences by nativity and residence in an enclave (2010)</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>27736827</t>
+          <t>20447917</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>10.15585/mmwr.mm6540a1</t>
+          <t>10.1158/1055-9965.epi-10-0021</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="F26" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; USCS</t>
+          <t>Included — quant-extracted synthesis; California Cancer Registry</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr"/>
@@ -1988,22 +1988,22 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>346</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Age/race differences in HER2 testing and in incidence rates for breast cancer triple subtypes: A population-based study and first report (2010)</t>
+          <t>Patterns and Trends in Age-Specific Black-White Differences in Breast Cancer Incidence and Mortality - United States, 1999-2014 (2016)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>20336785</t>
+          <t>27736827</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cncr.25016</t>
+          <t>10.15585/mmwr.mm6540a1</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F27" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; Atlanta SEER + Georgia registry</t>
+          <t>Included — quant-extracted synthesis; USCS</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr"/>
@@ -2023,22 +2023,22 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>381</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Recent trends in breast cancer incidence among 6 Asian groups in the Greater Bay Area of Northern California (2007)</t>
+          <t>Age/race differences in HER2 testing and in incidence rates for breast cancer triple subtypes: A population-based study and first report (2010)</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>17163416</t>
+          <t>20336785</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>10.1002/ijc.22432</t>
+          <t>10.1002/cncr.25016</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; Greater Bay Area / CCR</t>
+          <t>Included — quant-extracted synthesis; Atlanta SEER + Georgia registry</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr"/>
@@ -2058,22 +2058,22 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>419</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Trends in area-socioeconomic and race-ethnic disparities in breast cancer incidence, stage at diagnosis, screening, mortality, and survival among women ages 50 years and over (1987-2005) (2009)</t>
+          <t>Higher population-based incidence rates of triple-negative breast cancer among young African-American women (2011)</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>19124489</t>
+          <t>21656753</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-08-0679</t>
+          <t>10.1002/cncr.25862</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; SEER</t>
+          <t>Included — quant-extracted synthesis; California Cancer Registry</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr"/>
@@ -2093,22 +2093,22 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>461</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Trends in Cancer Incidence among American Indians and Alaska Natives and Non-Hispanic Whites in the United States, 1999-2015 (2020)</t>
+          <t>Trends and Patterns of Late and Unstaged Lung, Colorectal, Female Breast, and  Prostate Cancers among American Indians in the Northern Plains, 2002-2009 (2015)</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>31764279</t>
+          <t>26320932</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>10.1097/ede.0000000000001140</t>
+          <t>10.1353/hpu.2015.0089</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; CDC USCS (NPCR+SEER)</t>
+          <t>Included — quant-extracted synthesis; NE/ND/SD state registries</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr"/>
@@ -2128,22 +2128,22 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>463</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Characterizing breast cancer incidence and trends among Asian American, Native Hawaiian, and non-Hispanic White women in Hawaiʻi, 1990-2014 (2023)</t>
+          <t>Recent trends in breast cancer incidence among 6 Asian groups in the Greater Bay Area of Northern California (2007)</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>36504334</t>
+          <t>17163416</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>10.1007/s10552-022-01659-7</t>
+          <t>10.1002/ijc.22432</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; Hawaii Tumor Registry</t>
+          <t>Included — quant-extracted synthesis; Greater Bay Area / CCR</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr"/>
@@ -2163,22 +2163,22 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Breast cancer in the middle eastern population of California, 1988-2004 (2009)</t>
+          <t>Trends in area-socioeconomic and race-ethnic disparities in breast cancer incidence, stage at diagnosis, screening, mortality, and survival among women ages 50 years and over (1987-2005) (2009)</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>19292805</t>
+          <t>19124489</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>10.1111/j.1524-4741.2009.00694.x</t>
+          <t>10.1158/1055-9965.epi-08-0679</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; California Cancer Registry</t>
+          <t>Included — quant-extracted synthesis; SEER</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr"/>
@@ -2198,22 +2198,22 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>500</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Cancer among Asian Indians/Pakistanis living in the United States: Low incidence and generally above average survival (2009)</t>
+          <t>Trends in Cancer Incidence among American Indians and Alaska Natives and Non-Hispanic Whites in the United States, 1999-2015 (2020)</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>19067192</t>
+          <t>31764279</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>10.1007/s10552-008-9275-x</t>
+          <t>10.1097/ede.0000000000001140</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; SEER</t>
+          <t>Included — quant-extracted synthesis; CDC USCS (NPCR+SEER)</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr"/>
@@ -2233,22 +2233,22 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Cancer incidence, stage at diagnosis, and trends across the Navajo Nation, 2014–2018 (2025)</t>
+          <t>Characterizing breast cancer incidence and trends among Asian American, Native Hawaiian, and non-Hispanic White women in Hawaiʻi, 1990-2014 (2023)</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>41385397</t>
+          <t>36504334</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cncr.70202</t>
+          <t>10.1007/s10552-022-01659-7</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; NM Tumor Registry + AZ + UT (IHS-linked)</t>
+          <t>Included — quant-extracted synthesis; Hawaii Tumor Registry</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr"/>
@@ -2268,22 +2268,22 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>587</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Associations of Obesity, Physical Activity, and Screening With State-Level Trends and Racial and Ethnic Disparities of Breast Cancer Incidence and Mortality in the US (2022)</t>
+          <t>Breast cancer in the middle eastern population of California, 1988-2004 (2009)</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>35699957</t>
+          <t>19292805</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>10.1001/jamanetworkopen.2022.16958</t>
+          <t>10.1111/j.1524-4741.2009.00694.x</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; USCS</t>
+          <t>Included — quant-extracted synthesis; California Cancer Registry</t>
         </is>
       </c>
       <c r="G35" s="15" t="inlineStr"/>
@@ -2303,22 +2303,22 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>955</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Subtype-specific breast cancer incidence rates in black versus white men in the United States (2020)</t>
+          <t>Cancer among Asian Indians/Pakistanis living in the United States: Low incidence and generally above average survival (2009)</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>32337499</t>
+          <t>19067192</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>10.1093/jncics/pkz091</t>
+          <t>10.1007/s10552-008-9275-x</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; NPCR+SEER</t>
+          <t>Included — quant-extracted synthesis; SEER</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr"/>
@@ -2338,22 +2338,22 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Disparities in cancer incidence and trends among American Indians and Alaska natives in the United States, 2010–2015 (2019)</t>
+          <t>Cancer incidence, stage at diagnosis, and trends across the Navajo Nation, 2014–2018 (2025)</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>31575554</t>
+          <t>41385397</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-19-0288</t>
+          <t>10.1002/cncr.70202</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -2363,7 +2363,7 @@
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; NPCR (IHS-linked)</t>
+          <t>Included — quant-extracted synthesis; NM Tumor Registry + AZ + UT (IHS-linked)</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr"/>
@@ -2373,22 +2373,22 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Cancer incidence in first generation U.S. Hispanics: Cubans, Mexicans, Puerto Ricans, and New Latinos (2009)</t>
+          <t>Associations of Obesity, Physical Activity, and Screening With State-Level Trends and Racial and Ethnic Disparities of Breast Cancer Incidence and Mortality in the US (2022)</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>19661072</t>
+          <t>35699957</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>10.1158/1055-9965.epi-09-0329</t>
+          <t>10.1001/jamanetworkopen.2022.16958</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; Florida Cancer Data System</t>
+          <t>Included — quant-extracted synthesis; USCS</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr"/>
@@ -2408,22 +2408,22 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Cambodian cancer incidence rates in California and Washington, 1998-2002 (2007)</t>
+          <t>Cancer disparities among non-Hispanic urban American Indian and Alaska Native populations in the United States, 1999-2017 (2022)</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>17654663</t>
+          <t>35119703</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cncr.22914</t>
+          <t>10.1002/cncr.34122</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; SEER (CA + Puget Sound)</t>
+          <t>Included — quant-extracted synthesis; NPCR+SEER (IHS-linked)</t>
         </is>
       </c>
       <c r="G39" s="15" t="inlineStr"/>
@@ -2443,22 +2443,22 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>2406</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Patterns of cancer incidence among US Hispanics/Latinos, 1995-2000 (2006)</t>
+          <t>Subtype-specific breast cancer incidence rates in black versus white men in the United States (2020)</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>16933057</t>
+          <t>32337499</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>10.1007/s10552-006-0045-3</t>
+          <t>10.1093/jncics/pkz091</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; NAACCR</t>
+          <t>Included — quant-extracted synthesis; NPCR+SEER</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr"/>
@@ -2478,22 +2478,22 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Cancer incidence patterns in Koreans in the US and in Kangwha, South Korea (2003)</t>
+          <t>Disparities in cancer incidence and trends among American Indians and Alaska natives in the United States, 2010–2015 (2019)</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>12749722</t>
+          <t>31575554</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>10.1023/a:1023046121214</t>
+          <t>10.1158/1055-9965.epi-19-0288</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; SEER + California</t>
+          <t>Included — quant-extracted synthesis; NPCR (IHS-linked)</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr"/>
@@ -2513,18 +2513,22 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Incidence of and Trends in the Leading Cancers with Elevated Incidence among American Indian and Alaska Native Populations, 2012-2016 (2021)</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="inlineStr"/>
+          <t>Cancer incidence in first generation U.S. Hispanics: Cubans, Mexicans, Puerto Ricans, and New Latinos (2009)</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="inlineStr">
+        <is>
+          <t>19661072</t>
+        </is>
+      </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>10.1093/aje/kwaa222</t>
+          <t>10.1158/1055-9965.epi-09-0329</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -2534,7 +2538,7 @@
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; NPCR+SEER (IHS-linked)</t>
+          <t>Included — quant-extracted synthesis; Florida Cancer Data System</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr"/>
@@ -2544,22 +2548,22 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Cancer incidence and mortality patterns among specific Asian and Pacific Islander populations in the US (2008)</t>
+          <t>Cambodian cancer incidence rates in California and Washington, 1998-2002 (2007)</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>18066673</t>
+          <t>17654663</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>10.1007/s10552-007-9088-3</t>
+          <t>10.1002/cncr.22914</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -2569,7 +2573,7 @@
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; SEER + state</t>
+          <t>Included — quant-extracted synthesis; SEER (CA + Puget Sound)</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr"/>
@@ -2579,22 +2583,22 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Cancer incidence, mortality, and associated risk factors among Asian Americans of Chinese, Filipino, Vietnamese, Korean, and Japanese ethnicities (2007)</t>
+          <t>Patterns of cancer incidence among US Hispanics/Latinos, 1995-2000 (2006)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>17626117</t>
+          <t>16933057</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>10.3322/canjclin.57.4.190</t>
+          <t>10.1007/s10552-006-0045-3</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -2604,7 +2608,7 @@
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; California Cancer Registry</t>
+          <t>Included — quant-extracted synthesis; NAACCR</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr"/>
@@ -2614,22 +2618,22 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Cancer among Hispanic women in South Florida: An 18-year assessment - A report from the Florida Cancer Data System (2002)</t>
+          <t>Cancer incidence patterns in Koreans in the US and in Kangwha, South Korea (2003)</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>12365024</t>
+          <t>12749722</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cncr.10834</t>
+          <t>10.1023/a:1023046121214</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -2639,7 +2643,7 @@
       </c>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-extracted synthesis; Florida Cancer Data System</t>
+          <t>Included — quant-extracted synthesis; SEER + California</t>
         </is>
       </c>
       <c r="G45" s="15" t="inlineStr"/>
@@ -2649,22 +2653,18 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Racial and regional disparities of triple negative breast cancer incidence rates in the United States: An analysis of 2011-2019 NPCR and SEER incidence data (2022)</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="inlineStr">
-        <is>
-          <t>36530732</t>
-        </is>
-      </c>
+          <t>Incidence of and Trends in the Leading Cancers with Elevated Incidence among American Indian and Alaska Native Populations, 2012-2016 (2021)</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr"/>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>10.3389/fpubh.2022.1058722</t>
+          <t>10.1093/aje/kwaa222</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-eligible synthesis; NPCR + SEER (USCS)</t>
+          <t>Included — quant-extracted synthesis; NPCR+SEER (IHS-linked)</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr"/>
@@ -2684,22 +2684,22 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Higher population-based incidence rates of triple-negative breast cancer among young African-American women (2011)</t>
+          <t>Cancer incidence among Asian American populations in the United States, 2009-2011 (2016)</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>21656753</t>
+          <t>26661680</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cncr.25862</t>
+          <t>10.1002/ijc.29958</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-eligible synthesis; California Cancer Registry</t>
+          <t>Included — quant-extracted synthesis; SEER + state (NPCR)</t>
         </is>
       </c>
       <c r="G47" s="15" t="inlineStr"/>
@@ -2719,22 +2719,22 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Trends and Patterns of Late and Unstaged Lung, Colorectal, Female Breast, and  Prostate Cancers among American Indians in the Northern Plains, 2002-2009 (2015)</t>
+          <t>Cancer incidence and mortality patterns among specific Asian and Pacific Islander populations in the US (2008)</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>26320932</t>
+          <t>18066673</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>10.1353/hpu.2015.0089</t>
+          <t>10.1007/s10552-007-9088-3</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-eligible synthesis; NE/ND/SD state registries</t>
+          <t>Included — quant-extracted synthesis; SEER + state</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr"/>
@@ -2754,22 +2754,22 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>2137</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Cancer disparities among non-Hispanic urban American Indian and Alaska Native populations in the United States, 1999-2017 (2022)</t>
+          <t>Cancer incidence, mortality, and associated risk factors among Asian Americans of Chinese, Filipino, Vietnamese, Korean, and Japanese ethnicities (2007)</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>35119703</t>
+          <t>17626117</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>10.1002/cncr.34122</t>
+          <t>10.3322/canjclin.57.4.190</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-eligible synthesis; NPCR+SEER (IHS-linked)</t>
+          <t>Included — quant-extracted synthesis; California Cancer Registry</t>
         </is>
       </c>
       <c r="G49" s="15" t="inlineStr"/>
@@ -2789,22 +2789,22 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Cancer incidence among Asian American populations in the United States, 2009-2011 (2016)</t>
+          <t>Cancer among Hispanic women in South Florida: An 18-year assessment - A report from the Florida Cancer Data System (2002)</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>26661680</t>
+          <t>12365024</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>10.1002/ijc.29958</t>
+          <t>10.1002/cncr.10834</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>Included — quant-eligible synthesis; SEER + state (NPCR)</t>
+          <t>Included — quant-extracted synthesis; Florida Cancer Data System</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr"/>
@@ -12408,7 +12408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M147"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -12663,7 +12663,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Asian-American combined</t>
+          <t>Asian American (aggregate)</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Asian-American combined</t>
+          <t>Asian American (aggregate)</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -14685,32 +14685,32 @@
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>Black (men)</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>White (men)</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>male-BC</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>181.5</t>
         </is>
       </c>
       <c r="H43" s="13" t="inlineStr">
         <is>
-          <t>1.52 [1.44, 1.6]</t>
+          <t>0.98 [0.97, 0.98]</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (overall male)</t>
+          <t>Table 1 (female overall)</t>
         </is>
       </c>
       <c r="K43" s="15" t="inlineStr"/>
@@ -14730,34 +14730,42 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Sung2020_USCS50</t>
+          <t>Nash2019_ANTR</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>Black (men)</t>
+          <t>Alaska Native</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>White (men)</t>
+          <t>US White</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>male-BC-HRpos-HER2neg</t>
-        </is>
-      </c>
-      <c r="F44" s="13" t="inlineStr"/>
-      <c r="G44" s="13" t="inlineStr"/>
+          <t>AIAN</t>
+        </is>
+      </c>
+      <c r="F44" s="13" t="inlineStr">
+        <is>
+          <t>145.0 [130.4, 159.5]</t>
+        </is>
+      </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>133.0 [132.2, 133.8]</t>
+        </is>
+      </c>
       <c r="H44" s="13" t="inlineStr">
         <is>
-          <t>1.41 [1.32, 1.5]</t>
+          <t>1.09 [0.99, 1.21]</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
@@ -14767,7 +14775,7 @@
       </c>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table 3 (all ages)</t>
         </is>
       </c>
       <c r="K44" s="15" t="inlineStr"/>
@@ -14777,34 +14785,34 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>199</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Sung2020_USCS50</t>
+          <t>Baquet2008_SEER9</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>Black (men)</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>White (men)</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>male-BC-HRpos-HER2pos</t>
+          <t>age-lt40</t>
         </is>
       </c>
       <c r="F45" s="13" t="inlineStr"/>
       <c r="G45" s="13" t="inlineStr"/>
       <c r="H45" s="13" t="inlineStr">
         <is>
-          <t>1.65 [1.4, 1.93]</t>
+          <t>1.16 [1.1, 1.23]</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
@@ -14814,7 +14822,7 @@
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K45" s="15" t="inlineStr"/>
@@ -14824,34 +14832,34 @@
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Sung2020_USCS50</t>
+          <t>Zahrieh2021_NM-SEER</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>Black (men)</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>White (men)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>male-BC-TNBC</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr"/>
       <c r="G46" s="13" t="inlineStr"/>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>2.27 [1.67, 3.03]</t>
+          <t>0.384 [0.253, 0.546]</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
@@ -14861,7 +14869,7 @@
       </c>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Table (overall RR, Bayesian)</t>
         </is>
       </c>
       <c r="K46" s="15" t="inlineStr"/>
@@ -14871,34 +14879,34 @@
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Sung2020_USCS50</t>
+          <t>Loo2019_HTR</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>Black (men)</t>
+          <t>Native Hawaiian</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>White (men)</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>male-BC-HRneg-HER2pos</t>
+          <t>subtype-HRpos-HER2neg</t>
         </is>
       </c>
       <c r="F47" s="13" t="inlineStr"/>
       <c r="G47" s="13" t="inlineStr"/>
       <c r="H47" s="13" t="inlineStr">
         <is>
-          <t>2.62 [1.48, 4.43]</t>
+          <t>1.12 [1.11, 1.14]</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
@@ -14908,7 +14916,7 @@
       </c>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K47" s="15" t="inlineStr"/>
@@ -14918,42 +14926,34 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>2406</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Sung2020_USCS50</t>
+          <t>Loo2019_HTR</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>Black (women)</t>
+          <t>Native Hawaiian</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>White (women)</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
-        </is>
-      </c>
-      <c r="F48" s="13" t="inlineStr">
-        <is>
-          <t>177.0</t>
-        </is>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
-        <is>
-          <t>181.5</t>
-        </is>
-      </c>
+          <t>subtype-HRpos-HER2pos</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr"/>
+      <c r="G48" s="13" t="inlineStr"/>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>0.98 [0.97, 0.98]</t>
+          <t>1.35 [1.347, 1.351]</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (female overall)</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K48" s="15" t="inlineStr"/>
@@ -14973,42 +14973,34 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Nash2019_ANTR</t>
+          <t>Loo2019_HTR</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>Alaska Native</t>
+          <t>Native Hawaiian</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>US White</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
-        </is>
-      </c>
-      <c r="F49" s="13" t="inlineStr">
-        <is>
-          <t>145.0 [130.4, 159.5]</t>
-        </is>
-      </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t>133.0 [132.2, 133.8]</t>
-        </is>
-      </c>
+          <t>subtype-HRneg-HER2pos</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr"/>
+      <c r="G49" s="13" t="inlineStr"/>
       <c r="H49" s="13" t="inlineStr">
         <is>
-          <t>1.09 [0.99, 1.21]</t>
+          <t>1.19 [1.16, 1.21]</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
@@ -15018,7 +15010,7 @@
       </c>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>Table 3 (all ages)</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K49" s="15" t="inlineStr"/>
@@ -15028,17 +15020,17 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Baquet2008_SEER9</t>
+          <t>Loo2019_HTR</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>Black (age&lt;40)</t>
+          <t>Native Hawaiian</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
@@ -15048,14 +15040,14 @@
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>age-lt40</t>
+          <t>subtype-TNBC</t>
         </is>
       </c>
       <c r="F50" s="13" t="inlineStr"/>
       <c r="G50" s="13" t="inlineStr"/>
       <c r="H50" s="13" t="inlineStr">
         <is>
-          <t>1.16 [1.1, 1.23]</t>
+          <t>0.86 [0.79, 0.91]</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
@@ -15075,34 +15067,34 @@
     <row r="51">
       <c r="A51" s="13" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Zahrieh2021_NM-SEER</t>
+          <t>Loo2019_HTR</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>subtype-HRpos-HER2neg</t>
         </is>
       </c>
       <c r="F51" s="13" t="inlineStr"/>
       <c r="G51" s="13" t="inlineStr"/>
       <c r="H51" s="13" t="inlineStr">
         <is>
-          <t>0.384 [0.253, 0.546]</t>
+          <t>1.03 [1.03, 1.04]</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
@@ -15112,7 +15104,7 @@
       </c>
       <c r="J51" s="14" t="inlineStr">
         <is>
-          <t>Table (overall RR, Bayesian)</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K51" s="15" t="inlineStr"/>
@@ -15132,7 +15124,7 @@
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>Native Hawaiian</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
@@ -15142,14 +15134,14 @@
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2neg</t>
+          <t>subtype-HRpos-HER2pos</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr"/>
       <c r="G52" s="13" t="inlineStr"/>
       <c r="H52" s="13" t="inlineStr">
         <is>
-          <t>1.12 [1.11, 1.14]</t>
+          <t>1.03 [1.02, 1.05]</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
@@ -15179,7 +15171,7 @@
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>Native Hawaiian</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
@@ -15189,14 +15181,14 @@
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2pos</t>
+          <t>subtype-HRneg-HER2pos</t>
         </is>
       </c>
       <c r="F53" s="13" t="inlineStr"/>
       <c r="G53" s="13" t="inlineStr"/>
       <c r="H53" s="13" t="inlineStr">
         <is>
-          <t>1.35 [1.347, 1.351]</t>
+          <t>0.88 [0.82, 0.95]</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
@@ -15226,7 +15218,7 @@
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>Native Hawaiian</t>
+          <t>Filipina</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
@@ -15236,14 +15228,14 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRneg-HER2pos</t>
+          <t>subtype-HRpos-HER2neg</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr"/>
       <c r="G54" s="13" t="inlineStr"/>
       <c r="H54" s="13" t="inlineStr">
         <is>
-          <t>1.19 [1.16, 1.21]</t>
+          <t>0.64 [0.63, 0.66]</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
@@ -15273,7 +15265,7 @@
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>Native Hawaiian</t>
+          <t>Filipina</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
@@ -15283,14 +15275,14 @@
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
+          <t>subtype-HRpos-HER2pos</t>
         </is>
       </c>
       <c r="F55" s="13" t="inlineStr"/>
       <c r="G55" s="13" t="inlineStr"/>
       <c r="H55" s="13" t="inlineStr">
         <is>
-          <t>0.86 [0.79, 0.91]</t>
+          <t>0.88 [0.86, 0.91]</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
@@ -15320,7 +15312,7 @@
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Filipina</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
@@ -15330,14 +15322,14 @@
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2neg</t>
+          <t>subtype-TNBC</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr"/>
       <c r="G56" s="13" t="inlineStr"/>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>1.03 [1.03, 1.04]</t>
+          <t>0.84 [0.8, 0.88]</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
@@ -15367,7 +15359,7 @@
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
@@ -15377,14 +15369,14 @@
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2pos</t>
+          <t>subtype-HRpos-HER2neg</t>
         </is>
       </c>
       <c r="F57" s="13" t="inlineStr"/>
       <c r="G57" s="13" t="inlineStr"/>
       <c r="H57" s="13" t="inlineStr">
         <is>
-          <t>1.03 [1.02, 1.05]</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I57" s="14" t="inlineStr">
@@ -15414,7 +15406,7 @@
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
@@ -15424,14 +15416,14 @@
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRneg-HER2pos</t>
+          <t>subtype-HRpos-HER2pos</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr"/>
       <c r="G58" s="13" t="inlineStr"/>
       <c r="H58" s="13" t="inlineStr">
         <is>
-          <t>0.88 [0.82, 0.95]</t>
+          <t>0.72 [0.55, 0.9]</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
@@ -15461,7 +15453,7 @@
       </c>
       <c r="C59" s="13" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="D59" s="13" t="inlineStr">
@@ -15471,14 +15463,14 @@
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2neg</t>
+          <t>subtype-TNBC</t>
         </is>
       </c>
       <c r="F59" s="13" t="inlineStr"/>
       <c r="G59" s="13" t="inlineStr"/>
       <c r="H59" s="13" t="inlineStr">
         <is>
-          <t>0.64 [0.63, 0.66]</t>
+          <t>0.53 [0.39, 0.71]</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
@@ -15498,17 +15490,17 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>203</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>Loo2019_HTR</t>
+          <t>Brinton2008_SEER13</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
@@ -15518,24 +15510,32 @@
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2pos</t>
-        </is>
-      </c>
-      <c r="F60" s="13" t="inlineStr"/>
-      <c r="G60" s="13" t="inlineStr"/>
+          <t>age-lt40</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
       <c r="H60" s="13" t="inlineStr">
         <is>
-          <t>0.88 [0.86, 0.91]</t>
+          <t>1.533 [1.352, 1.739]</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-Poisson-SE</t>
         </is>
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="K60" s="15" t="inlineStr"/>
@@ -15545,44 +15545,52 @@
     <row r="61">
       <c r="A61" s="13" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>Loo2019_HTR</t>
+          <t>Ihenacho2023_HTR</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
         <is>
-          <t>Filipino</t>
+          <t>Native Hawaiian</t>
         </is>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
-        </is>
-      </c>
-      <c r="F61" s="13" t="inlineStr"/>
-      <c r="G61" s="13" t="inlineStr"/>
+          <t>age-ge50</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="inlineStr">
+        <is>
+          <t>137.6 [128.2, 147.4]</t>
+        </is>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>100.7 [94.7, 106.9]</t>
+        </is>
+      </c>
       <c r="H61" s="13" t="inlineStr">
         <is>
-          <t>0.84 [0.8, 0.88]</t>
+          <t>1.366 [1.246, 1.499]</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J61" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Results (older &gt;=50)</t>
         </is>
       </c>
       <c r="K61" s="15" t="inlineStr"/>
@@ -15592,44 +15600,52 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>Loo2019_HTR</t>
+          <t>Ihenacho2023_HTR</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2neg</t>
-        </is>
-      </c>
-      <c r="F62" s="13" t="inlineStr"/>
-      <c r="G62" s="13" t="inlineStr"/>
+          <t>age-ge50</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>107.1 [100.9, 113.4]</t>
+        </is>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>100.7 [94.7, 106.9]</t>
+        </is>
+      </c>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.064 [0.978, 1.157]</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J62" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Results (older &gt;=50)</t>
         </is>
       </c>
       <c r="K62" s="15" t="inlineStr"/>
@@ -15639,44 +15655,52 @@
     <row r="63">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Loo2019_HTR</t>
+          <t>Ihenacho2023_HTR</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Filipina</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2pos</t>
-        </is>
-      </c>
-      <c r="F63" s="13" t="inlineStr"/>
-      <c r="G63" s="13" t="inlineStr"/>
+          <t>age-ge50</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>77.9 [71.8, 84.2]</t>
+        </is>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>100.7 [94.7, 106.9]</t>
+        </is>
+      </c>
       <c r="H63" s="13" t="inlineStr">
         <is>
-          <t>0.72 [0.55, 0.9]</t>
+          <t>0.774 [0.700, 0.855]</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J63" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Results (older &gt;=50)</t>
         </is>
       </c>
       <c r="K63" s="15" t="inlineStr"/>
@@ -15686,44 +15710,52 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Loo2019_HTR</t>
+          <t>Ihenacho2023_HTR</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
-        </is>
-      </c>
-      <c r="F64" s="13" t="inlineStr"/>
-      <c r="G64" s="13" t="inlineStr"/>
+          <t>age-lt50</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>39.5 [33.9, 45.4]</t>
+        </is>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>26.7 [24.6, 28.9]</t>
+        </is>
+      </c>
       <c r="H64" s="13" t="inlineStr">
         <is>
-          <t>0.53 [0.39, 0.71]</t>
+          <t>1.479 [1.252, 1.748]</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J64" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Results (young &lt;50)</t>
         </is>
       </c>
       <c r="K64" s="15" t="inlineStr"/>
@@ -15733,52 +15765,52 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>522</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>Brinton2008_SEER13</t>
+          <t>Ihenacho2023_HTR</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Native Hawaiian</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>age-lt40</t>
+          <t>age-lt50</t>
         </is>
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>22.9 [19.2, 27.0]</t>
         </is>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>26.7 [24.6, 28.9]</t>
         </is>
       </c>
       <c r="H65" s="13" t="inlineStr">
         <is>
-          <t>1.533 [1.352, 1.739]</t>
+          <t>0.858 [0.710, 1.036]</t>
         </is>
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-Poisson-SE</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J65" s="14" t="inlineStr">
         <is>
-          <t>Table 1</t>
+          <t>Results (young &lt;50)</t>
         </is>
       </c>
       <c r="K65" s="15" t="inlineStr"/>
@@ -15798,7 +15830,7 @@
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>Native Hawaiian</t>
+          <t>Filipina</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
@@ -15808,22 +15840,22 @@
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>age-ge50</t>
+          <t>age-lt50</t>
         </is>
       </c>
       <c r="F66" s="13" t="inlineStr">
         <is>
-          <t>137.6 [128.2, 147.4]</t>
+          <t>20.5 [17.1, 24.3]</t>
         </is>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>100.7 [94.7, 106.9]</t>
+          <t>26.7 [24.6, 28.9]</t>
         </is>
       </c>
       <c r="H66" s="13" t="inlineStr">
         <is>
-          <t>1.366 [1.246, 1.499]</t>
+          <t>0.768 [0.633, 0.932]</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
@@ -15833,7 +15865,7 @@
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>Results (older &gt;=50)</t>
+          <t>Results (young &lt;50)</t>
         </is>
       </c>
       <c r="K66" s="15" t="inlineStr"/>
@@ -15843,17 +15875,17 @@
     <row r="67">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>Ihenacho2023_HTR</t>
+          <t>Davis Lynn2025_SEER17</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
@@ -15863,22 +15895,22 @@
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>age-ge50</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F67" s="13" t="inlineStr">
         <is>
-          <t>107.1 [100.9, 113.4]</t>
+          <t>148.5 [146.4, 150.7]</t>
         </is>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>100.7 [94.7, 106.9]</t>
+          <t>152.9 [151.9, 153.8]</t>
         </is>
       </c>
       <c r="H67" s="13" t="inlineStr">
         <is>
-          <t>1.064 [0.978, 1.157]</t>
+          <t>0.971 [0.956, 0.987]</t>
         </is>
       </c>
       <c r="I67" s="14" t="inlineStr">
@@ -15888,7 +15920,7 @@
       </c>
       <c r="J67" s="14" t="inlineStr">
         <is>
-          <t>Results (older &gt;=50)</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="K67" s="15" t="inlineStr"/>
@@ -15898,17 +15930,17 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Ihenacho2023_HTR</t>
+          <t>Davis Lynn2025_SEER17</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
@@ -15918,22 +15950,22 @@
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>age-ge50</t>
+          <t>subtype-HRpos</t>
         </is>
       </c>
       <c r="F68" s="13" t="inlineStr">
         <is>
-          <t>77.9 [71.8, 84.2]</t>
+          <t>105.4 [103.6, 107.3]</t>
         </is>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>100.7 [94.7, 106.9]</t>
+          <t>128.5 [127.9, 129.7]</t>
         </is>
       </c>
       <c r="H68" s="13" t="inlineStr">
         <is>
-          <t>0.774 [0.700, 0.855]</t>
+          <t>0.820 [0.805, 0.836]</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
@@ -15943,7 +15975,7 @@
       </c>
       <c r="J68" s="14" t="inlineStr">
         <is>
-          <t>Results (older &gt;=50)</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="K68" s="15" t="inlineStr"/>
@@ -15953,17 +15985,17 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>Ihenacho2023_HTR</t>
+          <t>Davis Lynn2025_SEER17</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
         <is>
-          <t>Japanese</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D69" s="13" t="inlineStr">
@@ -15973,22 +16005,22 @@
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>age-lt50</t>
+          <t>subtype-HRneg</t>
         </is>
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>39.5 [33.9, 45.4]</t>
+          <t>43.1 [42.0, 44.3]</t>
         </is>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>26.7 [24.6, 28.9]</t>
+          <t>24.0 [23.6, 24.4]</t>
         </is>
       </c>
       <c r="H69" s="13" t="inlineStr">
         <is>
-          <t>1.479 [1.252, 1.748]</t>
+          <t>1.796 [1.740, 1.853]</t>
         </is>
       </c>
       <c r="I69" s="14" t="inlineStr">
@@ -15998,7 +16030,7 @@
       </c>
       <c r="J69" s="14" t="inlineStr">
         <is>
-          <t>Results (young &lt;50)</t>
+          <t>Table 2</t>
         </is>
       </c>
       <c r="K69" s="15" t="inlineStr"/>
@@ -16008,17 +16040,17 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>333</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Ihenacho2023_HTR</t>
+          <t>Keegan2010_CCR</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>Native Hawaiian</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
@@ -16028,22 +16060,22 @@
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>age-lt50</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F70" s="13" t="inlineStr">
         <is>
-          <t>22.9 [19.2, 27.0]</t>
+          <t>78.3 [77.4, 79.1]</t>
         </is>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>26.7 [24.6, 28.9]</t>
+          <t>125.7 [125.1, 126.2]</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
         <is>
-          <t>0.858 [0.710, 1.036]</t>
+          <t>0.623 [0.616, 0.630]</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
@@ -16053,7 +16085,7 @@
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>Results (young &lt;50)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr"/>
@@ -16063,17 +16095,17 @@
     <row r="71">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Ihenacho2023_HTR</t>
+          <t>Xu2024_SEER</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>Filipina</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
@@ -16086,29 +16118,21 @@
           <t>age-lt50</t>
         </is>
       </c>
-      <c r="F71" s="13" t="inlineStr">
-        <is>
-          <t>20.5 [17.1, 24.3]</t>
-        </is>
-      </c>
-      <c r="G71" s="13" t="inlineStr">
-        <is>
-          <t>26.7 [24.6, 28.9]</t>
-        </is>
-      </c>
+      <c r="F71" s="13" t="inlineStr"/>
+      <c r="G71" s="13" t="inlineStr"/>
       <c r="H71" s="13" t="inlineStr">
         <is>
-          <t>0.768 [0.633, 0.932]</t>
+          <t>1.01 [1.0, 1.03]</t>
         </is>
       </c>
       <c r="I71" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J71" s="14" t="inlineStr">
         <is>
-          <t>Results (young &lt;50)</t>
+          <t>Table (ages 20-49)</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr"/>
@@ -16118,17 +16142,17 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>Davis Lynn2025_SEER17</t>
+          <t>Xu2024_SEER</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D72" s="13" t="inlineStr">
@@ -16138,32 +16162,24 @@
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="inlineStr">
-        <is>
-          <t>148.5 [146.4, 150.7]</t>
-        </is>
-      </c>
-      <c r="G72" s="13" t="inlineStr">
-        <is>
-          <t>152.9 [151.9, 153.8]</t>
-        </is>
-      </c>
+          <t>age-lt50</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr"/>
+      <c r="G72" s="13" t="inlineStr"/>
       <c r="H72" s="13" t="inlineStr">
         <is>
-          <t>0.971 [0.956, 0.987]</t>
+          <t>0.96 [0.95, 0.97]</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table (ages 20-49)</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr"/>
@@ -16173,17 +16189,17 @@
     <row r="73">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>Davis Lynn2025_SEER17</t>
+          <t>Xu2024_SEER</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
@@ -16193,32 +16209,24 @@
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos</t>
-        </is>
-      </c>
-      <c r="F73" s="13" t="inlineStr">
-        <is>
-          <t>105.4 [103.6, 107.3]</t>
-        </is>
-      </c>
-      <c r="G73" s="13" t="inlineStr">
-        <is>
-          <t>128.5 [127.9, 129.7]</t>
-        </is>
-      </c>
+          <t>age-lt50</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="inlineStr"/>
+      <c r="G73" s="13" t="inlineStr"/>
       <c r="H73" s="13" t="inlineStr">
         <is>
-          <t>0.820 [0.805, 0.836]</t>
+          <t>0.75 [0.72, 0.79]</t>
         </is>
       </c>
       <c r="I73" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J73" s="14" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table (ages 20-49)</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr"/>
@@ -16228,17 +16236,17 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Davis Lynn2025_SEER17</t>
+          <t>Xu2024_SEER</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
@@ -16248,32 +16256,24 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRneg</t>
-        </is>
-      </c>
-      <c r="F74" s="13" t="inlineStr">
-        <is>
-          <t>43.1 [42.0, 44.3]</t>
-        </is>
-      </c>
-      <c r="G74" s="13" t="inlineStr">
-        <is>
-          <t>24.0 [23.6, 24.4]</t>
-        </is>
-      </c>
+          <t>age-lt50</t>
+        </is>
+      </c>
+      <c r="F74" s="13" t="inlineStr"/>
+      <c r="G74" s="13" t="inlineStr"/>
       <c r="H74" s="13" t="inlineStr">
         <is>
-          <t>1.796 [1.740, 1.853]</t>
+          <t>0.76 [0.75, 0.77]</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>Table 2</t>
+          <t>Table (ages 20-49)</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr"/>
@@ -16283,17 +16283,17 @@
     <row r="75">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>333</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>Keegan2010_CCR</t>
+          <t>Sung2023_USCS</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
@@ -16303,32 +16303,32 @@
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>subtype-TNBC</t>
         </is>
       </c>
       <c r="F75" s="13" t="inlineStr">
         <is>
-          <t>78.3 [77.4, 79.1]</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
-          <t>125.7 [125.1, 126.2]</t>
+          <t>12.9</t>
         </is>
       </c>
       <c r="H75" s="13" t="inlineStr">
         <is>
-          <t>0.623 [0.616, 0.630]</t>
+          <t>1.950 [1.930, 1.980]</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J75" s="14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K75" s="15" t="inlineStr"/>
@@ -16338,34 +16338,42 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>Gomez2010_CCR</t>
+          <t>Sung2023_USCS</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
         <is>
-          <t>Chinese (US-born)</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>foreign-born Chinese</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>nativity</t>
-        </is>
-      </c>
-      <c r="F76" s="13" t="inlineStr"/>
-      <c r="G76" s="13" t="inlineStr"/>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F76" s="13" t="inlineStr">
+        <is>
+          <t>11.2</t>
+        </is>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
       <c r="H76" s="13" t="inlineStr">
         <is>
-          <t>1.84 [1.72, 1.96]</t>
+          <t>0.860 [0.800, 0.930]</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
@@ -16375,7 +16383,7 @@
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>Results</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K76" s="15" t="inlineStr"/>
@@ -16385,34 +16393,42 @@
     <row r="77">
       <c r="A77" s="13" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>Gomez2010_CCR</t>
+          <t>Sung2023_USCS</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>Filipina (US-born)</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>foreign-born Filipina</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>nativity</t>
-        </is>
-      </c>
-      <c r="F77" s="13" t="inlineStr"/>
-      <c r="G77" s="13" t="inlineStr"/>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="inlineStr">
+        <is>
+          <t>11.1</t>
+        </is>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
       <c r="H77" s="13" t="inlineStr">
         <is>
-          <t>1.32 [1.2, 1.44]</t>
+          <t>0.860 [0.840, 0.880]</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
@@ -16422,7 +16438,7 @@
       </c>
       <c r="J77" s="14" t="inlineStr">
         <is>
-          <t>Results</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K77" s="15" t="inlineStr"/>
@@ -16432,17 +16448,17 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>Xu2024_SEER</t>
+          <t>Sung2023_USCS</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
@@ -16452,14 +16468,22 @@
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>age-lt50</t>
-        </is>
-      </c>
-      <c r="F78" s="13" t="inlineStr"/>
-      <c r="G78" s="13" t="inlineStr"/>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>12.9</t>
+        </is>
+      </c>
       <c r="H78" s="13" t="inlineStr">
         <is>
-          <t>1.01 [1.0, 1.03]</t>
+          <t>0.700 [0.680, 0.720]</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
@@ -16469,7 +16493,7 @@
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>Table (ages 20-49)</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K78" s="15" t="inlineStr"/>
@@ -16479,34 +16503,34 @@
     <row r="79">
       <c r="A79" s="13" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>Xu2024_SEER</t>
+          <t>Melkonian2019_IHS-PRCDA</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>age-lt50</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F79" s="13" t="inlineStr"/>
       <c r="G79" s="13" t="inlineStr"/>
       <c r="H79" s="13" t="inlineStr">
         <is>
-          <t>0.96 [0.95, 0.97]</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="I79" s="14" t="inlineStr">
@@ -16516,7 +16540,7 @@
       </c>
       <c r="J79" s="14" t="inlineStr">
         <is>
-          <t>Table (ages 20-49)</t>
+          <t>Results (Table 3)</t>
         </is>
       </c>
       <c r="K79" s="15" t="inlineStr"/>
@@ -16526,44 +16550,52 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Xu2024_SEER</t>
+          <t>Xie2022_USCS</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White (NH)</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>age-lt50</t>
-        </is>
-      </c>
-      <c r="F80" s="13" t="inlineStr"/>
-      <c r="G80" s="13" t="inlineStr"/>
+          <t>aggregate-vs-NHW</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="inlineStr">
+        <is>
+          <t>123.2 [122.9, 123.6]</t>
+        </is>
+      </c>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
+          <t>131.0 [130.8, 131.1]</t>
+        </is>
+      </c>
       <c r="H80" s="13" t="inlineStr">
         <is>
-          <t>0.75 [0.72, 0.79]</t>
+          <t>0.940 [0.938, 0.943]</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>Table (ages 20-49)</t>
+          <t>Table (avg rate)</t>
         </is>
       </c>
       <c r="K80" s="15" t="inlineStr"/>
@@ -16573,44 +16605,52 @@
     <row r="81">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>Xu2024_SEER</t>
+          <t>Xie2022_USCS</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White (NH)</t>
         </is>
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>age-lt50</t>
-        </is>
-      </c>
-      <c r="F81" s="13" t="inlineStr"/>
-      <c r="G81" s="13" t="inlineStr"/>
+          <t>aggregate-vs-NHW</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="inlineStr">
+        <is>
+          <t>94.0 [92.7, 95.4]</t>
+        </is>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>131.0 [130.8, 131.1]</t>
+        </is>
+      </c>
       <c r="H81" s="13" t="inlineStr">
         <is>
-          <t>0.76 [0.75, 0.77]</t>
+          <t>0.718 [0.707, 0.728]</t>
         </is>
       </c>
       <c r="I81" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J81" s="14" t="inlineStr">
         <is>
-          <t>Table (ages 20-49)</t>
+          <t>Table (avg rate)</t>
         </is>
       </c>
       <c r="K81" s="15" t="inlineStr"/>
@@ -16620,52 +16660,52 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>Sung2023_USCS</t>
+          <t>Xie2022_USCS</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White (NH)</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F82" s="13" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>90.9 [90.4, 91.4]</t>
         </is>
       </c>
       <c r="G82" s="13" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>131.0 [130.8, 131.1]</t>
         </is>
       </c>
       <c r="H82" s="13" t="inlineStr">
         <is>
-          <t>1.950 [1.930, 1.980]</t>
+          <t>0.694 [0.690, 0.698]</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Table (avg rate)</t>
         </is>
       </c>
       <c r="K82" s="15" t="inlineStr"/>
@@ -16675,52 +16715,52 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>Sung2023_USCS</t>
+          <t>Xie2022_USCS</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White (NH)</t>
         </is>
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F83" s="13" t="inlineStr">
         <is>
-          <t>11.2</t>
+          <t>93.0 [92.7, 93.4]</t>
         </is>
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>131.0 [130.8, 131.1]</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
         <is>
-          <t>0.860 [0.800, 0.930]</t>
+          <t>0.710 [0.707, 0.713]</t>
         </is>
       </c>
       <c r="I83" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J83" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Table (avg rate)</t>
         </is>
       </c>
       <c r="K83" s="15" t="inlineStr"/>
@@ -16730,52 +16770,52 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>381</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>Sung2023_USCS</t>
+          <t>Lund2010_AtlantaSEER</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White (NH)</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
+          <t>subtype-HRpos-HER2neg</t>
         </is>
       </c>
       <c r="F84" s="13" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>110.7</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
         <is>
-          <t>0.860 [0.840, 0.880]</t>
+          <t>0.783</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Discussion text</t>
         </is>
       </c>
       <c r="K84" s="15" t="inlineStr"/>
@@ -16785,22 +16825,22 @@
     <row r="85">
       <c r="A85" s="13" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>381</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>Sung2023_USCS</t>
+          <t>Lund2010_AtlantaSEER</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White (NH)</t>
         </is>
       </c>
       <c r="E85" s="13" t="inlineStr">
@@ -16810,27 +16850,27 @@
       </c>
       <c r="F85" s="13" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
         <is>
-          <t>0.700 [0.680, 0.720]</t>
+          <t>1.871</t>
         </is>
       </c>
       <c r="I85" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates</t>
         </is>
       </c>
       <c r="J85" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Discussion text</t>
         </is>
       </c>
       <c r="K85" s="15" t="inlineStr"/>
@@ -16840,44 +16880,52 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>2510</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>Melkonian2019_IHS-PRCDA</t>
+          <t>Harper2009_SEER</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>White (NH)</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
-        </is>
-      </c>
-      <c r="F86" s="13" t="inlineStr"/>
-      <c r="G86" s="13" t="inlineStr"/>
+          <t>age-ge50</t>
+        </is>
+      </c>
+      <c r="F86" s="13" t="inlineStr">
+        <is>
+          <t>313.7</t>
+        </is>
+      </c>
+      <c r="G86" s="13" t="inlineStr">
+        <is>
+          <t>343.4</t>
+        </is>
+      </c>
       <c r="H86" s="13" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.914</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>Results (Table 3)</t>
+          <t>Table 1 (women 50+)</t>
         </is>
       </c>
       <c r="K86" s="15" t="inlineStr"/>
@@ -16887,17 +16935,17 @@
     <row r="87">
       <c r="A87" s="13" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>Xie2022_USCS</t>
+          <t>Harper2009_SEER</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D87" s="13" t="inlineStr">
@@ -16907,32 +16955,32 @@
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>age-ge50</t>
         </is>
       </c>
       <c r="F87" s="13" t="inlineStr">
         <is>
-          <t>123.2 [122.9, 123.6]</t>
+          <t>226.2</t>
         </is>
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>131.0 [130.8, 131.1]</t>
+          <t>343.4</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
         <is>
-          <t>0.940 [0.938, 0.943]</t>
+          <t>0.659</t>
         </is>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>computed-from-rates</t>
         </is>
       </c>
       <c r="J87" s="14" t="inlineStr">
         <is>
-          <t>Table (avg rate)</t>
+          <t>Table 1 (women 50+)</t>
         </is>
       </c>
       <c r="K87" s="15" t="inlineStr"/>
@@ -16942,12 +16990,12 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>Xie2022_USCS</t>
+          <t>Harper2009_SEER</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -16962,32 +17010,32 @@
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>age-ge50</t>
         </is>
       </c>
       <c r="F88" s="13" t="inlineStr">
         <is>
-          <t>94.0 [92.7, 95.4]</t>
+          <t>222.1</t>
         </is>
       </c>
       <c r="G88" s="13" t="inlineStr">
         <is>
-          <t>131.0 [130.8, 131.1]</t>
+          <t>343.4</t>
         </is>
       </c>
       <c r="H88" s="13" t="inlineStr">
         <is>
-          <t>0.718 [0.707, 0.728]</t>
+          <t>0.647</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>computed-from-rates</t>
         </is>
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>Table (avg rate)</t>
+          <t>Table 1 (women 50+)</t>
         </is>
       </c>
       <c r="K88" s="15" t="inlineStr"/>
@@ -16997,17 +17045,17 @@
     <row r="89">
       <c r="A89" s="13" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>485</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>Xie2022_USCS</t>
+          <t>Harper2009_SEER</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D89" s="13" t="inlineStr">
@@ -17017,32 +17065,32 @@
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>age-ge50</t>
         </is>
       </c>
       <c r="F89" s="13" t="inlineStr">
         <is>
-          <t>90.9 [90.4, 91.4]</t>
+          <t>226.8</t>
         </is>
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>131.0 [130.8, 131.1]</t>
+          <t>343.4</t>
         </is>
       </c>
       <c r="H89" s="13" t="inlineStr">
         <is>
-          <t>0.694 [0.690, 0.698]</t>
+          <t>0.660</t>
         </is>
       </c>
       <c r="I89" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>computed-from-rates</t>
         </is>
       </c>
       <c r="J89" s="14" t="inlineStr">
         <is>
-          <t>Table (avg rate)</t>
+          <t>Table 1 (women 50+)</t>
         </is>
       </c>
       <c r="K89" s="15" t="inlineStr"/>
@@ -17052,22 +17100,22 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>Xie2022_USCS</t>
+          <t>Hendrick2021_SEER9</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>White (NH)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
@@ -17075,29 +17123,21 @@
           <t>aggregate-vs-NHW</t>
         </is>
       </c>
-      <c r="F90" s="13" t="inlineStr">
-        <is>
-          <t>93.0 [92.7, 93.4]</t>
-        </is>
-      </c>
-      <c r="G90" s="13" t="inlineStr">
-        <is>
-          <t>131.0 [130.8, 131.1]</t>
-        </is>
-      </c>
+      <c r="F90" s="13" t="inlineStr"/>
+      <c r="G90" s="13" t="inlineStr"/>
       <c r="H90" s="13" t="inlineStr">
         <is>
-          <t>0.710 [0.707, 0.713]</t>
+          <t>0.97 [0.95, 1.0]</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>Table (avg rate)</t>
+          <t>Table (women 40-75)</t>
         </is>
       </c>
       <c r="K90" s="15" t="inlineStr"/>
@@ -17107,52 +17147,44 @@
     <row r="91">
       <c r="A91" s="13" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>Lund2010_AtlantaSEER</t>
+          <t>Hendrick2021_SEER9</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D91" s="13" t="inlineStr">
         <is>
-          <t>White (NH)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2neg</t>
-        </is>
-      </c>
-      <c r="F91" s="13" t="inlineStr">
-        <is>
-          <t>86.7</t>
-        </is>
-      </c>
-      <c r="G91" s="13" t="inlineStr">
-        <is>
-          <t>110.7</t>
-        </is>
-      </c>
+          <t>aggregate-vs-NHW</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="inlineStr"/>
+      <c r="G91" s="13" t="inlineStr"/>
       <c r="H91" s="13" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.92 [0.9, 0.95]</t>
         </is>
       </c>
       <c r="I91" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J91" s="14" t="inlineStr">
         <is>
-          <t>Discussion text</t>
+          <t>Table (women 40-75)</t>
         </is>
       </c>
       <c r="K91" s="15" t="inlineStr"/>
@@ -17162,52 +17194,44 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>Lund2010_AtlantaSEER</t>
+          <t>Hendrick2021_SEER9</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>White (NH)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
-        </is>
-      </c>
-      <c r="F92" s="13" t="inlineStr">
-        <is>
-          <t>36.3</t>
-        </is>
-      </c>
-      <c r="G92" s="13" t="inlineStr">
-        <is>
-          <t>19.4</t>
-        </is>
-      </c>
+          <t>aggregate-vs-NHW</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="inlineStr"/>
+      <c r="G92" s="13" t="inlineStr"/>
       <c r="H92" s="13" t="inlineStr">
         <is>
-          <t>1.871</t>
+          <t>0.58 [0.52, 0.65]</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>Discussion text</t>
+          <t>Table (women 40-75)</t>
         </is>
       </c>
       <c r="K92" s="15" t="inlineStr"/>
@@ -17217,52 +17241,44 @@
     <row r="93">
       <c r="A93" s="13" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>66</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>Harper2009_SEER</t>
+          <t>Hendrick2021_SEER9</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D93" s="13" t="inlineStr">
         <is>
-          <t>White (NH)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>age-ge50</t>
-        </is>
-      </c>
-      <c r="F93" s="13" t="inlineStr">
-        <is>
-          <t>313.7</t>
-        </is>
-      </c>
-      <c r="G93" s="13" t="inlineStr">
-        <is>
-          <t>343.4</t>
-        </is>
-      </c>
+          <t>aggregate-vs-NHW</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="inlineStr"/>
+      <c r="G93" s="13" t="inlineStr"/>
       <c r="H93" s="13" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>0.75 [0.73, 0.76]</t>
         </is>
       </c>
       <c r="I93" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J93" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (women 50+)</t>
+          <t>Table (women 40-75)</t>
         </is>
       </c>
       <c r="K93" s="15" t="inlineStr"/>
@@ -17272,52 +17288,52 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>Harper2009_SEER</t>
+          <t>Howlader2014_SEER18</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>White (NH)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr">
         <is>
-          <t>age-ge50</t>
+          <t>subtype-HRpos-HER2neg</t>
         </is>
       </c>
       <c r="F94" s="13" t="inlineStr">
         <is>
-          <t>226.2</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
-          <t>343.4</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="H94" s="13" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>0.739 [0.712, 0.768]</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (women 50+)</t>
+          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
         </is>
       </c>
       <c r="K94" s="15" t="inlineStr"/>
@@ -17327,52 +17343,52 @@
     <row r="95">
       <c r="A95" s="13" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>Harper2009_SEER</t>
+          <t>Howlader2014_SEER18</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D95" s="13" t="inlineStr">
         <is>
-          <t>White (NH)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>age-ge50</t>
+          <t>subtype-HRpos-HER2neg</t>
         </is>
       </c>
       <c r="F95" s="13" t="inlineStr">
         <is>
-          <t>222.1</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
-          <t>343.4</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="H95" s="13" t="inlineStr">
         <is>
-          <t>0.647</t>
+          <t>0.689 [0.662, 0.717]</t>
         </is>
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J95" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (women 50+)</t>
+          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
         </is>
       </c>
       <c r="K95" s="15" t="inlineStr"/>
@@ -17382,12 +17398,12 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>Harper2009_SEER</t>
+          <t>Howlader2014_SEER18</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
@@ -17397,37 +17413,37 @@
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>White (NH)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>age-ge50</t>
+          <t>subtype-HRpos-HER2neg</t>
         </is>
       </c>
       <c r="F96" s="13" t="inlineStr">
         <is>
-          <t>226.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>343.4</t>
+          <t>126.7</t>
         </is>
       </c>
       <c r="H96" s="13" t="inlineStr">
         <is>
-          <t>0.660</t>
+          <t>0.604 [0.581, 0.627]</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (women 50+)</t>
+          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
         </is>
       </c>
       <c r="K96" s="15" t="inlineStr"/>
@@ -17437,12 +17453,12 @@
     <row r="97">
       <c r="A97" s="13" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>Hendrick2021_SEER9</t>
+          <t>Howlader2014_SEER18</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
@@ -17457,24 +17473,32 @@
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
-        </is>
-      </c>
-      <c r="F97" s="13" t="inlineStr"/>
-      <c r="G97" s="13" t="inlineStr"/>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="inlineStr">
+        <is>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
       <c r="H97" s="13" t="inlineStr">
         <is>
-          <t>0.97 [0.95, 1.0]</t>
+          <t>1.817 [1.697, 1.946]</t>
         </is>
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J97" s="14" t="inlineStr">
         <is>
-          <t>Table (women 40-75)</t>
+          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
         </is>
       </c>
       <c r="K97" s="15" t="inlineStr"/>
@@ -17484,12 +17508,12 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>Hendrick2021_SEER9</t>
+          <t>Howlader2014_SEER18</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -17504,24 +17528,32 @@
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
-        </is>
-      </c>
-      <c r="F98" s="13" t="inlineStr"/>
-      <c r="G98" s="13" t="inlineStr"/>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="G98" s="13" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
       <c r="H98" s="13" t="inlineStr">
         <is>
-          <t>0.92 [0.9, 0.95]</t>
+          <t>0.640 [0.572, 0.716]</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>Table (women 40-75)</t>
+          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
         </is>
       </c>
       <c r="K98" s="15" t="inlineStr"/>
@@ -17531,17 +17563,17 @@
     <row r="99">
       <c r="A99" s="13" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>Hendrick2021_SEER9</t>
+          <t>Howlader2014_SEER18</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D99" s="13" t="inlineStr">
@@ -17551,24 +17583,32 @@
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
-        </is>
-      </c>
-      <c r="F99" s="13" t="inlineStr"/>
-      <c r="G99" s="13" t="inlineStr"/>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="G99" s="13" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
+      </c>
       <c r="H99" s="13" t="inlineStr">
         <is>
-          <t>0.58 [0.52, 0.65]</t>
+          <t>0.824 [0.756, 0.897]</t>
         </is>
       </c>
       <c r="I99" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J99" s="14" t="inlineStr">
         <is>
-          <t>Table (women 40-75)</t>
+          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
         </is>
       </c>
       <c r="K99" s="15" t="inlineStr"/>
@@ -17578,17 +17618,17 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>Hendrick2021_SEER9</t>
+          <t>Howlader2014_SEER18</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D100" s="13" t="inlineStr">
@@ -17598,24 +17638,32 @@
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
-        </is>
-      </c>
-      <c r="F100" s="13" t="inlineStr"/>
-      <c r="G100" s="13" t="inlineStr"/>
+          <t>subtype-HRpos-HER2pos</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="inlineStr">
+        <is>
+          <t>17.2</t>
+        </is>
+      </c>
+      <c r="G100" s="13" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
       <c r="H100" s="13" t="inlineStr">
         <is>
-          <t>0.75 [0.73, 0.76]</t>
+          <t>1.004 [0.916, 1.101]</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>Table (women 40-75)</t>
+          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
         </is>
       </c>
       <c r="K100" s="15" t="inlineStr"/>
@@ -17635,7 +17683,7 @@
       </c>
       <c r="C101" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D101" s="13" t="inlineStr">
@@ -17645,22 +17693,22 @@
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2neg</t>
+          <t>subtype-HRpos-HER2pos</t>
         </is>
       </c>
       <c r="F101" s="13" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="H101" s="13" t="inlineStr">
         <is>
-          <t>0.739 [0.712, 0.768]</t>
+          <t>0.850 [0.768, 0.941]</t>
         </is>
       </c>
       <c r="I101" s="14" t="inlineStr">
@@ -17690,7 +17738,7 @@
       </c>
       <c r="C102" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D102" s="13" t="inlineStr">
@@ -17700,22 +17748,22 @@
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2neg</t>
+          <t>subtype-HRpos-HER2pos</t>
         </is>
       </c>
       <c r="F102" s="13" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>126.7</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="H102" s="13" t="inlineStr">
         <is>
-          <t>0.689 [0.662, 0.717]</t>
+          <t>0.687 [0.625, 0.756]</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
@@ -17735,17 +17783,17 @@
     <row r="103">
       <c r="A103" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>Howlader2014_SEER18</t>
+          <t>Kong2020_SEER18</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D103" s="13" t="inlineStr">
@@ -17755,32 +17803,24 @@
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2neg</t>
-        </is>
-      </c>
-      <c r="F103" s="13" t="inlineStr">
-        <is>
-          <t>76.4</t>
-        </is>
-      </c>
-      <c r="G103" s="13" t="inlineStr">
-        <is>
-          <t>126.7</t>
-        </is>
-      </c>
+          <t>subtype-HRpos-HER2pos</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="inlineStr"/>
+      <c r="G103" s="13" t="inlineStr"/>
       <c r="H103" s="13" t="inlineStr">
         <is>
-          <t>0.604 [0.581, 0.627]</t>
+          <t>1.12 [1.08, 1.16]</t>
         </is>
       </c>
       <c r="I103" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J103" s="14" t="inlineStr">
         <is>
-          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K103" s="15" t="inlineStr"/>
@@ -17790,12 +17830,12 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>Howlader2014_SEER18</t>
+          <t>Kong2020_SEER18</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
@@ -17810,32 +17850,24 @@
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
-        </is>
-      </c>
-      <c r="F104" s="13" t="inlineStr">
-        <is>
-          <t>33.3</t>
-        </is>
-      </c>
-      <c r="G104" s="13" t="inlineStr">
-        <is>
-          <t>18.3</t>
-        </is>
-      </c>
+          <t>subtype-HRneg-HER2pos</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="inlineStr"/>
+      <c r="G104" s="13" t="inlineStr"/>
       <c r="H104" s="13" t="inlineStr">
         <is>
-          <t>1.817 [1.697, 1.946]</t>
+          <t>1.46 [1.38, 1.54]</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K104" s="15" t="inlineStr"/>
@@ -17845,17 +17877,17 @@
     <row r="105">
       <c r="A105" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>Howlader2014_SEER18</t>
+          <t>Kong2020_SEER18</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D105" s="13" t="inlineStr">
@@ -17868,29 +17900,21 @@
           <t>subtype-TNBC</t>
         </is>
       </c>
-      <c r="F105" s="13" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="G105" s="13" t="inlineStr">
-        <is>
-          <t>18.3</t>
-        </is>
-      </c>
+      <c r="F105" s="13" t="inlineStr"/>
+      <c r="G105" s="13" t="inlineStr"/>
       <c r="H105" s="13" t="inlineStr">
         <is>
-          <t>0.640 [0.572, 0.716]</t>
+          <t>2.07 [2.01, 2.14]</t>
         </is>
       </c>
       <c r="I105" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J105" s="14" t="inlineStr">
         <is>
-          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K105" s="15" t="inlineStr"/>
@@ -17900,17 +17924,17 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>Howlader2014_SEER18</t>
+          <t>Kong2020_SEER18</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D106" s="13" t="inlineStr">
@@ -17920,32 +17944,24 @@
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
-        </is>
-      </c>
-      <c r="F106" s="13" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
-      </c>
-      <c r="G106" s="13" t="inlineStr">
-        <is>
-          <t>18.3</t>
-        </is>
-      </c>
+          <t>subtype-HRpos-HER2neg</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="inlineStr"/>
+      <c r="G106" s="13" t="inlineStr"/>
       <c r="H106" s="13" t="inlineStr">
         <is>
-          <t>0.824 [0.756, 0.897]</t>
+          <t>0.86 [0.84, 0.87]</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J106" s="14" t="inlineStr">
         <is>
-          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K106" s="15" t="inlineStr"/>
@@ -17955,17 +17971,17 @@
     <row r="107">
       <c r="A107" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>Howlader2014_SEER18</t>
+          <t>Kong2020_SEER18</t>
         </is>
       </c>
       <c r="C107" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D107" s="13" t="inlineStr">
@@ -17975,32 +17991,24 @@
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2pos</t>
-        </is>
-      </c>
-      <c r="F107" s="13" t="inlineStr">
-        <is>
-          <t>17.2</t>
-        </is>
-      </c>
-      <c r="G107" s="13" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
+          <t>subtype-HRneg-HER2pos</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="inlineStr"/>
+      <c r="G107" s="13" t="inlineStr"/>
       <c r="H107" s="13" t="inlineStr">
         <is>
-          <t>1.004 [0.916, 1.101]</t>
+          <t>1.41 [1.33, 1.49]</t>
         </is>
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J107" s="14" t="inlineStr">
         <is>
-          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K107" s="15" t="inlineStr"/>
@@ -18010,12 +18018,12 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>Howlader2014_SEER18</t>
+          <t>Kong2020_SEER18</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
@@ -18030,32 +18038,24 @@
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2pos</t>
-        </is>
-      </c>
-      <c r="F108" s="13" t="inlineStr">
-        <is>
-          <t>14.3</t>
-        </is>
-      </c>
-      <c r="G108" s="13" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
+          <t>subtype-HRpos-HER2neg</t>
+        </is>
+      </c>
+      <c r="F108" s="13" t="inlineStr"/>
+      <c r="G108" s="13" t="inlineStr"/>
       <c r="H108" s="13" t="inlineStr">
         <is>
-          <t>0.850 [0.768, 0.941]</t>
+          <t>0.87 [0.85, 0.88]</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K108" s="15" t="inlineStr"/>
@@ -18065,17 +18065,17 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>286</t>
         </is>
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>Howlader2014_SEER18</t>
+          <t>Kong2020_SEER18</t>
         </is>
       </c>
       <c r="C109" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D109" s="13" t="inlineStr">
@@ -18085,32 +18085,24 @@
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2pos</t>
-        </is>
-      </c>
-      <c r="F109" s="13" t="inlineStr">
-        <is>
-          <t>11.8</t>
-        </is>
-      </c>
-      <c r="G109" s="13" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="inlineStr"/>
+      <c r="G109" s="13" t="inlineStr"/>
       <c r="H109" s="13" t="inlineStr">
         <is>
-          <t>0.687 [0.625, 0.756]</t>
+          <t>0.79 [0.75, 0.83]</t>
         </is>
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J109" s="14" t="inlineStr">
         <is>
-          <t>Suppl Table 3 (age-std by me from age-specific rates, 2000 US std)</t>
+          <t>Results text</t>
         </is>
       </c>
       <c r="K109" s="15" t="inlineStr"/>
@@ -18130,7 +18122,7 @@
       </c>
       <c r="C110" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D110" s="13" t="inlineStr">
@@ -18140,14 +18132,14 @@
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2pos</t>
+          <t>subtype-HRpos-HER2neg</t>
         </is>
       </c>
       <c r="F110" s="13" t="inlineStr"/>
       <c r="G110" s="13" t="inlineStr"/>
       <c r="H110" s="13" t="inlineStr">
         <is>
-          <t>1.12 [1.08, 1.16]</t>
+          <t>0.78 [0.76, 0.79]</t>
         </is>
       </c>
       <c r="I110" s="14" t="inlineStr">
@@ -18177,7 +18169,7 @@
       </c>
       <c r="C111" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D111" s="13" t="inlineStr">
@@ -18187,14 +18179,14 @@
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRneg-HER2pos</t>
+          <t>subtype-HRpos-HER2pos</t>
         </is>
       </c>
       <c r="F111" s="13" t="inlineStr"/>
       <c r="G111" s="13" t="inlineStr"/>
       <c r="H111" s="13" t="inlineStr">
         <is>
-          <t>1.46 [1.38, 1.54]</t>
+          <t>0.91 [0.88, 0.94]</t>
         </is>
       </c>
       <c r="I111" s="14" t="inlineStr">
@@ -18224,7 +18216,7 @@
       </c>
       <c r="C112" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D112" s="13" t="inlineStr">
@@ -18241,7 +18233,7 @@
       <c r="G112" s="13" t="inlineStr"/>
       <c r="H112" s="13" t="inlineStr">
         <is>
-          <t>2.07 [2.01, 2.14]</t>
+          <t>0.94 [0.91, 0.98]</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
@@ -18261,17 +18253,17 @@
     <row r="113">
       <c r="A113" s="13" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>Kong2020_SEER18</t>
+          <t>Liu2012_LACounty</t>
         </is>
       </c>
       <c r="C113" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="D113" s="13" t="inlineStr">
@@ -18281,24 +18273,32 @@
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2neg</t>
-        </is>
-      </c>
-      <c r="F113" s="13" t="inlineStr"/>
-      <c r="G113" s="13" t="inlineStr"/>
+          <t>disaggregated-AANHPI</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="inlineStr">
+        <is>
+          <t>83.9</t>
+        </is>
+      </c>
+      <c r="G113" s="13" t="inlineStr">
+        <is>
+          <t>145.8</t>
+        </is>
+      </c>
       <c r="H113" s="13" t="inlineStr">
         <is>
-          <t>0.86 [0.84, 0.87]</t>
+          <t>0.575</t>
         </is>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>directly-reported-rate</t>
         </is>
       </c>
       <c r="J113" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>text (overall AAIR 2007)</t>
         </is>
       </c>
       <c r="K113" s="15" t="inlineStr"/>
@@ -18308,17 +18308,17 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>Kong2020_SEER18</t>
+          <t>Liu2012_LACounty</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>Korean</t>
         </is>
       </c>
       <c r="D114" s="13" t="inlineStr">
@@ -18328,24 +18328,32 @@
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRneg-HER2pos</t>
-        </is>
-      </c>
-      <c r="F114" s="13" t="inlineStr"/>
-      <c r="G114" s="13" t="inlineStr"/>
+          <t>disaggregated-AANHPI</t>
+        </is>
+      </c>
+      <c r="F114" s="13" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="G114" s="13" t="inlineStr">
+        <is>
+          <t>145.8</t>
+        </is>
+      </c>
       <c r="H114" s="13" t="inlineStr">
         <is>
-          <t>1.41 [1.33, 1.49]</t>
+          <t>0.558</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>directly-reported-rate</t>
         </is>
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>text (overall AAIR 2007)</t>
         </is>
       </c>
       <c r="K114" s="15" t="inlineStr"/>
@@ -18355,17 +18363,17 @@
     <row r="115">
       <c r="A115" s="13" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>Kong2020_SEER18</t>
+          <t>Liu2012_LACounty</t>
         </is>
       </c>
       <c r="C115" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D115" s="13" t="inlineStr">
@@ -18375,24 +18383,32 @@
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2neg</t>
-        </is>
-      </c>
-      <c r="F115" s="13" t="inlineStr"/>
-      <c r="G115" s="13" t="inlineStr"/>
+          <t>aggregate-vs-NHW</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="inlineStr">
+        <is>
+          <t>125.2</t>
+        </is>
+      </c>
+      <c r="G115" s="13" t="inlineStr">
+        <is>
+          <t>145.8</t>
+        </is>
+      </c>
       <c r="H115" s="13" t="inlineStr">
         <is>
-          <t>0.87 [0.85, 0.88]</t>
+          <t>0.859</t>
         </is>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>directly-reported-rate</t>
         </is>
       </c>
       <c r="J115" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>text (overall AAIR 2007)</t>
         </is>
       </c>
       <c r="K115" s="15" t="inlineStr"/>
@@ -18402,17 +18418,17 @@
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>Kong2020_SEER18</t>
+          <t>Liu2012_LACounty</t>
         </is>
       </c>
       <c r="C116" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D116" s="13" t="inlineStr">
@@ -18422,24 +18438,32 @@
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
-        </is>
-      </c>
-      <c r="F116" s="13" t="inlineStr"/>
-      <c r="G116" s="13" t="inlineStr"/>
+          <t>aggregate-vs-NHW</t>
+        </is>
+      </c>
+      <c r="F116" s="13" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="G116" s="13" t="inlineStr">
+        <is>
+          <t>145.8</t>
+        </is>
+      </c>
       <c r="H116" s="13" t="inlineStr">
         <is>
-          <t>0.79 [0.75, 0.83]</t>
+          <t>0.532</t>
         </is>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>directly-reported-rate</t>
         </is>
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>text (overall AAIR 2007)</t>
         </is>
       </c>
       <c r="K116" s="15" t="inlineStr"/>
@@ -18449,34 +18473,42 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
-          <t>Kong2020_SEER18</t>
+          <t>Zhang2025_USCS_female</t>
         </is>
       </c>
       <c r="C117" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D117" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White (NH)</t>
         </is>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2neg</t>
-        </is>
-      </c>
-      <c r="F117" s="13" t="inlineStr"/>
-      <c r="G117" s="13" t="inlineStr"/>
+          <t>aggregate-vs-NHW</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="inlineStr">
+        <is>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="G117" s="13" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="H117" s="13" t="inlineStr">
         <is>
-          <t>0.78 [0.76, 0.79]</t>
+          <t>0.93 [0.92, 0.94]</t>
         </is>
       </c>
       <c r="I117" s="14" t="inlineStr">
@@ -18486,7 +18518,7 @@
       </c>
       <c r="J117" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Table (breast, rate ratio)</t>
         </is>
       </c>
       <c r="K117" s="15" t="inlineStr"/>
@@ -18496,34 +18528,42 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>Kong2020_SEER18</t>
+          <t>Zhang2025_USCS_female</t>
         </is>
       </c>
       <c r="C118" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White (NH)</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos-HER2pos</t>
-        </is>
-      </c>
-      <c r="F118" s="13" t="inlineStr"/>
-      <c r="G118" s="13" t="inlineStr"/>
+          <t>aggregate-vs-NHW</t>
+        </is>
+      </c>
+      <c r="F118" s="13" t="inlineStr">
+        <is>
+          <t>110.3</t>
+        </is>
+      </c>
+      <c r="G118" s="13" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="H118" s="13" t="inlineStr">
         <is>
-          <t>0.91 [0.88, 0.94]</t>
+          <t>0.79 [0.79, 0.8]</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr">
@@ -18533,7 +18573,7 @@
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Table (breast, rate ratio)</t>
         </is>
       </c>
       <c r="K118" s="15" t="inlineStr"/>
@@ -18543,34 +18583,42 @@
     <row r="119">
       <c r="A119" s="13" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B119" s="14" t="inlineStr">
         <is>
-          <t>Kong2020_SEER18</t>
+          <t>Zhang2025_USCS_female</t>
         </is>
       </c>
       <c r="C119" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="D119" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White (NH)</t>
         </is>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
-        </is>
-      </c>
-      <c r="F119" s="13" t="inlineStr"/>
-      <c r="G119" s="13" t="inlineStr"/>
+          <t>aggregate-vs-NHW</t>
+        </is>
+      </c>
+      <c r="F119" s="13" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="G119" s="13" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
       <c r="H119" s="13" t="inlineStr">
         <is>
-          <t>0.94 [0.91, 0.98]</t>
+          <t>0.81 [0.77, 0.85]</t>
         </is>
       </c>
       <c r="I119" s="14" t="inlineStr">
@@ -18580,7 +18628,7 @@
       </c>
       <c r="J119" s="14" t="inlineStr">
         <is>
-          <t>Results text</t>
+          <t>Table (breast, rate ratio)</t>
         </is>
       </c>
       <c r="K119" s="15" t="inlineStr"/>
@@ -18590,52 +18638,52 @@
     <row r="120">
       <c r="A120" s="13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>Liu2012_LACounty</t>
+          <t>Zhang2025_USCS_female</t>
         </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
         <is>
-          <t>Chinese</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D120" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White (NH)</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>disaggregated-AANHPI</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F120" s="13" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>101.2</t>
         </is>
       </c>
       <c r="G120" s="13" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="H120" s="13" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>0.73 [0.72, 0.73]</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-rate</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>text (overall AAIR 2007)</t>
+          <t>Table (breast, rate ratio)</t>
         </is>
       </c>
       <c r="K120" s="15" t="inlineStr"/>
@@ -18645,52 +18693,52 @@
     <row r="121">
       <c r="A121" s="13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B121" s="14" t="inlineStr">
         <is>
-          <t>Liu2012_LACounty</t>
+          <t>Gleason2012_SEER</t>
         </is>
       </c>
       <c r="C121" s="13" t="inlineStr">
         <is>
-          <t>Korean</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D121" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>disaggregated-AANHPI</t>
+          <t>subtype-HRpos</t>
         </is>
       </c>
       <c r="F121" s="13" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>1026.9</t>
         </is>
       </c>
       <c r="G121" s="13" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>1460.1</t>
         </is>
       </c>
       <c r="H121" s="13" t="inlineStr">
         <is>
-          <t>0.558</t>
+          <t>0.703 [0.685, 0.722]</t>
         </is>
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-rate</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J121" s="14" t="inlineStr">
         <is>
-          <t>text (overall AAIR 2007)</t>
+          <t>Table 1 (cumulative incidence CIR)</t>
         </is>
       </c>
       <c r="K121" s="15" t="inlineStr"/>
@@ -18700,12 +18748,12 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>Liu2012_LACounty</t>
+          <t>Gleason2012_SEER</t>
         </is>
       </c>
       <c r="C122" s="13" t="inlineStr">
@@ -18715,37 +18763,37 @@
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>subtype-HRneg</t>
         </is>
       </c>
       <c r="F122" s="13" t="inlineStr">
         <is>
-          <t>125.2</t>
+          <t>625.9</t>
         </is>
       </c>
       <c r="G122" s="13" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>391.3</t>
         </is>
       </c>
       <c r="H122" s="13" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>1.600 [1.548, 1.652]</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-rate</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>text (overall AAIR 2007)</t>
+          <t>Table 1 (cumulative incidence CIR)</t>
         </is>
       </c>
       <c r="K122" s="15" t="inlineStr"/>
@@ -18755,52 +18803,52 @@
     <row r="123">
       <c r="A123" s="13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B123" s="14" t="inlineStr">
         <is>
-          <t>Liu2012_LACounty</t>
+          <t>Gleason2012_SEER</t>
         </is>
       </c>
       <c r="C123" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D123" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>subtype-ERpos-PRneg</t>
         </is>
       </c>
       <c r="F123" s="13" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>271.2</t>
         </is>
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
-          <t>145.8</t>
+          <t>278.3</t>
         </is>
       </c>
       <c r="H123" s="13" t="inlineStr">
         <is>
-          <t>0.532</t>
+          <t>0.974 [0.925, 1.027]</t>
         </is>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-rate</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J123" s="14" t="inlineStr">
         <is>
-          <t>text (overall AAIR 2007)</t>
+          <t>Table 1 (cumulative incidence CIR)</t>
         </is>
       </c>
       <c r="K123" s="15" t="inlineStr"/>
@@ -18810,12 +18858,12 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>200</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>Zhang2025_USCS_female</t>
+          <t>Gleason2012_SEER</t>
         </is>
       </c>
       <c r="C124" s="13" t="inlineStr">
@@ -18825,37 +18873,37 @@
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>White (NH)</t>
+          <t>White</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>subtype-ERneg-PRpos</t>
         </is>
       </c>
       <c r="F124" s="13" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="H124" s="13" t="inlineStr">
         <is>
-          <t>0.93 [0.92, 0.94]</t>
+          <t>1.459 [1.267, 1.679]</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>Table (breast, rate ratio)</t>
+          <t>Table 1 (cumulative incidence CIR)</t>
         </is>
       </c>
       <c r="K124" s="15" t="inlineStr"/>
@@ -18865,42 +18913,38 @@
     <row r="125">
       <c r="A125" s="13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="B125" s="14" t="inlineStr">
         <is>
-          <t>Zhang2025_USCS_female</t>
+          <t>Yazzie2025_Navajo</t>
         </is>
       </c>
       <c r="C125" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>AIAN (Navajo)</t>
         </is>
       </c>
       <c r="D125" s="13" t="inlineStr">
         <is>
-          <t>White (NH)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="F125" s="13" t="inlineStr">
         <is>
-          <t>110.3</t>
-        </is>
-      </c>
-      <c r="G125" s="13" t="inlineStr">
-        <is>
-          <t>139.0</t>
-        </is>
-      </c>
+          <t>60.9</t>
+        </is>
+      </c>
+      <c r="G125" s="13" t="inlineStr"/>
       <c r="H125" s="13" t="inlineStr">
         <is>
-          <t>0.79 [0.79, 0.8]</t>
+          <t>0.49 [0.44, 0.55]</t>
         </is>
       </c>
       <c r="I125" s="14" t="inlineStr">
@@ -18910,7 +18954,7 @@
       </c>
       <c r="J125" s="14" t="inlineStr">
         <is>
-          <t>Table (breast, rate ratio)</t>
+          <t>Table (Navajo vs NHW)</t>
         </is>
       </c>
       <c r="K125" s="15" t="inlineStr"/>
@@ -18920,22 +18964,22 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t>Zhang2025_USCS_female</t>
+          <t>Ellington2022_USCS</t>
         </is>
       </c>
       <c r="C126" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D126" s="13" t="inlineStr">
         <is>
-          <t>White (NH)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
@@ -18945,27 +18989,27 @@
       </c>
       <c r="F126" s="13" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="H126" s="13" t="inlineStr">
         <is>
-          <t>0.81 [0.77, 0.85]</t>
+          <t>0.933 [0.920, 0.946]</t>
         </is>
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-Poisson-SE</t>
         </is>
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>Table (breast, rate ratio)</t>
+          <t>MMWR Table (women &gt;=20)</t>
         </is>
       </c>
       <c r="K126" s="15" t="inlineStr"/>
@@ -18975,12 +19019,12 @@
     <row r="127">
       <c r="A127" s="13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B127" s="14" t="inlineStr">
         <is>
-          <t>Zhang2025_USCS_female</t>
+          <t>Ellington2022_USCS</t>
         </is>
       </c>
       <c r="C127" s="13" t="inlineStr">
@@ -18990,7 +19034,7 @@
       </c>
       <c r="D127" s="13" t="inlineStr">
         <is>
-          <t>White (NH)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
@@ -19000,27 +19044,27 @@
       </c>
       <c r="F127" s="13" t="inlineStr">
         <is>
-          <t>101.2</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="G127" s="13" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="H127" s="13" t="inlineStr">
         <is>
-          <t>0.73 [0.72, 0.73]</t>
+          <t>0.718 [0.707, 0.731]</t>
         </is>
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-Poisson-SE</t>
         </is>
       </c>
       <c r="J127" s="14" t="inlineStr">
         <is>
-          <t>Table (breast, rate ratio)</t>
+          <t>MMWR Table (women &gt;=20)</t>
         </is>
       </c>
       <c r="K127" s="15" t="inlineStr"/>
@@ -19030,52 +19074,52 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>Gleason2012_SEER</t>
+          <t>Ellington2022_USCS</t>
         </is>
       </c>
       <c r="C128" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRpos</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F128" s="13" t="inlineStr">
         <is>
-          <t>1026.9</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
-          <t>1460.1</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
         <is>
-          <t>0.703 [0.685, 0.722]</t>
+          <t>0.769 [0.752, 0.788]</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>computed-from-rates-Poisson-SE</t>
         </is>
       </c>
       <c r="J128" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (cumulative incidence CIR)</t>
+          <t>MMWR Table (women &gt;=20)</t>
         </is>
       </c>
       <c r="K128" s="15" t="inlineStr"/>
@@ -19085,52 +19129,52 @@
     <row r="129">
       <c r="A129" s="13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>169</t>
         </is>
       </c>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>Gleason2012_SEER</t>
+          <t>Ellington2022_USCS</t>
         </is>
       </c>
       <c r="C129" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="D129" s="13" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>subtype-HRneg</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F129" s="13" t="inlineStr">
         <is>
-          <t>625.9</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="G129" s="13" t="inlineStr">
         <is>
-          <t>391.3</t>
+          <t>186.5</t>
         </is>
       </c>
       <c r="H129" s="13" t="inlineStr">
         <is>
-          <t>1.600 [1.548, 1.652]</t>
+          <t>0.683 [0.642, 0.726]</t>
         </is>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>computed-from-rates-Poisson-SE</t>
         </is>
       </c>
       <c r="J129" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (cumulative incidence CIR)</t>
+          <t>MMWR Table (women &gt;=20)</t>
         </is>
       </c>
       <c r="K129" s="15" t="inlineStr"/>
@@ -19140,52 +19184,52 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>587</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>Gleason2012_SEER</t>
+          <t>Nasseri2009</t>
         </is>
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Middle Eastern</t>
         </is>
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>subtype-ERpos-PRneg</t>
+          <t>disaggregated-MENA</t>
         </is>
       </c>
       <c r="F130" s="13" t="inlineStr">
         <is>
-          <t>271.2</t>
+          <t>126.2</t>
         </is>
       </c>
       <c r="G130" s="13" t="inlineStr">
         <is>
-          <t>278.3</t>
+          <t>146.9</t>
         </is>
       </c>
       <c r="H130" s="13" t="inlineStr">
         <is>
-          <t>0.974 [0.925, 1.027]</t>
+          <t>0.86 [0.84, 0.88]</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-with-CI</t>
+          <t>directly-reported-IRR</t>
         </is>
       </c>
       <c r="J130" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (cumulative incidence CIR)</t>
+          <t>Abstract/Results (126.2/146.9)</t>
         </is>
       </c>
       <c r="K130" s="15" t="inlineStr"/>
@@ -19195,42 +19239,42 @@
     <row r="131">
       <c r="A131" s="13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B131" s="14" t="inlineStr">
         <is>
-          <t>Gleason2012_SEER</t>
+          <t>Nash2022</t>
         </is>
       </c>
       <c r="C131" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Alaska Native</t>
         </is>
       </c>
       <c r="D131" s="13" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>NHW (external SEER-Explorer)</t>
         </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>subtype-ERneg-PRpos</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="F131" s="13" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>130.8 [116.7, 146.0]</t>
         </is>
       </c>
       <c r="G131" s="13" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>137.4</t>
         </is>
       </c>
       <c r="H131" s="13" t="inlineStr">
         <is>
-          <t>1.459 [1.267, 1.679]</t>
+          <t>0.952 [0.851, 1.065]</t>
         </is>
       </c>
       <c r="I131" s="14" t="inlineStr">
@@ -19240,7 +19284,7 @@
       </c>
       <c r="J131" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (cumulative incidence CIR)</t>
+          <t>Table 1 (female breast, 340 cases IR 130.8)</t>
         </is>
       </c>
       <c r="K131" s="15" t="inlineStr"/>
@@ -19250,48 +19294,48 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>955</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>Yazzie2025_Navajo</t>
+          <t>Goggins2009</t>
         </is>
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>AIAN (Navajo)</t>
+          <t>Asian Indian/Pakistani</t>
         </is>
       </c>
       <c r="D132" s="13" t="inlineStr">
         <is>
-          <t>NHW</t>
+          <t>US White (SIR reference)</t>
         </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>disaggregated-AANHPI</t>
         </is>
       </c>
       <c r="F132" s="13" t="inlineStr">
         <is>
-          <t>60.9</t>
+          <t>59.52</t>
         </is>
       </c>
       <c r="G132" s="13" t="inlineStr"/>
       <c r="H132" s="13" t="inlineStr">
         <is>
-          <t>0.49 [0.44, 0.55]</t>
+          <t>0.61 [0.56, 0.66]</t>
         </is>
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>directly-reported-SIR</t>
         </is>
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>Table (Navajo vs NHW)</t>
+          <t>Table 1 (Breast female SIR 0.61)</t>
         </is>
       </c>
       <c r="K132" s="15" t="inlineStr"/>
@@ -19301,17 +19345,17 @@
     <row r="133">
       <c r="A133" s="13" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="B133" s="14" t="inlineStr">
         <is>
-          <t>Ellington2022_USCS</t>
+          <t>Wilkinson2002</t>
         </is>
       </c>
       <c r="C133" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Hispanic/Latina (aggregate)</t>
         </is>
       </c>
       <c r="D133" s="13" t="inlineStr">
@@ -19321,32 +19365,32 @@
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>Hispanic-origin</t>
         </is>
       </c>
       <c r="F133" s="13" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="G133" s="13" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>125.8</t>
         </is>
       </c>
       <c r="H133" s="13" t="inlineStr">
         <is>
-          <t>0.933 [0.920, 0.946]</t>
+          <t>0.651 [0.624, 0.679]</t>
         </is>
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-Poisson-SE</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J133" s="14" t="inlineStr">
         <is>
-          <t>MMWR Table (women &gt;=20)</t>
+          <t>Table 1 (breast invasive 1990-1998)</t>
         </is>
       </c>
       <c r="K133" s="15" t="inlineStr"/>
@@ -19356,17 +19400,17 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>Ellington2022_USCS</t>
+          <t>Mills2005</t>
         </is>
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Hmong</t>
         </is>
       </c>
       <c r="D134" s="13" t="inlineStr">
@@ -19376,22 +19420,22 @@
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>disaggregated-AANHPI</t>
         </is>
       </c>
       <c r="F134" s="13" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="G134" s="13" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="H134" s="13" t="inlineStr">
         <is>
-          <t>0.718 [0.707, 0.731]</t>
+          <t>0.164 [0.120, 0.224]</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
@@ -19401,7 +19445,7 @@
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>MMWR Table (women &gt;=20)</t>
+          <t>Table 2 (Breast female: Hmong 23.8 n=39, NHW 145.5)</t>
         </is>
       </c>
       <c r="K134" s="15" t="inlineStr"/>
@@ -19411,17 +19455,17 @@
     <row r="135">
       <c r="A135" s="13" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="B135" s="14" t="inlineStr">
         <is>
-          <t>Ellington2022_USCS</t>
+          <t>Kem2007</t>
         </is>
       </c>
       <c r="C135" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>Cambodian</t>
         </is>
       </c>
       <c r="D135" s="13" t="inlineStr">
@@ -19431,22 +19475,22 @@
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>disaggregated-AANHPI</t>
         </is>
       </c>
       <c r="F135" s="13" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="G135" s="13" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>155.5</t>
         </is>
       </c>
       <c r="H135" s="13" t="inlineStr">
         <is>
-          <t>0.769 [0.752, 0.788]</t>
+          <t>0.264 [0.204, 0.341]</t>
         </is>
       </c>
       <c r="I135" s="14" t="inlineStr">
@@ -19456,7 +19500,7 @@
       </c>
       <c r="J135" s="14" t="inlineStr">
         <is>
-          <t>MMWR Table (women &gt;=20)</t>
+          <t>Table 1 Women Breast (high rate 41.0, count 58, NHW 155.5, ratio 0.26)</t>
         </is>
       </c>
       <c r="K135" s="15" t="inlineStr"/>
@@ -19466,17 +19510,17 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>Ellington2022_USCS</t>
+          <t>Gomez2026_SEER21</t>
         </is>
       </c>
       <c r="C136" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D136" s="13" t="inlineStr">
@@ -19491,27 +19535,27 @@
       </c>
       <c r="F136" s="13" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>131.2 [130.1, 132.2]</t>
         </is>
       </c>
       <c r="G136" s="13" t="inlineStr">
         <is>
-          <t>186.5</t>
+          <t>139.5 [139.0, 140.0]</t>
         </is>
       </c>
       <c r="H136" s="13" t="inlineStr">
         <is>
-          <t>0.683 [0.642, 0.726]</t>
+          <t>0.941 [0.932, 0.949]</t>
         </is>
       </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-Poisson-SE</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>MMWR Table (women &gt;=20)</t>
+          <t>eTable3</t>
         </is>
       </c>
       <c r="K136" s="15" t="inlineStr"/>
@@ -19521,17 +19565,17 @@
     <row r="137">
       <c r="A137" s="13" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B137" s="14" t="inlineStr">
         <is>
-          <t>Nasseri2009</t>
+          <t>Gomez2026_SEER21</t>
         </is>
       </c>
       <c r="C137" s="13" t="inlineStr">
         <is>
-          <t>Middle Eastern</t>
+          <t>Hispanic</t>
         </is>
       </c>
       <c r="D137" s="13" t="inlineStr">
@@ -19541,32 +19585,32 @@
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>disaggregated-MENA</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F137" s="13" t="inlineStr">
         <is>
-          <t>126.2</t>
+          <t>104.0 [103.3, 104.7]</t>
         </is>
       </c>
       <c r="G137" s="13" t="inlineStr">
         <is>
-          <t>146.9</t>
+          <t>139.5 [139.0, 140.0]</t>
         </is>
       </c>
       <c r="H137" s="13" t="inlineStr">
         <is>
-          <t>0.86 [0.84, 0.88]</t>
+          <t>0.746 [0.74, 0.751]</t>
         </is>
       </c>
       <c r="I137" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-IRR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J137" s="14" t="inlineStr">
         <is>
-          <t>Abstract/Results (126.2/146.9)</t>
+          <t>eTable3</t>
         </is>
       </c>
       <c r="K137" s="15" t="inlineStr"/>
@@ -19576,42 +19620,42 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>Nash2022</t>
+          <t>Gomez2026_SEER21</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
         <is>
-          <t>Alaska Native</t>
+          <t>AIAN</t>
         </is>
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>NHW (external SEER-Explorer)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F138" s="13" t="inlineStr">
         <is>
-          <t>130.8 [116.7, 146.0]</t>
+          <t>98.7 [94.5, 103.1]</t>
         </is>
       </c>
       <c r="G138" s="13" t="inlineStr">
         <is>
-          <t>137.4</t>
+          <t>139.5 [139.0, 140.0]</t>
         </is>
       </c>
       <c r="H138" s="13" t="inlineStr">
         <is>
-          <t>0.952 [0.851, 1.065]</t>
+          <t>0.708 [0.677, 0.739]</t>
         </is>
       </c>
       <c r="I138" s="14" t="inlineStr">
@@ -19621,7 +19665,7 @@
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (female breast, 340 cases IR 130.8)</t>
+          <t>eTable3</t>
         </is>
       </c>
       <c r="K138" s="15" t="inlineStr"/>
@@ -19631,48 +19675,52 @@
     <row r="139">
       <c r="A139" s="13" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B139" s="14" t="inlineStr">
         <is>
-          <t>Goggins2009</t>
+          <t>Gomez2026_SEER21</t>
         </is>
       </c>
       <c r="C139" s="13" t="inlineStr">
         <is>
-          <t>Asian Indian/Pakistani</t>
+          <t>Asian/PI (aggregate)</t>
         </is>
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>US White (SIR reference)</t>
+          <t>NHW</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>disaggregated-AANHPI</t>
+          <t>aggregate-vs-NHW</t>
         </is>
       </c>
       <c r="F139" s="13" t="inlineStr">
         <is>
-          <t>59.52</t>
-        </is>
-      </c>
-      <c r="G139" s="13" t="inlineStr"/>
+          <t>112.9 [111.8, 113.9]</t>
+        </is>
+      </c>
+      <c r="G139" s="13" t="inlineStr">
+        <is>
+          <t>139.5 [139.0, 140.0]</t>
+        </is>
+      </c>
       <c r="H139" s="13" t="inlineStr">
         <is>
-          <t>0.61 [0.56, 0.66]</t>
+          <t>0.809 [0.801, 0.817]</t>
         </is>
       </c>
       <c r="I139" s="14" t="inlineStr">
         <is>
-          <t>directly-reported-SIR</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J139" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (Breast female SIR 0.61)</t>
+          <t>eTable3</t>
         </is>
       </c>
       <c r="K139" s="15" t="inlineStr"/>
@@ -19682,17 +19730,17 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>4333</t>
+          <t>234</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>Wilkinson2002</t>
+          <t>Gomez2026_SEER21</t>
         </is>
       </c>
       <c r="C140" s="13" t="inlineStr">
         <is>
-          <t>Hispanic/Latina (aggregate)</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="D140" s="13" t="inlineStr">
@@ -19702,22 +19750,22 @@
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Hispanic-origin</t>
+          <t>subtype-TNBC</t>
         </is>
       </c>
       <c r="F140" s="13" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>25.4 [25.0, 25.9]</t>
         </is>
       </c>
       <c r="G140" s="13" t="inlineStr">
         <is>
-          <t>125.8</t>
+          <t>12.7 [12.5, 12.8]</t>
         </is>
       </c>
       <c r="H140" s="13" t="inlineStr">
         <is>
-          <t>0.651 [0.624, 0.679]</t>
+          <t>2.0 [1.958, 2.043]</t>
         </is>
       </c>
       <c r="I140" s="14" t="inlineStr">
@@ -19727,7 +19775,7 @@
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>Table 1 (breast invasive 1990-1998)</t>
+          <t>eTable3 (TNBC row)</t>
         </is>
       </c>
       <c r="K140" s="15" t="inlineStr"/>
@@ -19737,17 +19785,17 @@
     <row r="141">
       <c r="A141" s="13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B141" s="14" t="inlineStr">
         <is>
-          <t>Mills2005</t>
+          <t>Gomez 2010</t>
         </is>
       </c>
       <c r="C141" s="13" t="inlineStr">
         <is>
-          <t>Hmong</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="D141" s="13" t="inlineStr">
@@ -19762,27 +19810,27 @@
       </c>
       <c r="F141" s="13" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>73.5 [71.6, 75.4]</t>
         </is>
       </c>
       <c r="G141" s="13" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>146.1 [145.5, 146.7]</t>
         </is>
       </c>
       <c r="H141" s="13" t="inlineStr">
         <is>
-          <t>0.164 [0.120, 0.224]</t>
+          <t>0.503 [0.490, 0.516]</t>
         </is>
       </c>
       <c r="I141" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-Poisson-SE</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J141" s="14" t="inlineStr">
         <is>
-          <t>Table 2 (Breast female: Hmong 23.8 n=39, NHW 145.5)</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="K141" s="15" t="inlineStr"/>
@@ -19792,17 +19840,17 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>Kem2007</t>
+          <t>Gomez 2010</t>
         </is>
       </c>
       <c r="C142" s="13" t="inlineStr">
         <is>
-          <t>Cambodian</t>
+          <t>Japanese</t>
         </is>
       </c>
       <c r="D142" s="13" t="inlineStr">
@@ -19817,27 +19865,27 @@
       </c>
       <c r="F142" s="13" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>102.5 [99.3, 105.9]</t>
         </is>
       </c>
       <c r="G142" s="13" t="inlineStr">
         <is>
-          <t>155.5</t>
+          <t>146.1 [145.5, 146.7]</t>
         </is>
       </c>
       <c r="H142" s="13" t="inlineStr">
         <is>
-          <t>0.264 [0.204, 0.341]</t>
+          <t>0.702 [0.679, 0.725]</t>
         </is>
       </c>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>computed-from-rates-Poisson-SE</t>
+          <t>computed-from-rates-with-CI</t>
         </is>
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>Table 1 Women Breast (high rate 41.0, count 58, NHW 155.5, ratio 0.26)</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="K142" s="15" t="inlineStr"/>
@@ -19847,17 +19895,17 @@
     <row r="143">
       <c r="A143" s="13" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B143" s="14" t="inlineStr">
         <is>
-          <t>Gomez2026_SEER21</t>
+          <t>Gomez 2010</t>
         </is>
       </c>
       <c r="C143" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Filipina</t>
         </is>
       </c>
       <c r="D143" s="13" t="inlineStr">
@@ -19867,22 +19915,22 @@
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>disaggregated-AANHPI</t>
         </is>
       </c>
       <c r="F143" s="13" t="inlineStr">
         <is>
-          <t>131.2 [130.1, 132.2]</t>
+          <t>100.4 [98.1, 102.8]</t>
         </is>
       </c>
       <c r="G143" s="13" t="inlineStr">
         <is>
-          <t>139.5 [139.0, 140.0]</t>
+          <t>146.1 [145.5, 146.7]</t>
         </is>
       </c>
       <c r="H143" s="13" t="inlineStr">
         <is>
-          <t>0.941 [0.932, 0.949]</t>
+          <t>0.687 [0.671, 0.704]</t>
         </is>
       </c>
       <c r="I143" s="14" t="inlineStr">
@@ -19892,7 +19940,7 @@
       </c>
       <c r="J143" s="14" t="inlineStr">
         <is>
-          <t>eTable3</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="K143" s="15" t="inlineStr"/>
@@ -19902,17 +19950,17 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>Gomez2026_SEER21</t>
+          <t>Gomez 2010</t>
         </is>
       </c>
       <c r="C144" s="13" t="inlineStr">
         <is>
-          <t>Hispanic</t>
+          <t>Korean</t>
         </is>
       </c>
       <c r="D144" s="13" t="inlineStr">
@@ -19922,22 +19970,22 @@
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>disaggregated-AANHPI</t>
         </is>
       </c>
       <c r="F144" s="13" t="inlineStr">
         <is>
-          <t>104.0 [103.3, 104.7]</t>
+          <t>46.3 [43.8, 49.0]</t>
         </is>
       </c>
       <c r="G144" s="13" t="inlineStr">
         <is>
-          <t>139.5 [139.0, 140.0]</t>
+          <t>146.1 [145.5, 146.7]</t>
         </is>
       </c>
       <c r="H144" s="13" t="inlineStr">
         <is>
-          <t>0.746 [0.74, 0.751]</t>
+          <t>0.317 [0.300, 0.335]</t>
         </is>
       </c>
       <c r="I144" s="14" t="inlineStr">
@@ -19947,7 +19995,7 @@
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>eTable3</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="K144" s="15" t="inlineStr"/>
@@ -19957,17 +20005,17 @@
     <row r="145">
       <c r="A145" s="13" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>236</t>
         </is>
       </c>
       <c r="B145" s="14" t="inlineStr">
         <is>
-          <t>Gomez2026_SEER21</t>
+          <t>Gomez 2010</t>
         </is>
       </c>
       <c r="C145" s="13" t="inlineStr">
         <is>
-          <t>AIAN</t>
+          <t>Vietnamese</t>
         </is>
       </c>
       <c r="D145" s="13" t="inlineStr">
@@ -19977,22 +20025,22 @@
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>disaggregated-AANHPI</t>
         </is>
       </c>
       <c r="F145" s="13" t="inlineStr">
         <is>
-          <t>98.7 [94.5, 103.1]</t>
+          <t>59.9 [56.7, 63.1]</t>
         </is>
       </c>
       <c r="G145" s="13" t="inlineStr">
         <is>
-          <t>139.5 [139.0, 140.0]</t>
+          <t>146.1 [145.5, 146.7]</t>
         </is>
       </c>
       <c r="H145" s="13" t="inlineStr">
         <is>
-          <t>0.708 [0.677, 0.739]</t>
+          <t>0.410 [0.389, 0.433]</t>
         </is>
       </c>
       <c r="I145" s="14" t="inlineStr">
@@ -20002,7 +20050,7 @@
       </c>
       <c r="J145" s="14" t="inlineStr">
         <is>
-          <t>eTable3</t>
+          <t>Table 1</t>
         </is>
       </c>
       <c r="K145" s="15" t="inlineStr"/>
@@ -20012,17 +20060,17 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>Gomez2026_SEER21</t>
+          <t>Jin 2016</t>
         </is>
       </c>
       <c r="C146" s="13" t="inlineStr">
         <is>
-          <t>Asian/PI (aggregate)</t>
+          <t>Chinese</t>
         </is>
       </c>
       <c r="D146" s="13" t="inlineStr">
@@ -20032,22 +20080,22 @@
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>aggregate-vs-NHW</t>
+          <t>disaggregated-AANHPI</t>
         </is>
       </c>
       <c r="F146" s="13" t="inlineStr">
         <is>
-          <t>112.9 [111.8, 113.9]</t>
+          <t>82.8 [80.1, 85.5]</t>
         </is>
       </c>
       <c r="G146" s="13" t="inlineStr">
         <is>
-          <t>139.5 [139.0, 140.0]</t>
+          <t>134.4 [133.8, 135.1]</t>
         </is>
       </c>
       <c r="H146" s="13" t="inlineStr">
         <is>
-          <t>0.809 [0.801, 0.817]</t>
+          <t>0.616 [0.596, 0.637]</t>
         </is>
       </c>
       <c r="I146" s="14" t="inlineStr">
@@ -20057,7 +20105,7 @@
       </c>
       <c r="J146" s="14" t="inlineStr">
         <is>
-          <t>eTable3</t>
+          <t>Table 4</t>
         </is>
       </c>
       <c r="K146" s="15" t="inlineStr"/>
@@ -20067,17 +20115,17 @@
     <row r="147">
       <c r="A147" s="13" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="B147" s="14" t="inlineStr">
         <is>
-          <t>Gomez2026_SEER21</t>
+          <t>Jin 2016</t>
         </is>
       </c>
       <c r="C147" s="13" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Filipina</t>
         </is>
       </c>
       <c r="D147" s="13" t="inlineStr">
@@ -20087,22 +20135,22 @@
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>subtype-TNBC</t>
+          <t>disaggregated-AANHPI</t>
         </is>
       </c>
       <c r="F147" s="13" t="inlineStr">
         <is>
-          <t>25.4 [25.0, 25.9]</t>
+          <t>111.3 [108.0, 114.7]</t>
         </is>
       </c>
       <c r="G147" s="13" t="inlineStr">
         <is>
-          <t>12.7 [12.5, 12.8]</t>
+          <t>134.4 [133.8, 135.1]</t>
         </is>
       </c>
       <c r="H147" s="13" t="inlineStr">
         <is>
-          <t>2.0 [1.958, 2.043]</t>
+          <t>0.828 [0.803, 0.854]</t>
         </is>
       </c>
       <c r="I147" s="14" t="inlineStr">
@@ -20112,17 +20160,732 @@
       </c>
       <c r="J147" s="14" t="inlineStr">
         <is>
-          <t>eTable3 (TNBC row)</t>
+          <t>Table 4</t>
         </is>
       </c>
       <c r="K147" s="15" t="inlineStr"/>
       <c r="L147" s="15" t="inlineStr"/>
       <c r="M147" s="16" t="inlineStr"/>
     </row>
+    <row r="148">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="inlineStr">
+        <is>
+          <t>Jin 2016</t>
+        </is>
+      </c>
+      <c r="C148" s="13" t="inlineStr">
+        <is>
+          <t>Japanese</t>
+        </is>
+      </c>
+      <c r="D148" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E148" s="13" t="inlineStr">
+        <is>
+          <t>disaggregated-AANHPI</t>
+        </is>
+      </c>
+      <c r="F148" s="13" t="inlineStr">
+        <is>
+          <t>127.8 [122.0, 133.8]</t>
+        </is>
+      </c>
+      <c r="G148" s="13" t="inlineStr">
+        <is>
+          <t>134.4 [133.8, 135.1]</t>
+        </is>
+      </c>
+      <c r="H148" s="13" t="inlineStr">
+        <is>
+          <t>0.951 [0.908, 0.996]</t>
+        </is>
+      </c>
+      <c r="I148" s="14" t="inlineStr">
+        <is>
+          <t>computed-from-rates-with-CI</t>
+        </is>
+      </c>
+      <c r="J148" s="14" t="inlineStr">
+        <is>
+          <t>Table 4</t>
+        </is>
+      </c>
+      <c r="K148" s="15" t="inlineStr"/>
+      <c r="L148" s="15" t="inlineStr"/>
+      <c r="M148" s="16" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="13" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="B149" s="14" t="inlineStr">
+        <is>
+          <t>Jin 2016</t>
+        </is>
+      </c>
+      <c r="C149" s="13" t="inlineStr">
+        <is>
+          <t>Korean</t>
+        </is>
+      </c>
+      <c r="D149" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E149" s="13" t="inlineStr">
+        <is>
+          <t>disaggregated-AANHPI</t>
+        </is>
+      </c>
+      <c r="F149" s="13" t="inlineStr">
+        <is>
+          <t>75.6 [71.4, 79.8]</t>
+        </is>
+      </c>
+      <c r="G149" s="13" t="inlineStr">
+        <is>
+          <t>134.4 [133.8, 135.1]</t>
+        </is>
+      </c>
+      <c r="H149" s="13" t="inlineStr">
+        <is>
+          <t>0.562 [0.532, 0.595]</t>
+        </is>
+      </c>
+      <c r="I149" s="14" t="inlineStr">
+        <is>
+          <t>computed-from-rates-with-CI</t>
+        </is>
+      </c>
+      <c r="J149" s="14" t="inlineStr">
+        <is>
+          <t>Table 4</t>
+        </is>
+      </c>
+      <c r="K149" s="15" t="inlineStr"/>
+      <c r="L149" s="15" t="inlineStr"/>
+      <c r="M149" s="16" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="13" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="B150" s="14" t="inlineStr">
+        <is>
+          <t>Jin 2016</t>
+        </is>
+      </c>
+      <c r="C150" s="13" t="inlineStr">
+        <is>
+          <t>Asian Indian/Pakistani</t>
+        </is>
+      </c>
+      <c r="D150" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E150" s="13" t="inlineStr">
+        <is>
+          <t>disaggregated-AANHPI</t>
+        </is>
+      </c>
+      <c r="F150" s="13" t="inlineStr">
+        <is>
+          <t>106.3 [101.9, 110.9]</t>
+        </is>
+      </c>
+      <c r="G150" s="13" t="inlineStr">
+        <is>
+          <t>134.4 [133.8, 135.1]</t>
+        </is>
+      </c>
+      <c r="H150" s="13" t="inlineStr">
+        <is>
+          <t>0.791 [0.758, 0.825]</t>
+        </is>
+      </c>
+      <c r="I150" s="14" t="inlineStr">
+        <is>
+          <t>computed-from-rates-with-CI</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="inlineStr">
+        <is>
+          <t>Table 4</t>
+        </is>
+      </c>
+      <c r="K150" s="15" t="inlineStr"/>
+      <c r="L150" s="15" t="inlineStr"/>
+      <c r="M150" s="16" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="13" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="B151" s="14" t="inlineStr">
+        <is>
+          <t>Jin 2016</t>
+        </is>
+      </c>
+      <c r="C151" s="13" t="inlineStr">
+        <is>
+          <t>Vietnamese</t>
+        </is>
+      </c>
+      <c r="D151" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E151" s="13" t="inlineStr">
+        <is>
+          <t>disaggregated-AANHPI</t>
+        </is>
+      </c>
+      <c r="F151" s="13" t="inlineStr">
+        <is>
+          <t>72.2 [67.9, 76.6]</t>
+        </is>
+      </c>
+      <c r="G151" s="13" t="inlineStr">
+        <is>
+          <t>134.4 [133.8, 135.1]</t>
+        </is>
+      </c>
+      <c r="H151" s="13" t="inlineStr">
+        <is>
+          <t>0.537 [0.506, 0.571]</t>
+        </is>
+      </c>
+      <c r="I151" s="14" t="inlineStr">
+        <is>
+          <t>computed-from-rates-with-CI</t>
+        </is>
+      </c>
+      <c r="J151" s="14" t="inlineStr">
+        <is>
+          <t>Table 4</t>
+        </is>
+      </c>
+      <c r="K151" s="15" t="inlineStr"/>
+      <c r="L151" s="15" t="inlineStr"/>
+      <c r="M151" s="16" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="13" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="B152" s="14" t="inlineStr">
+        <is>
+          <t>Jin 2016</t>
+        </is>
+      </c>
+      <c r="C152" s="13" t="inlineStr">
+        <is>
+          <t>Asian American (aggregate)</t>
+        </is>
+      </c>
+      <c r="D152" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E152" s="13" t="inlineStr">
+        <is>
+          <t>disaggregated-AANHPI</t>
+        </is>
+      </c>
+      <c r="F152" s="13" t="inlineStr">
+        <is>
+          <t>94.5 [93.0, 96.0]</t>
+        </is>
+      </c>
+      <c r="G152" s="13" t="inlineStr">
+        <is>
+          <t>134.4 [133.8, 135.1]</t>
+        </is>
+      </c>
+      <c r="H152" s="13" t="inlineStr">
+        <is>
+          <t>0.703 [0.692, 0.715]</t>
+        </is>
+      </c>
+      <c r="I152" s="14" t="inlineStr">
+        <is>
+          <t>computed-from-rates-with-CI</t>
+        </is>
+      </c>
+      <c r="J152" s="14" t="inlineStr">
+        <is>
+          <t>Table 4</t>
+        </is>
+      </c>
+      <c r="K152" s="15" t="inlineStr"/>
+      <c r="L152" s="15" t="inlineStr"/>
+      <c r="M152" s="16" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="13" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="B153" s="14" t="inlineStr">
+        <is>
+          <t>Watanabe-Galloway 2015</t>
+        </is>
+      </c>
+      <c r="C153" s="13" t="inlineStr">
+        <is>
+          <t>AIAN (Northern Plains)</t>
+        </is>
+      </c>
+      <c r="D153" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E153" s="13" t="inlineStr">
+        <is>
+          <t>AIAN</t>
+        </is>
+      </c>
+      <c r="F153" s="13" t="inlineStr">
+        <is>
+          <t>134.6</t>
+        </is>
+      </c>
+      <c r="G153" s="13" t="inlineStr">
+        <is>
+          <t>149.3</t>
+        </is>
+      </c>
+      <c r="H153" s="13" t="inlineStr">
+        <is>
+          <t>0.902</t>
+        </is>
+      </c>
+      <c r="I153" s="14" t="inlineStr">
+        <is>
+          <t>directly-reported-rate</t>
+        </is>
+      </c>
+      <c r="J153" s="14" t="inlineStr">
+        <is>
+          <t>Table 2 (All: AI/AN 134.6, NHW 149.3; RR 0.9)</t>
+        </is>
+      </c>
+      <c r="K153" s="15" t="inlineStr"/>
+      <c r="L153" s="15" t="inlineStr"/>
+      <c r="M153" s="16" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="13" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="B154" s="14" t="inlineStr">
+        <is>
+          <t>Melkonian 2022</t>
+        </is>
+      </c>
+      <c r="C154" s="13" t="inlineStr">
+        <is>
+          <t>AIAN</t>
+        </is>
+      </c>
+      <c r="D154" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E154" s="13" t="inlineStr">
+        <is>
+          <t>aggregate-vs-NHW</t>
+        </is>
+      </c>
+      <c r="F154" s="13" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G154" s="13" t="inlineStr">
+        <is>
+          <t>129.6</t>
+        </is>
+      </c>
+      <c r="H154" s="13" t="inlineStr">
+        <is>
+          <t>0.573</t>
+        </is>
+      </c>
+      <c r="I154" s="14" t="inlineStr">
+        <is>
+          <t>directly-reported-rate</t>
+        </is>
+      </c>
+      <c r="J154" s="14" t="inlineStr">
+        <is>
+          <t>Table 2 (urban AI/AN 74.2, urban NHW 129.6; RR 0.57)</t>
+        </is>
+      </c>
+      <c r="K154" s="15" t="inlineStr"/>
+      <c r="L154" s="15" t="inlineStr"/>
+      <c r="M154" s="16" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="13" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="B155" s="14" t="inlineStr">
+        <is>
+          <t>Amirikia 2011</t>
+        </is>
+      </c>
+      <c r="C155" s="13" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D155" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E155" s="13" t="inlineStr">
+        <is>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F155" s="13" t="inlineStr">
+        <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="G155" s="13" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="H155" s="13" t="inlineStr">
+        <is>
+          <t>1.873</t>
+        </is>
+      </c>
+      <c r="I155" s="14" t="inlineStr">
+        <is>
+          <t>computed-from-rates</t>
+        </is>
+      </c>
+      <c r="J155" s="14" t="inlineStr">
+        <is>
+          <t>Table 2 (age-specific TNBC by race)</t>
+        </is>
+      </c>
+      <c r="K155" s="15" t="inlineStr"/>
+      <c r="L155" s="15" t="inlineStr"/>
+      <c r="M155" s="16" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="13" t="inlineStr">
+        <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t>Amirikia 2011</t>
+        </is>
+      </c>
+      <c r="C156" s="13" t="inlineStr">
+        <is>
+          <t>Hispanic</t>
+        </is>
+      </c>
+      <c r="D156" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E156" s="13" t="inlineStr">
+        <is>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F156" s="13" t="inlineStr">
+        <is>
+          <t>10.2</t>
+        </is>
+      </c>
+      <c r="G156" s="13" t="inlineStr">
+        <is>
+          <t>12.6</t>
+        </is>
+      </c>
+      <c r="H156" s="13" t="inlineStr">
+        <is>
+          <t>0.810</t>
+        </is>
+      </c>
+      <c r="I156" s="14" t="inlineStr">
+        <is>
+          <t>computed-from-rates</t>
+        </is>
+      </c>
+      <c r="J156" s="14" t="inlineStr">
+        <is>
+          <t>Table 2 (age-specific TNBC by race)</t>
+        </is>
+      </c>
+      <c r="K156" s="15" t="inlineStr"/>
+      <c r="L156" s="15" t="inlineStr"/>
+      <c r="M156" s="16" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="13" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B157" s="14" t="inlineStr">
+        <is>
+          <t>Zhang 2022</t>
+        </is>
+      </c>
+      <c r="C157" s="13" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="D157" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="inlineStr">
+        <is>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F157" s="13" t="inlineStr">
+        <is>
+          <t>25.0</t>
+        </is>
+      </c>
+      <c r="G157" s="13" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="H157" s="13" t="inlineStr">
+        <is>
+          <t>1.953</t>
+        </is>
+      </c>
+      <c r="I157" s="14" t="inlineStr">
+        <is>
+          <t>directly-reported-rate</t>
+        </is>
+      </c>
+      <c r="J157" s="14" t="inlineStr">
+        <is>
+          <t>p.4 text (Figure 2A): 2019 AAIR by race</t>
+        </is>
+      </c>
+      <c r="K157" s="15" t="inlineStr"/>
+      <c r="L157" s="15" t="inlineStr"/>
+      <c r="M157" s="16" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="13" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B158" s="14" t="inlineStr">
+        <is>
+          <t>Zhang 2022</t>
+        </is>
+      </c>
+      <c r="C158" s="13" t="inlineStr">
+        <is>
+          <t>Hispanic</t>
+        </is>
+      </c>
+      <c r="D158" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E158" s="13" t="inlineStr">
+        <is>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F158" s="13" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="G158" s="13" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="H158" s="13" t="inlineStr">
+        <is>
+          <t>0.898</t>
+        </is>
+      </c>
+      <c r="I158" s="14" t="inlineStr">
+        <is>
+          <t>directly-reported-rate</t>
+        </is>
+      </c>
+      <c r="J158" s="14" t="inlineStr">
+        <is>
+          <t>p.4 text (Figure 2A): 2019 AAIR by race</t>
+        </is>
+      </c>
+      <c r="K158" s="15" t="inlineStr"/>
+      <c r="L158" s="15" t="inlineStr"/>
+      <c r="M158" s="16" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="13" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B159" s="14" t="inlineStr">
+        <is>
+          <t>Zhang 2022</t>
+        </is>
+      </c>
+      <c r="C159" s="13" t="inlineStr">
+        <is>
+          <t>AIAN</t>
+        </is>
+      </c>
+      <c r="D159" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E159" s="13" t="inlineStr">
+        <is>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F159" s="13" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="G159" s="13" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="H159" s="13" t="inlineStr">
+        <is>
+          <t>0.734</t>
+        </is>
+      </c>
+      <c r="I159" s="14" t="inlineStr">
+        <is>
+          <t>directly-reported-rate</t>
+        </is>
+      </c>
+      <c r="J159" s="14" t="inlineStr">
+        <is>
+          <t>p.4 text (Figure 2A): 2019 AAIR by race</t>
+        </is>
+      </c>
+      <c r="K159" s="15" t="inlineStr"/>
+      <c r="L159" s="15" t="inlineStr"/>
+      <c r="M159" s="16" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="13" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B160" s="14" t="inlineStr">
+        <is>
+          <t>Zhang 2022</t>
+        </is>
+      </c>
+      <c r="C160" s="13" t="inlineStr">
+        <is>
+          <t>Asian/PI (aggregate)</t>
+        </is>
+      </c>
+      <c r="D160" s="13" t="inlineStr">
+        <is>
+          <t>NHW</t>
+        </is>
+      </c>
+      <c r="E160" s="13" t="inlineStr">
+        <is>
+          <t>subtype-TNBC</t>
+        </is>
+      </c>
+      <c r="F160" s="13" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="G160" s="13" t="inlineStr">
+        <is>
+          <t>12.8</t>
+        </is>
+      </c>
+      <c r="H160" s="13" t="inlineStr">
+        <is>
+          <t>0.742</t>
+        </is>
+      </c>
+      <c r="I160" s="14" t="inlineStr">
+        <is>
+          <t>directly-reported-rate</t>
+        </is>
+      </c>
+      <c r="J160" s="14" t="inlineStr">
+        <is>
+          <t>p.4 text (Figure 2A): 2019 AAIR by race</t>
+        </is>
+      </c>
+      <c r="K160" s="15" t="inlineStr"/>
+      <c r="L160" s="15" t="inlineStr"/>
+      <c r="M160" s="16" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M147"/>
+  <autoFilter ref="A1:M160"/>
   <dataValidations count="1">
-    <dataValidation sqref="K3:K147" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K3:K160" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20137,7 +20900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21607,17 +22370,17 @@
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>Gomez2026_SEER21</t>
+          <t>Zhang 2022</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>SEER-21</t>
+          <t>NPCR+SEER (USCS)</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>2018-2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -21652,7 +22415,7 @@
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
@@ -21667,12 +22430,12 @@
       </c>
       <c r="M20" s="13" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="N20" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:No (unlinked national registry undercounts AI/AN); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O20" s="15" t="inlineStr"/>
@@ -21682,17 +22445,17 @@
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Gomez2010_CCR</t>
+          <t>Gomez2026_SEER21</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>California Cancer Registry</t>
+          <t>SEER-21</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>1988-2004</t>
+          <t>2018-2022</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
@@ -21727,7 +22490,7 @@
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
@@ -21742,12 +22505,12 @@
       </c>
       <c r="M21" s="13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:No (unlinked national registry undercounts AI/AN); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O21" s="15" t="inlineStr"/>
@@ -21757,17 +22520,17 @@
     <row r="22">
       <c r="A22" s="13" t="inlineStr">
         <is>
-          <t>Anderson2008_SEER_19066264</t>
+          <t>Gomez 2010</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>California Cancer Registry (CCR)</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1988-2004</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
@@ -21832,17 +22595,17 @@
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Kong2020_SEER18</t>
+          <t>Anderson2008_SEER_19066264</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>SEER 18</t>
+          <t>SEER</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>2010-2015</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
@@ -21882,7 +22645,7 @@
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="L23" s="13" t="inlineStr">
@@ -21892,12 +22655,12 @@
       </c>
       <c r="M23" s="13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Unclear (standard population not clearly stated); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O23" s="15" t="inlineStr"/>
@@ -21907,17 +22670,17 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>Gomez2017_CCR</t>
+          <t>Kong2020_SEER18</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>California Cancer Registry</t>
+          <t>SEER 18</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>2009-2013</t>
+          <t>2010-2015</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -21982,7 +22745,7 @@
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>Keegan2010_CCR</t>
+          <t>Gomez2017_CCR</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
@@ -21992,7 +22755,7 @@
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>1988-2004</t>
+          <t>2009-2013</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
@@ -22057,17 +22820,17 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>Richardson2016_27736827</t>
+          <t>Keegan2010_CCR</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>USCS(NPCR+SEER)</t>
+          <t>California Cancer Registry</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1988-2004</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
@@ -22132,17 +22895,17 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>Lund2010_AtlantaSEER</t>
+          <t>Richardson2016_27736827</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>Metropolitan Atlanta (SEER)</t>
+          <t>USCS(NPCR+SEER)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>2003-2004</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
@@ -22182,7 +22945,7 @@
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L27" s="13" t="inlineStr">
@@ -22192,12 +22955,12 @@
       </c>
       <c r="M27" s="13" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:No (age-adjusted estimate reported as a point value without a variance/CI); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O27" s="15" t="inlineStr"/>
@@ -22207,17 +22970,17 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>Keegan2007_GBACR</t>
+          <t>Lund2010_AtlantaSEER</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>Greater Bay Area (Northern CA, SEER)</t>
+          <t>Metropolitan Atlanta (SEER)</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>1990-2002</t>
+          <t>2003-2004</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
@@ -22257,7 +23020,7 @@
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L28" s="13" t="inlineStr">
@@ -22267,12 +23030,12 @@
       </c>
       <c r="M28" s="13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="N28" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:No (age-adjusted estimate reported as a point value without a variance/CI); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O28" s="15" t="inlineStr"/>
@@ -22282,17 +23045,17 @@
     <row r="29">
       <c r="A29" s="13" t="inlineStr">
         <is>
-          <t>Harper2009_SEER</t>
+          <t>Amirikia 2011</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>SEER</t>
+          <t>California Cancer Registry (CCR)</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1988-2006</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
@@ -22357,17 +23120,17 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>Gopalani2020_31764279</t>
+          <t>Watanabe-Galloway 2015</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>IHS-linked</t>
+          <t>NE/ND/SD state registries</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>1999-2015</t>
+          <t>2002-2009</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
@@ -22392,7 +23155,7 @@
       </c>
       <c r="H30" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Unclear</t>
         </is>
       </c>
       <c r="I30" s="13" t="inlineStr">
@@ -22402,7 +23165,7 @@
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
@@ -22417,12 +23180,12 @@
       </c>
       <c r="M30" s="13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="N30" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (IHS/tribal registry linkage (validated AI/AN classification)); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Unclear (registry coverage/completeness not documented); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:No (unlinked national registry undercounts AI/AN); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O30" s="15" t="inlineStr"/>
@@ -22432,17 +23195,17 @@
     <row r="31">
       <c r="A31" s="13" t="inlineStr">
         <is>
-          <t>Ihenacho2023_HTR</t>
+          <t>Keegan2007_GBACR</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>Hawaii Tumor Registry (SEER)</t>
+          <t>Greater Bay Area (Northern CA, SEER)</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>2010-2014</t>
+          <t>1990-2002</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
@@ -22507,17 +23270,17 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>Nasseri2009</t>
+          <t>Harper2009_SEER</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>California-CCR</t>
+          <t>SEER</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>1988-2004</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -22552,14 +23315,14 @@
       </c>
       <c r="J32" s="13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="L32" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -22572,7 +23335,7 @@
       </c>
       <c r="N32" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:No (race/ethnicity by surname recognition (misclassification risk)); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:No (age-adjusted estimate reported as a point value without a variance/CI); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O32" s="15" t="inlineStr"/>
@@ -22582,17 +23345,17 @@
     <row r="33">
       <c r="A33" s="13" t="inlineStr">
         <is>
-          <t>Goggins2009</t>
+          <t>Gopalani2020_31764279</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>SEER (SF/Seattle/Detroit/Atlanta/CT/LA/SanJose)</t>
+          <t>IHS-linked</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>1988-2004</t>
+          <t>1999-2015</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
@@ -22647,7 +23410,7 @@
       </c>
       <c r="N33" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (IHS/tribal registry linkage (validated AI/AN classification)); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O33" s="15" t="inlineStr"/>
@@ -22657,17 +23420,17 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>Yazzie2025_Navajo</t>
+          <t>Ihenacho2023_HTR</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>Navajo Nation registry (IHS)</t>
+          <t>Hawaii Tumor Registry (SEER)</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>2014-2018</t>
+          <t>2010-2014</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
@@ -22722,7 +23485,7 @@
       </c>
       <c r="N34" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (IHS/tribal registry linkage (validated AI/AN classification)); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O34" s="15" t="inlineStr"/>
@@ -22732,17 +23495,17 @@
     <row r="35">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>Xie2022_USCS</t>
+          <t>Nasseri2009</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>USCS(NPCR+SEER)</t>
+          <t>California-CCR</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>1999-2017</t>
+          <t>1988-2004</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
@@ -22777,7 +23540,7 @@
       </c>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -22792,12 +23555,12 @@
       </c>
       <c r="M35" s="13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="N35" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:No (race/ethnicity by surname recognition (misclassification risk)); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O35" s="15" t="inlineStr"/>
@@ -22807,17 +23570,17 @@
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>Sung2020_USCS50</t>
+          <t>Goggins2009</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>USCS 50-state (NPCR+SEER)</t>
+          <t>SEER (SF/Seattle/Detroit/Atlanta/CT/LA/SanJose)</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>2011-2015</t>
+          <t>1988-2004</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
@@ -22882,17 +23645,17 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>Melkonian2019_IHS-PRCDA</t>
+          <t>Yazzie2025_Navajo</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>IHS-linked (NPCR/SEER, PRCDA)</t>
+          <t>Navajo Nation registry (IHS)</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>2012-2016</t>
+          <t>2014-2018</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -22957,17 +23720,17 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>Pinheiro2009_FL</t>
+          <t>Xie2022_USCS</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>Florida Cancer Registry</t>
+          <t>USCS(NPCR+SEER)</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>1999-2001</t>
+          <t>1999-2017</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -23032,17 +23795,17 @@
     <row r="39">
       <c r="A39" s="13" t="inlineStr">
         <is>
-          <t>Kem2007</t>
+          <t>Melkonian 2022</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>California-CCR + Puget Sound (SEER)</t>
+          <t>USCS-AIAD urban (IHS-linked, UIHO)</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>1998-2002</t>
+          <t>2008-2017</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
@@ -23077,7 +23840,7 @@
       </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -23092,12 +23855,12 @@
       </c>
       <c r="M39" s="13" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="N39" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:No (race/ethnicity by surname recognition (misclassification risk)); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (IHS/tribal registry linkage (validated AI/AN classification)); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O39" s="15" t="inlineStr"/>
@@ -23107,17 +23870,17 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>Carozza2006_multistate</t>
+          <t>Sung2020_USCS50</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>Multi-state registries (NAACCR)</t>
+          <t>USCS 50-state (NPCR+SEER)</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>1995-2000</t>
+          <t>2011-2015</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
@@ -23182,17 +23945,17 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>Gomez2003_SEERplusCCR</t>
+          <t>Melkonian2019_IHS-PRCDA</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>SEER + California CR</t>
+          <t>IHS-linked (NPCR/SEER, PRCDA)</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>1988-1992</t>
+          <t>2012-2016</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -23247,7 +24010,7 @@
       </c>
       <c r="N41" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (IHS/tribal registry linkage (validated AI/AN classification)); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O41" s="15" t="inlineStr"/>
@@ -23257,17 +24020,17 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>Melkonian2021_IHS-PRCDA</t>
+          <t>Pinheiro2009_FL</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>IHS-linked (NPCR/SEER, PRCDA)</t>
+          <t>Florida Cancer Registry</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>2012-2016</t>
+          <t>1999-2001</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
@@ -23322,7 +24085,7 @@
       </c>
       <c r="N42" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (IHS/tribal registry linkage (validated AI/AN classification)); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O42" s="15" t="inlineStr"/>
@@ -23332,12 +24095,12 @@
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>Miller2008_NAACCR-API</t>
+          <t>Kem2007</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>NAACCR/SEER API (state+SEER registries)</t>
+          <t>California-CCR + Puget Sound (SEER)</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
@@ -23377,7 +24140,7 @@
       </c>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -23392,12 +24155,12 @@
       </c>
       <c r="M43" s="13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="N43" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:No (race/ethnicity by surname recognition (misclassification risk)); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O43" s="15" t="inlineStr"/>
@@ -23407,17 +24170,17 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>McCracken2007_CCR</t>
+          <t>Carozza2006_multistate</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>California Cancer Registry</t>
+          <t>Multi-state registries (NAACCR)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>2000-2002</t>
+          <t>1995-2000</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -23457,7 +24220,7 @@
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
@@ -23467,12 +24230,12 @@
       </c>
       <c r="M44" s="13" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="N44" s="13" t="inlineStr">
         <is>
-          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:No (age-adjusted estimate reported as a point value without a variance/CI); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
         </is>
       </c>
       <c r="O44" s="15" t="inlineStr"/>
@@ -23482,17 +24245,17 @@
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>Wilkinson2002</t>
+          <t>Gomez2003_SEERplusCCR</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>Florida (Miami-Dade FCDS)</t>
+          <t>SEER + California CR</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>1990-1998</t>
+          <t>1988-1992</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
@@ -23554,13 +24317,388 @@
       <c r="P45" s="16" t="inlineStr"/>
       <c r="Q45" s="15" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>Melkonian2021_IHS-PRCDA</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="inlineStr">
+        <is>
+          <t>IHS-linked (NPCR/SEER, PRCDA)</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>2012-2016</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L46" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M46" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N46" s="13" t="inlineStr">
+        <is>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (IHS/tribal registry linkage (validated AI/AN classification)); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+        </is>
+      </c>
+      <c r="O46" s="15" t="inlineStr"/>
+      <c r="P46" s="16" t="inlineStr"/>
+      <c r="Q46" s="15" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>Jin 2016</t>
+        </is>
+      </c>
+      <c r="B47" s="13" t="inlineStr">
+        <is>
+          <t>8-state SEER+NPCR (Jin)</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>2009-2011</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M47" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N47" s="13" t="inlineStr">
+        <is>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+        </is>
+      </c>
+      <c r="O47" s="15" t="inlineStr"/>
+      <c r="P47" s="16" t="inlineStr"/>
+      <c r="Q47" s="15" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>Miller2008_NAACCR-API</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>NAACCR/SEER API (state+SEER registries)</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>1998-2002</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L48" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M48" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N48" s="13" t="inlineStr">
+        <is>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+        </is>
+      </c>
+      <c r="O48" s="15" t="inlineStr"/>
+      <c r="P48" s="16" t="inlineStr"/>
+      <c r="Q48" s="15" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>McCracken2007_CCR</t>
+        </is>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
+        <is>
+          <t>California Cancer Registry</t>
+        </is>
+      </c>
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>2000-2002</t>
+        </is>
+      </c>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F49" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L49" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M49" s="13" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="N49" s="13" t="inlineStr">
+        <is>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:No (age-adjusted estimate reported as a point value without a variance/CI); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+        </is>
+      </c>
+      <c r="O49" s="15" t="inlineStr"/>
+      <c r="P49" s="16" t="inlineStr"/>
+      <c r="Q49" s="15" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>Wilkinson2002</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
+        <is>
+          <t>Florida (Miami-Dade FCDS)</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>1990-1998</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L50" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M50" s="13" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N50" s="13" t="inlineStr">
+        <is>
+          <t>Q1_frame:Yes (population-based cancer registry covering a defined population); Q2_sampling:Yes (registry ascertains all diagnosed cases (census-like)); Q3_size:Yes (national/multi-registry or adequate case count for a stable rate); Q4_described:Yes (registry, diagnosis period, groups and standard population described); Q5_coverage:Yes (high-completeness registry); Q6_condition:Yes (invasive breast cancer via registry/pathology record linkage); Q7_measurement:Yes (standard registry race/ethnicity coding; ICD-O condition coding); Q8_analysis:Yes (age-standardized to a stated standard with a reported/computed variance); Q9_response:Yes (not applicable (census-like registry ascertainment))</t>
+        </is>
+      </c>
+      <c r="O50" s="15" t="inlineStr"/>
+      <c r="P50" s="16" t="inlineStr"/>
+      <c r="Q50" s="15" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q45"/>
+  <autoFilter ref="A1:Q50"/>
   <dataValidations count="2">
-    <dataValidation sqref="O3:O45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O3:O50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="P3:P45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P3:P50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Low,Moderate,High"</formula1>
     </dataValidation>
   </dataValidations>
